--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>更新日期：2024.10.10 07:31:09</t>
+          <t>更新日期：2024.10.10 13:18:14</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>maa://38298 (82.14)</t>
+          <t>maa://38298 (82.76)</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>maa://23020 (95.77), maa://29023 (100.0), maa://34319 (100.0), *maa://39515 (66.67)</t>
+          <t>maa://23020 (95.77), maa://29023 (100.0), maa://34319 (100.0), *maa://39515 (66.67), maa://41690 (100.0)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>maa://32414 (98.41), maa://32505 (100.0), maa://39155 (94.44)</t>
+          <t>maa://32414 (98.42), maa://32505 (100.0), maa://39155 (94.44)</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D314" s="12" t="inlineStr">
         <is>
-          <t>maa://32647 (96.86), maa://32415 (96.26), maa://34677 (100.0), maa://32892 (100.0)</t>
+          <t>maa://32647 (96.87), maa://32415 (96.26), maa://34677 (100.0), maa://32892 (100.0)</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="D330" s="12" t="inlineStr">
         <is>
-          <t>*maa://40957 (76.92), *maa://41128 (69.23), *maa://41035 (75.0)</t>
+          <t>*maa://40957 (77.78), *maa://41128 (69.23), *maa://41035 (75.0)</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>更新日期：2024.10.17 12:52:30</t>
+          <t>更新日期：2024.10.17 13:18:35</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>更新日期：2024.10.20 13:17:20</t>
+          <t>更新日期：2024.10.21 13:19:04</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>maa://20976 (97.56), maa://20815 (100.0)</t>
+          <t>maa://20976 (97.58), maa://20815 (100.0)</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>maa://24472 (84.67), *maa://35841 (54.55)</t>
+          <t>maa://24472 (84.78), *maa://35841 (54.55)</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>maa://29627 (92.55), maa://29633 (92.02), maa://29659 (82.14), maa://29861 (100.0)</t>
+          <t>maa://29627 (92.55), maa://29633 (92.06), maa://29659 (82.14), maa://29861 (100.0)</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>maa://25760 (82.26), *maa://35854 (69.23), **maa://20872 (50.0)</t>
+          <t>maa://25760 (82.54), *maa://35854 (69.23), **maa://20872 (50.0)</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>maa://20956 (95.14), *maa://20830 (77.78)</t>
+          <t>maa://20956 (95.17), *maa://20830 (77.78)</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>*maa://30667 (75.61), maa://30666 (83.07), *maa://26836 (75.0), **maa://30739 (45.71), maa://37607 (92.13), *maa://34428 (66.2), *maa://30723 (51.92), maa://39588 (85.71), *maa://37850 (66.67)</t>
+          <t>*maa://30667 (75.61), maa://30666 (83.07), *maa://26836 (75.0), **maa://30739 (45.71), maa://37607 (92.19), *maa://34428 (66.2), *maa://30723 (51.92), maa://39588 (85.71), *maa://37850 (66.67)</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>maa://32414 (98.44), maa://32505 (100.0), maa://39155 (94.74)</t>
+          <t>maa://32414 (98.45), maa://32505 (100.0), maa://39155 (94.74)</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>maa://39692 (99.43), *maa://39810 (80.0)</t>
+          <t>maa://39692 (99.44), *maa://39810 (80.0)</t>
         </is>
       </c>
       <c r="E297" s="3" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>maa://30671 (81.34), maa://30669 (98.28), maa://37275 (82.35), *maa://32410 (63.64), maa://41605 (100.0), maa://33671 (100.0)</t>
+          <t>maa://30671 (81.34), maa://30669 (98.31), maa://37275 (82.35), *maa://32410 (63.64), maa://41605 (100.0), maa://33671 (100.0)</t>
         </is>
       </c>
       <c r="E309" s="3" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D314" s="12" t="inlineStr">
         <is>
-          <t>maa://32647 (96.93), maa://32415 (96.3), maa://34677 (100.0), maa://32892 (100.0)</t>
+          <t>maa://32647 (96.94), maa://32415 (96.3), maa://34677 (100.0), maa://32892 (100.0)</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>maa://36646 (98.26), maa://36845 (94.19), **maa://39217 (41.67)</t>
+          <t>maa://36646 (98.28), maa://36845 (94.19), **maa://39217 (41.67)</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="D326" s="12" t="inlineStr">
         <is>
-          <t>maa://36645 (98.24), maa://36841 (93.33), maa://37484 (93.18), maa://37858 (90.91)</t>
+          <t>maa://36645 (98.25), maa://36841 (93.33), maa://37484 (93.18), maa://37858 (90.91)</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="D330" s="12" t="inlineStr">
         <is>
-          <t>*maa://40957 (78.18), *maa://41128 (73.33), *maa://41035 (80.0)</t>
+          <t>*maa://40957 (79.31), *maa://41128 (73.33), *maa://41035 (80.0)</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -502,7 +502,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>更新日期：2024.10.23 13:18:28</t>
+          <t>更新日期：2024.10.24 13:19:30</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>maa://30500 (98.15), *maa://27290 (70.59), maa://42154 (100.0)</t>
+          <t>maa://30500 (98.18), *maa://27290 (70.59), maa://42154 (100.0)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>*maa://20916 (79.17)</t>
+          <t>*maa://20916 (76.92)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>maa://20953 (94.44), maa://31173 (85.71)</t>
+          <t>maa://20953 (94.44), maa://31173 (87.5)</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>*maa://20965 (69.23)</t>
+          <t>*maa://20965 (70.37)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>maa://38298 (82.76)</t>
+          <t>maa://38298 (83.33)</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>maa://20844 (95.83)</t>
+          <t>maa://20844 (96.0)</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>maa://28187 (96.67), maa://33504 (100.0), maa://39520 (100.0)</t>
+          <t>maa://28187 (96.88), maa://33504 (100.0), maa://39520 (100.0)</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>maa://28567 (97.37), **maa://20947 (44.12), maa://30525 (100.0), *maa://28188 (75.0), maa://38735 (100.0), maa://30524 (100.0)</t>
+          <t>maa://28567 (97.44), **maa://20947 (44.12), maa://30525 (100.0), *maa://28188 (75.0), maa://38735 (100.0), maa://30524 (100.0)</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>maa://36643 (97.24), maa://36864 (100.0), maa://39140 (100.0)</t>
+          <t>maa://36643 (97.27), maa://36864 (100.0), maa://39140 (100.0)</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>*maa://28190 (56.67), maa://20880 (89.47)</t>
+          <t>*maa://28190 (56.67), maa://20880 (90.0)</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>maa://24609 (87.5)</t>
+          <t>maa://24609 (88.24)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>*maa://39240 (57.14), maa://40517 (88.89)</t>
+          <t>*maa://39240 (57.14), maa://40517 (90.0)</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>*maa://29094 (60.61), maa://28904 (86.36), **maa://20931 (42.31)</t>
+          <t>*maa://29094 (60.61), maa://28904 (83.33), **maa://20931 (42.31)</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>*maa://20933 (76.09), maa://20822 (100.0)</t>
+          <t>*maa://20933 (76.6), maa://20822 (100.0)</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>maa://29650 (97.37)</t>
+          <t>maa://29650 (97.5)</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>maa://23019 (100.0), maa://20837 (100.0), maa://37113 (100.0), maa://40517 (88.89), *maa://37666 (75.0), maa://41686 (100.0)</t>
+          <t>maa://23019 (100.0), maa://20837 (100.0), maa://37113 (100.0), maa://40517 (90.0), *maa://37666 (75.0), maa://41686 (100.0)</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>maa://23020 (95.77), maa://29023 (100.0), maa://34319 (100.0), *maa://39515 (75.0), maa://41690 (100.0)</t>
+          <t>maa://23020 (95.83), maa://29023 (100.0), maa://34319 (100.0), *maa://39515 (75.0), maa://41690 (100.0)</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>maa://36641 (98.2), maa://36865 (95.33), maa://37300 (100.0)</t>
+          <t>maa://36641 (98.21), maa://36865 (95.37), maa://37300 (100.0)</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>maa://25760 (82.81), *maa://35854 (69.23), **maa://20872 (50.0)</t>
+          <t>maa://25760 (83.08), *maa://35854 (69.23), **maa://20872 (50.0)</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>maa://20956 (95.21), *maa://20830 (77.78)</t>
+          <t>maa://20956 (95.24), *maa://20830 (77.78)</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>maa://39238 (98.86)</t>
+          <t>maa://39238 (98.88)</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>maa://28187 (96.67), maa://39520 (100.0)</t>
+          <t>maa://28187 (96.88), maa://39520 (100.0)</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>*maa://30667 (75.76), maa://30666 (83.16), *maa://26836 (75.18), **maa://30739 (45.71), maa://37607 (92.25), *maa://34428 (66.2), *maa://30723 (51.92), maa://39588 (85.71), *maa://37850 (66.67)</t>
+          <t>*maa://30667 (75.83), maa://30666 (83.16), *maa://26836 (75.36), **maa://30739 (45.71), maa://37607 (92.31), *maa://34428 (66.2), *maa://30723 (51.92), maa://39588 (85.71), *maa://37850 (66.67)</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>maa://20867 (92.86), *maa://32202 (80.0), *maa://38485 (75.0)</t>
+          <t>maa://20867 (92.86), *maa://32202 (80.0), *maa://38485 (80.0)</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="D237" s="14" t="inlineStr">
         <is>
-          <t>maa://42287 (100.0), maa://42225 (100.0)</t>
+          <t>maa://42287 (85.71), maa://42225 (100.0)</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
@@ -7627,7 +7627,7 @@
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>maa://22467 (93.1)</t>
+          <t>maa://22467 (93.33)</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>maa://20899 (90.07)</t>
+          <t>maa://20899 (90.14)</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>maa://32414 (98.45), maa://32505 (100.0), maa://39155 (94.74)</t>
+          <t>maa://32414 (98.46), maa://32505 (100.0), maa://39155 (94.74)</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="D290" s="12" t="inlineStr">
         <is>
-          <t>maa://25775 (92.45), *maa://25393 (76.92)</t>
+          <t>maa://25775 (92.59), *maa://25393 (76.92)</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>maa://39692 (99.45), *maa://39810 (80.0)</t>
+          <t>maa://39692 (99.46), *maa://39810 (80.0)</t>
         </is>
       </c>
       <c r="E297" s="3" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>maa://30671 (81.34), maa://30669 (98.31), maa://37275 (82.35), *maa://32410 (63.64), maa://41605 (100.0), maa://33671 (100.0)</t>
+          <t>maa://30671 (81.48), maa://30669 (98.36), maa://37275 (82.35), *maa://32410 (63.64), maa://41605 (100.0), maa://33671 (100.0)</t>
         </is>
       </c>
       <c r="E309" s="3" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D314" s="12" t="inlineStr">
         <is>
-          <t>maa://32647 (96.97), maa://32415 (96.3), maa://34677 (100.0), maa://32892 (100.0)</t>
+          <t>maa://32647 (96.97), maa://32415 (96.33), maa://34677 (100.0), maa://32892 (100.0)</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="D319" s="12" t="inlineStr">
         <is>
-          <t>maa://34865 (96.48), maa://34717 (92.73)</t>
+          <t>maa://34865 (96.5), maa://34717 (92.73)</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="D324" s="12" t="inlineStr">
         <is>
-          <t>**maa://42224 (50.0), maa://42299 (100.0)</t>
+          <t>maa://42299 (100.0), **maa://42224 (50.0)</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="D330" s="12" t="inlineStr">
         <is>
-          <t>*maa://40957 (79.66), *maa://41128 (75.0), *maa://41035 (80.0)</t>
+          <t>maa://40957 (80.33), *maa://41128 (75.0), maa://41035 (81.82)</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="D336" s="14" t="inlineStr">
         <is>
-          <t>maa://41110 (96.97)</t>
+          <t>maa://41110 (97.06)</t>
         </is>
       </c>
       <c r="E336" s="14" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2024.12.08 15:46:46</t>
+          <t>更新日期：2024.12.10 13:19:52</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -1044,27 +1044,27 @@
       <c r="AB14" s="11" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>慕斯</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>2-2</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>maa://44401 (100.0)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>&gt; 完成5次战斗；必须编入非助战慕斯并上场，且每次战斗至少释放1次炸毛&gt; 3星通关主题曲2-2；必须编入非助战慕斯并上场，且队伍中不能有术师干员</t>
         </is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>maa://44235 (84.21)</t>
+          <t>maa://44235 (86.36)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>maa://20976 (97.73), maa://20815 (100.0)</t>
+          <t>maa://20976 (97.75), maa://20815 (100.0)</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>maa://36643 (97.4), maa://36864 (97.06), maa://39140 (100.0)</t>
+          <t>maa://36643 (97.42), maa://36864 (97.06), maa://39140 (100.0)</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>maa://25018 (96.21), maa://25776 (90.48), maa://28361 (96.77), maa://25772 (92.5), *maa://25161 (80.0), maa://32653 (85.71)</t>
+          <t>maa://25018 (96.22), maa://25776 (90.48), maa://28361 (96.77), maa://25772 (92.5), *maa://25161 (80.0), maa://32653 (85.71)</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>maa://21422 (98.82)</t>
+          <t>maa://21422 (98.84)</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>maa://44232 (95.45), maa://44305 (100.0)</t>
+          <t>maa://44232 (96.08), maa://44305 (100.0)</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>maa://20975 (90.0), maa://30806 (100.0)</t>
+          <t>maa://20975 (90.91), maa://30806 (100.0)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>maa://32418 (99.5)</t>
+          <t>maa://32418 (99.51)</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>maa://42223 (99.27), maa://42292 (94.12), maa://42402 (100.0)</t>
+          <t>maa://42223 (99.28), maa://42292 (94.12), maa://42402 (100.0)</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.17), maa://36845 (94.85), maa://31558 (96.55), **maa://39217 (35.71), maa://30668 (84.62)</t>
+          <t>maa://30710 (97.2), maa://36845 (94.85), maa://31558 (96.77), **maa://39217 (35.71), maa://30668 (84.62)</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="D304" s="12" t="inlineStr">
         <is>
-          <t>maa://39692 (99.65), maa://39810 (81.25)</t>
+          <t>maa://39692 (99.66), maa://39810 (81.25)</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="D315" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (95.24)</t>
+          <t>maa://44234 (96.15)</t>
         </is>
       </c>
       <c r="E315" s="3" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="D316" s="12" t="inlineStr">
         <is>
-          <t>maa://42968 (99.41)</t>
+          <t>maa://42968 (99.42)</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D319" s="12" t="inlineStr">
         <is>
-          <t>maa://30671 (80.95), maa://30669 (98.57), maa://37275 (82.86), *maa://32410 (63.64), maa://41605 (100.0), maa://33671 (100.0)</t>
+          <t>maa://30671 (80.95), maa://30669 (98.59), maa://37275 (82.86), *maa://32410 (63.64), maa://41605 (100.0), maa://33671 (100.0)</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="D320" s="12" t="inlineStr">
         <is>
-          <t>maa://38295 (96.3)</t>
+          <t>maa://38295 (96.36)</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="D334" s="14" t="inlineStr">
         <is>
-          <t>maa://42299 (93.33), **maa://42224 (50.0)</t>
+          <t>maa://42299 (93.75), **maa://42224 (50.0)</t>
         </is>
       </c>
       <c r="E334" s="14" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D335" s="14" t="inlineStr">
         <is>
-          <t>maa://36646 (98.56), maa://36845 (94.85), **maa://39217 (35.71)</t>
+          <t>maa://36646 (98.57), maa://36845 (94.85), **maa://39217 (35.71)</t>
         </is>
       </c>
       <c r="E335" s="14" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>maa://40957 (85.11), maa://41035 (88.89), maa://41128 (80.77)</t>
+          <t>maa://40957 (85.11), maa://41035 (89.19), maa://41128 (80.77)</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>maa://41110 (97.87)</t>
+          <t>maa://41110 (97.92)</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>*maa://42970 (79.31)</t>
+          <t>maa://42970 (80.22)</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.02.22 13:17:25</t>
+          <t>更新日期：2025.02.26 13:18:30</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>*maa://20849 (64.1), *maa://28758 (60.61), maa://29036 (95.0), *maa://42172 (75.0), maa://30285 (100.0)</t>
+          <t>*maa://20849 (64.1), *maa://28758 (60.61), maa://29036 (95.24), *maa://42172 (75.0), maa://30285 (100.0)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>maa://36644 (87.66), maa://36866 (97.73), maa://27794 (100.0), maa://45572 (100.0)</t>
+          <t>maa://36644 (87.74), maa://36866 (97.73), maa://27794 (100.0), maa://45572 (100.0)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>maa://44235 (96.94), maa://45604 (100.0)</t>
+          <t>maa://44235 (97.0), maa://45604 (100.0)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>maa://38298 (85.33)</t>
+          <t>maa://38298 (84.62)</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>maa://28784 (94.12), maa://29088 (91.75), maa://20974 (96.0), maa://31124 (96.72), maa://28950 (92.31), *maa://33612 (75.0), maa://29087 (100.0), *maa://20823 (80.0), **maa://42200 (50.0), maa://41832 (85.71)</t>
+          <t>maa://28784 (94.12), maa://29088 (91.75), maa://20974 (96.0), maa://31124 (96.77), maa://28950 (92.31), *maa://33612 (75.0), maa://29087 (100.0), *maa://20823 (80.0), **maa://42200 (50.0), maa://41832 (85.71)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>maa://20943 (99.25)</t>
+          <t>maa://20943 (99.26)</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>maa://24472 (87.29), *maa://35841 (61.54)</t>
+          <t>maa://24472 (87.36), *maa://35841 (61.54)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>maa://20966 (100.0)</t>
+          <t>*maa://20966 (75.0)</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>maa://25018 (95.99), maa://25776 (90.91), maa://28361 (96.88), maa://25772 (93.75), *maa://25161 (80.0), maa://32653 (85.71), *maa://45194 (80.0)</t>
+          <t>maa://25018 (96.01), maa://25776 (90.91), maa://28361 (96.97), maa://25772 (93.75), *maa://25161 (80.0), maa://32653 (85.71), maa://45194 (83.33)</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>*maa://28554 (77.27), *maa://45081 (66.67)</t>
+          <t>*maa://28554 (78.26), *maa://45081 (66.67)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>maa://20908 (98.22), maa://35723 (95.12), *maa://23346 (77.78), maa://38822 (100.0)</t>
+          <t>maa://20908 (98.23), maa://35723 (95.12), *maa://23346 (77.78), maa://38822 (100.0)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>maa://36641 (98.19), maa://36865 (96.3), maa://42918 (100.0), maa://44119 (97.3), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
+          <t>maa://36641 (98.2), maa://36865 (96.32), maa://42918 (100.0), maa://44119 (97.3), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>maa://44232 (99.0), maa://44305 (100.0), maa://45603 (95.24)</t>
+          <t>maa://44232 (99.02), maa://44305 (100.0), maa://45603 (95.24)</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>maa://29633 (93.77), maa://29627 (92.96), maa://29659 (83.87), maa://29861 (100.0)</t>
+          <t>maa://29633 (93.84), maa://29627 (93.0), maa://29659 (83.87), maa://29861 (100.0)</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>maa://32418 (99.62)</t>
+          <t>maa://32418 (99.63)</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>maa://20969 (85.19), maa://41303 (100.0)</t>
+          <t>maa://20969 (85.71), maa://41303 (100.0)</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (88.21), *maa://35854 (77.08), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (13.33)</t>
+          <t>maa://44224 (87.82), *maa://35854 (77.08), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (13.33)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>maa://28133 (91.11), maa://28277 (80.77), **maa://39217 (37.5), maa://25369 (93.75), *maa://33132 (66.67)</t>
+          <t>maa://28133 (91.3), maa://28277 (80.77), **maa://39217 (37.5), maa://25369 (93.75), *maa://33132 (66.67)</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>maa://20878 (87.1)</t>
+          <t>maa://20878 (87.5)</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>maa://20922 (92.98), *maa://32623 (68.75), *maa://34242 (80.0), maa://34900 (84.62)</t>
+          <t>maa://20922 (93.1), *maa://32623 (68.75), *maa://34242 (80.0), maa://34900 (84.62)</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>*maa://30667 (77.62), maa://30666 (83.81), *maa://26836 (78.48), maa://37607 (94.43), *maa://34428 (70.83), **maa://30739 (44.44), *maa://30723 (54.39), maa://39588 (89.13), *maa://37850 (75.0)</t>
+          <t>*maa://30667 (77.43), maa://30666 (83.49), *maa://26836 (78.62), maa://37607 (94.5), *maa://34428 (71.13), **maa://30739 (44.44), *maa://30723 (55.17), maa://39588 (89.58), *maa://37850 (75.0)</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>maa://20867 (92.86), maa://38485 (92.31), *maa://32202 (80.0)</t>
+          <t>maa://20867 (92.86), maa://38485 (93.33), *maa://32202 (80.0)</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>maa://28923 (91.23), maa://28906 (98.0), ***maa://28825 (12.0)</t>
+          <t>maa://28923 (91.23), maa://28906 (98.08), ***maa://28825 (12.0)</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>maa://42287 (92.73), maa://45570 (100.0), maa://42225 (100.0)</t>
+          <t>maa://42287 (93.1), maa://45570 (100.0), maa://42225 (100.0)</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>maa://22467 (94.74)</t>
+          <t>maa://22467 (94.87)</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>maa://28133 (91.11), maa://33394 (100.0)</t>
+          <t>maa://28133 (91.3), maa://33394 (100.0)</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.58), maa://36845 (95.58), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.19)</t>
+          <t>maa://30710 (97.6), maa://36845 (95.58), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.19)</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>maa://25774 (98.41), maa://28133 (91.11), maa://22469 (91.84), **maa://39217 (37.5), **maa://31349 (50.0)</t>
+          <t>maa://25774 (98.41), maa://28133 (91.3), maa://22469 (92.0), **maa://39217 (37.5), **maa://31349 (50.0)</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>maa://32414 (98.64), maa://32505 (100.0), maa://39155 (96.43)</t>
+          <t>maa://32414 (98.65), maa://32505 (100.0), maa://39155 (96.43)</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D294" s="12" t="inlineStr">
         <is>
-          <t>maa://36005 (100.0)</t>
+          <t>maa://36005 (90.0)</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="D301" s="12" t="inlineStr">
         <is>
-          <t>*maa://43090 (72.73)</t>
+          <t>*maa://43090 (66.67)</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>maa://34867 (97.3), maa://34715 (100.0)</t>
+          <t>maa://34867 (97.37), maa://34715 (100.0)</t>
         </is>
       </c>
       <c r="E309" s="3" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D317" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (98.46)</t>
+          <t>maa://44234 (98.51)</t>
         </is>
       </c>
       <c r="E317" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>maa://30671 (81.82), maa://30669 (98.98), maa://37275 (81.58), *maa://32410 (66.67), maa://41605 (100.0), maa://33671 (100.0)</t>
+          <t>maa://30671 (81.82), maa://30669 (98.99), maa://37275 (81.58), *maa://32410 (66.67), maa://41605 (100.0), maa://33671 (100.0)</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="D322" s="12" t="inlineStr">
         <is>
-          <t>maa://38295 (96.0)</t>
+          <t>maa://38295 (96.05)</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>maa://32416 (87.8)</t>
+          <t>maa://32416 (88.1)</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="D327" s="12" t="inlineStr">
         <is>
-          <t>maa://32647 (97.69), maa://32415 (96.38), maa://34677 (100.0), maa://32892 (100.0)</t>
+          <t>maa://32647 (97.7), maa://32415 (96.4), maa://34677 (100.0), maa://32892 (100.0)</t>
         </is>
       </c>
       <c r="E327" s="3" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>maa://42299 (97.22), *maa://42224 (70.0)</t>
+          <t>maa://42299 (97.3), *maa://42224 (70.0)</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>maa://36646 (98.54), maa://36845 (95.58), **maa://39217 (37.5)</t>
+          <t>maa://36646 (98.55), maa://36845 (95.58), **maa://39217 (37.5)</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>maa://42635 (96.15)</t>
+          <t>maa://42635 (96.3)</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>maa://40957 (88.5), maa://44635 (89.02), maa://41035 (90.38), maa://41128 (82.86), maa://44660 (91.43)</t>
+          <t>maa://40957 (88.55), maa://44635 (89.02), maa://41035 (90.38), maa://41128 (82.86), maa://44660 (91.43)</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>maa://41110 (97.75), maa://45605 (100.0)</t>
+          <t>maa://41110 (97.78), maa://45605 (100.0)</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>maa://42970 (88.52), maa://44745 (95.45), maa://45952 (100.0), ***maa://46851 (25.0), maa://44896 (100.0)</t>
+          <t>maa://42970 (88.1), maa://44745 (95.45), maa://45952 (100.0), ***maa://46851 (25.0), maa://44896 (100.0)</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>maa://47023 (84.62)</t>
+          <t>maa://47023 (85.71)</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.02 13:19:18</t>
+          <t>更新日期：2025.03.03 13:19:02</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>maa://28567 (97.96), **maa://20947 (44.12), maa://30525 (100.0), maa://38735 (100.0), *maa://28188 (66.67), maa://30524 (100.0)</t>
+          <t>maa://28567 (98.0), **maa://20947 (44.12), maa://30525 (100.0), maa://38735 (100.0), *maa://28188 (66.67), maa://30524 (100.0)</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>*maa://20933 (78.57), maa://20822 (100.0)</t>
+          <t>*maa://20933 (78.95), maa://20822 (100.0)</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>maa://28484 (97.12), **maa://23736 (42.42), *maa://31185 (80.0), maa://30306 (100.0)</t>
+          <t>maa://28484 (97.17), **maa://23736 (42.42), *maa://31185 (80.0), maa://30306 (100.0)</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>maa://36641 (98.2), maa://36865 (96.32), maa://42918 (100.0), maa://44119 (97.3), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
+          <t>maa://36641 (98.2), maa://36865 (96.32), maa://42918 (100.0), maa://44119 (97.37), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>maa://44232 (99.02), maa://44305 (100.0), maa://45603 (95.45)</t>
+          <t>maa://44232 (99.03), maa://44305 (100.0), maa://45603 (95.45)</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (87.94), *maa://35854 (77.08), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (13.33)</t>
+          <t>maa://44224 (88.0), *maa://35854 (77.08), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (13.33)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>maa://42223 (99.5), maa://42292 (97.14), maa://42402 (100.0)</t>
+          <t>maa://42223 (99.51), maa://42292 (97.14), maa://42402 (100.0)</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.6), maa://36845 (95.58), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.19)</t>
+          <t>maa://30710 (97.62), maa://36845 (95.58), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.19)</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="D298" s="12" t="inlineStr">
         <is>
-          <t>maa://25775 (93.44), *maa://25393 (71.43)</t>
+          <t>maa://25775 (93.55), *maa://25393 (71.43)</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D317" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (98.51)</t>
+          <t>maa://44234 (98.53)</t>
         </is>
       </c>
       <c r="E317" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>maa://30671 (81.82), maa://30669 (99.0), maa://37275 (81.58), *maa://32410 (66.67), maa://41605 (100.0), maa://33671 (100.0)</t>
+          <t>maa://30671 (81.82), maa://30669 (99.01), maa://37275 (81.58), *maa://32410 (66.67), maa://41605 (100.0), maa://33671 (100.0)</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>maa://40957 (88.55), maa://44635 (89.29), maa://41035 (90.57), maa://41128 (82.86), maa://44660 (91.43)</t>
+          <t>maa://40957 (88.6), maa://44635 (89.41), maa://41035 (90.57), maa://41128 (82.86), maa://44660 (91.43)</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.02 13:19:18</t>
+          <t>更新日期：2025.03.05 13:18:50</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>maa://36644 (87.74), maa://36866 (97.73), maa://27794 (100.0), maa://45572 (100.0)</t>
+          <t>maa://36644 (87.82), maa://36866 (97.73), maa://27794 (100.0), maa://45572 (100.0)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>maa://27970 (98.48), maa://41118 (83.33)</t>
+          <t>maa://27970 (98.51), maa://41118 (85.71)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>maa://38298 (84.81)</t>
+          <t>maa://38298 (85.0)</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>maa://28567 (97.96), **maa://20947 (44.12), maa://30525 (100.0), maa://38735 (100.0), *maa://28188 (66.67), maa://30524 (100.0)</t>
+          <t>maa://28567 (98.0), **maa://20947 (44.12), maa://30525 (100.0), maa://38735 (100.0), *maa://28188 (66.67), maa://30524 (100.0)</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>maa://28784 (94.13), maa://29088 (91.75), maa://20974 (96.0), maa://31124 (96.79), maa://28950 (92.31), *maa://33612 (75.0), maa://29087 (100.0), *maa://20823 (80.0), **maa://42200 (50.0), maa://41832 (85.71)</t>
+          <t>maa://28784 (94.13), maa://29088 (91.28), maa://20974 (96.1), maa://31124 (96.81), maa://28950 (92.31), *maa://33612 (75.0), maa://29087 (100.0), *maa://20823 (80.0), **maa://42200 (50.0), maa://41832 (85.71)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>*maa://28190 (59.38), maa://20880 (92.0)</t>
+          <t>*maa://28190 (59.38), maa://20880 (92.31)</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>*maa://29094 (64.86), maa://28904 (86.67), **maa://20931 (42.31)</t>
+          <t>*maa://29094 (66.67), maa://28904 (86.67), **maa://20931 (42.31)</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>maa://25018 (96.01), maa://25776 (90.91), maa://28361 (96.97), maa://25772 (93.75), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (83.33)</t>
+          <t>maa://25018 (96.01), maa://25776 (91.04), maa://28361 (96.97), maa://25772 (93.75), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (83.33)</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>*maa://20933 (78.57), maa://20822 (100.0)</t>
+          <t>*maa://20933 (78.95), maa://20822 (100.0)</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>maa://28484 (97.12), **maa://23736 (42.42), *maa://31185 (80.0), maa://30306 (100.0)</t>
+          <t>maa://28484 (97.2), **maa://23736 (42.42), *maa://31185 (80.0), maa://30306 (100.0)</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>maa://20971 (83.33)</t>
+          <t>maa://20971 (85.71)</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>maa://36641 (98.2), maa://36865 (96.32), maa://42918 (100.0), maa://44119 (97.3), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
+          <t>maa://36641 (98.2), maa://36865 (96.32), maa://42918 (100.0), maa://44119 (97.37), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>maa://44232 (99.02), maa://44305 (100.0), maa://45603 (95.45)</t>
+          <t>maa://44232 (99.03), maa://44305 (100.0), maa://45603 (95.45)</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="C165" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>maa://20975 (90.91), maa://30806 (100.0)</t>
+          <t>maa://20975 (90.91), maa://30806 (100.0), **maa://47950 (50.0)</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>maa://29633 (93.84), maa://29627 (93.03), maa://29659 (83.87), maa://29861 (100.0)</t>
+          <t>maa://29633 (93.17), maa://29627 (93.03), maa://29659 (83.87), maa://29861 (100.0)</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>maa://20911 (93.33), *maa://29012 (66.67)</t>
+          <t>maa://20911 (93.75), *maa://29012 (66.67)</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (87.94), *maa://35854 (77.08), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (13.33)</t>
+          <t>maa://44224 (88.0), *maa://35854 (77.08), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (13.33)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>maa://42223 (99.5), maa://42292 (97.14), maa://42402 (100.0)</t>
+          <t>maa://42223 (99.51), maa://42292 (97.14), maa://42402 (100.0)</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>maa://20922 (93.1), *maa://32623 (68.75), *maa://34242 (80.0), maa://34900 (84.62)</t>
+          <t>maa://20922 (93.22), *maa://32623 (68.75), *maa://34242 (80.0), maa://34900 (84.62)</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>*maa://30667 (77.49), maa://30666 (83.49), *maa://26836 (78.62), maa://37607 (94.56), *maa://34428 (71.13), **maa://30739 (44.44), *maa://30723 (55.17), maa://39588 (89.58), *maa://37850 (75.0)</t>
+          <t>*maa://30667 (77.49), maa://30666 (83.49), *maa://26836 (78.75), maa://37607 (94.61), *maa://34428 (71.13), **maa://30739 (44.44), *maa://30723 (55.17), maa://39588 (89.58), *maa://37850 (75.0)</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>maa://28923 (91.28), maa://28906 (98.08), ***maa://28825 (12.0)</t>
+          <t>maa://28923 (91.33), maa://28906 (98.08), ***maa://28825 (12.0)</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.6), maa://36845 (95.58), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.19)</t>
+          <t>maa://30710 (97.62), maa://36845 (95.58), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.19)</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="D298" s="12" t="inlineStr">
         <is>
-          <t>maa://25775 (93.44), *maa://25393 (71.43)</t>
+          <t>maa://25775 (93.55), *maa://25393 (71.43)</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D317" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (98.51)</t>
+          <t>maa://44234 (98.53)</t>
         </is>
       </c>
       <c r="E317" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>maa://30671 (81.82), maa://30669 (99.0), maa://37275 (81.58), *maa://32410 (66.67), maa://41605 (100.0), maa://33671 (100.0)</t>
+          <t>maa://30671 (81.82), maa://30669 (99.01), maa://37275 (81.58), *maa://32410 (66.67), maa://41605 (100.0), maa://33671 (100.0)</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>maa://32416 (88.1)</t>
+          <t>maa://32416 (88.37)</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="D332" s="14" t="inlineStr">
         <is>
-          <t>maa://34865 (97.41), maa://34717 (93.85), **maa://45066 (50.0)</t>
+          <t>maa://34865 (97.42), maa://34717 (93.85), **maa://45066 (50.0)</t>
         </is>
       </c>
       <c r="E332" s="14" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>maa://40957 (88.55), maa://44635 (89.29), maa://41035 (90.57), maa://41128 (82.86), maa://44660 (91.43)</t>
+          <t>maa://40957 (88.6), maa://44635 (89.53), maa://41035 (90.74), maa://41128 (82.86), maa://44660 (91.43)</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>maa://41110 (97.8), maa://45605 (100.0)</t>
+          <t>maa://41110 (97.83), maa://45605 (100.0)</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>maa://42970 (88.1), maa://44745 (95.45), maa://45952 (100.0), ***maa://46851 (20.0), maa://44896 (100.0)</t>
+          <t>maa://42970 (88.15), maa://44745 (95.45), maa://45952 (100.0), ***maa://46851 (20.0), maa://44896 (100.0)</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB368"/>
+  <dimension ref="A1:AB369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.08 16:37:02</t>
+          <t>更新日期：2025.03.09 13:14:58</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>*maa://45081 (66.67)</t>
+          <t>*maa://45081 (75.0)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>maa://20976 (97.52), maa://20815 (100.0)</t>
+          <t>maa://20976 (97.54), maa://20815 (100.0)</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>maa://36643 (97.71), maa://36864 (97.59), maa://39140 (100.0)</t>
+          <t>maa://36643 (97.72), maa://36864 (97.59), maa://39140 (100.0)</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>maa://24472 (87.36), *maa://35841 (61.54)</t>
+          <t>maa://24472 (87.43), *maa://35841 (61.54)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>maa://25018 (96.02), maa://25776 (91.04), maa://28361 (97.06), maa://25772 (93.75), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (83.33)</t>
+          <t>maa://25018 (96.04), maa://25776 (91.04), maa://28361 (97.06), maa://25772 (93.75), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (83.33)</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>*maa://28554 (78.26), *maa://45081 (66.67)</t>
+          <t>*maa://28554 (78.26), *maa://45081 (75.0)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>maa://29633 (93.17), maa://29627 (93.03), maa://29659 (83.87), maa://29861 (100.0)</t>
+          <t>maa://29633 (93.19), maa://29627 (93.03), maa://29659 (83.87), maa://29861 (100.0)</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (88.29), *maa://35854 (77.55), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (13.33)</t>
+          <t>maa://44224 (88.35), *maa://35854 (77.55), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (13.33)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>maa://39156 (94.44), *maa://39550 (58.82)</t>
+          <t>maa://39156 (94.52), *maa://39550 (58.82)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -7912,22 +7912,22 @@
       </c>
       <c r="B262" s="16" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C262" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>*maa://20825 (66.67), *maa://21445 (76.92), *maa://35726 (63.64), ***maa://20891 (30.0)</t>
+          <t>maa://48265 (100.0)</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计部署非助战鸿雪的“打字机”10次&gt; 3星通关主题曲2-10；必须编入非助战鸿雪并上场，且使用鸿雪或“打字机”歼灭碎骨</t>
+          <t>&gt; 完成5次战斗；必须编入非助战鸿雪并上场，且每次战斗至少释放1次锐笔速写&gt; 3星通关主题曲9-7标准实战环境，必须编入非助战鸿雪并上场，且使用鸿雪歼灭至少10名敌人，其中包括至少1个深池重甲卫士</t>
         </is>
       </c>
     </row>
@@ -7939,22 +7939,22 @@
       </c>
       <c r="B263" s="16" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C263" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>maa://48265 (100.0)</t>
+          <t>*maa://20825 (66.67), *maa://21445 (76.92), *maa://35726 (63.64), ***maa://20891 (30.0)</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战鸿雪并上场，且每次战斗至少释放1次锐笔速写&gt; 3星通关主题曲9-7标准实战环境，必须编入非助战鸿雪并上场，且使用鸿雪歼灭至少10名敌人，其中包括至少1个深池重甲卫士</t>
+          <t>&gt; 战斗中累计部署非助战鸿雪的“打字机”10次&gt; 3星通关主题曲2-10；必须编入非助战鸿雪并上场，且使用鸿雪或“打字机”歼灭碎骨</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>maa://25769 (96.92)</t>
+          <t>maa://25769 (96.95)</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>maa://48266 (100.0), maa://48267 (100.0)</t>
+          <t>maa://48267 (100.0), maa://48266 (100.0)</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.62), maa://36845 (95.58), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.19)</t>
+          <t>maa://30710 (97.64), maa://36845 (95.58), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.19)</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (98.53)</t>
+          <t>maa://44234 (98.55)</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -10790,6 +10790,33 @@
       <c r="E368" t="inlineStr">
         <is>
           <t>&gt; 使用非助战隐德来希累计造成100000点伤害&gt; 3星通关主题曲10-12标准实战环境；必须编入非助战隐德来希并上场，且隐德来希至少使用3次灵与欲的惜别</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="13" t="inlineStr">
+        <is>
+          <t>钼铅</t>
+        </is>
+      </c>
+      <c r="B369" s="13" t="inlineStr">
+        <is>
+          <t>9-6</t>
+        </is>
+      </c>
+      <c r="C369" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中非助战钼铅累计部署小型炸弹30个&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战钼铅并上场，且使用钼铅至少击败1名深池重甲卫士</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB368"/>
+  <dimension ref="A1:AB369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.08 16:37:02</t>
+          <t>更新日期：2025.03.10 13:15:47</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>*maa://45081 (66.67)</t>
+          <t>*maa://45081 (75.0)</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>maa://36644 (87.82), maa://36866 (97.73), maa://27794 (100.0), maa://45572 (100.0)</t>
+          <t>maa://36644 (87.9), maa://36866 (97.73), maa://27794 (100.0), maa://45572 (100.0)</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>maa://20916 (80.65)</t>
+          <t>maa://20916 (81.25)</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>maa://20847 (96.15)</t>
+          <t>maa://20847 (96.3)</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>maa://44235 (97.12), maa://45604 (100.0)</t>
+          <t>maa://44235 (97.14), maa://45604 (100.0)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>maa://20976 (97.52), maa://20815 (100.0)</t>
+          <t>maa://20976 (97.54), maa://20815 (100.0)</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>maa://36643 (97.71), maa://36864 (97.59), maa://39140 (100.0)</t>
+          <t>maa://36643 (97.72), maa://36864 (97.59), maa://39140 (100.0)</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>maa://20886 (90.0), maa://25136 (95.65)</t>
+          <t>maa://20886 (90.0), maa://25136 (95.83)</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>maa://24472 (87.36), *maa://35841 (61.54)</t>
+          <t>maa://24472 (87.43), *maa://35841 (61.54)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>maa://25018 (96.02), maa://25776 (91.04), maa://28361 (97.06), maa://25772 (93.75), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (83.33)</t>
+          <t>maa://25018 (96.05), maa://25776 (91.18), maa://28361 (97.06), maa://25772 (93.75), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (83.33)</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>*maa://28554 (78.26), *maa://45081 (66.67)</t>
+          <t>*maa://28554 (78.26), *maa://45081 (75.0)</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>maa://36641 (98.2), maa://36865 (96.35), maa://42918 (100.0), maa://44119 (97.37), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
+          <t>maa://36641 (98.2), maa://36865 (96.38), maa://42918 (100.0), maa://44119 (97.37), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>maa://29633 (93.17), maa://29627 (93.03), maa://29659 (83.87), maa://29861 (100.0)</t>
+          <t>maa://29633 (93.19), maa://29627 (93.03), maa://29659 (83.87), maa://29861 (100.0)</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (88.29), *maa://35854 (77.55), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (13.33)</t>
+          <t>maa://44224 (88.46), *maa://35854 (77.55), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (12.5)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>maa://39156 (94.44), *maa://39550 (58.82)</t>
+          <t>maa://39156 (94.52), *maa://39550 (58.82)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>maa://29058 (95.45), maa://39140 (100.0), maa://38723 (100.0)</t>
+          <t>maa://29058 (95.52), maa://39140 (100.0), maa://38723 (100.0)</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>*maa://30667 (77.54), maa://30666 (83.49), *maa://26836 (78.75), maa://37607 (94.65), *maa://34428 (71.13), **maa://30739 (44.44), *maa://30723 (55.17), maa://39588 (89.58), *maa://37850 (75.0)</t>
+          <t>*maa://30667 (77.59), maa://30666 (83.49), *maa://26836 (78.75), maa://37607 (94.67), *maa://34428 (71.13), **maa://30739 (44.44), *maa://30723 (55.17), maa://39588 (89.58), *maa://37850 (75.0)</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>maa://20867 (92.86), maa://38485 (93.33), *maa://32202 (80.0)</t>
+          <t>maa://20867 (93.33), maa://38485 (93.33), *maa://32202 (80.0)</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>maa://20877 (98.46), maa://20836 (100.0), *maa://45067 (66.67), maa://20632 (100.0)</t>
+          <t>maa://20877 (98.48), maa://20836 (100.0), *maa://45067 (66.67), maa://20632 (100.0)</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
@@ -7912,22 +7912,22 @@
       </c>
       <c r="B262" s="16" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C262" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>*maa://20825 (66.67), *maa://21445 (76.92), *maa://35726 (63.64), ***maa://20891 (30.0)</t>
+          <t>maa://48265 (100.0)</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计部署非助战鸿雪的“打字机”10次&gt; 3星通关主题曲2-10；必须编入非助战鸿雪并上场，且使用鸿雪或“打字机”歼灭碎骨</t>
+          <t>&gt; 完成5次战斗；必须编入非助战鸿雪并上场，且每次战斗至少释放1次锐笔速写&gt; 3星通关主题曲9-7标准实战环境，必须编入非助战鸿雪并上场，且使用鸿雪歼灭至少10名敌人，其中包括至少1个深池重甲卫士</t>
         </is>
       </c>
     </row>
@@ -7939,22 +7939,22 @@
       </c>
       <c r="B263" s="16" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C263" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>maa://48265 (100.0)</t>
+          <t>*maa://20825 (66.67), *maa://21445 (76.92), *maa://35726 (63.64), ***maa://20891 (30.0)</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战鸿雪并上场，且每次战斗至少释放1次锐笔速写&gt; 3星通关主题曲9-7标准实战环境，必须编入非助战鸿雪并上场，且使用鸿雪歼灭至少10名敌人，其中包括至少1个深池重甲卫士</t>
+          <t>&gt; 战斗中累计部署非助战鸿雪的“打字机”10次&gt; 3星通关主题曲2-10；必须编入非助战鸿雪并上场，且使用鸿雪或“打字机”歼灭碎骨</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>maa://25769 (96.92)</t>
+          <t>maa://25769 (96.95)</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>maa://48266 (100.0), maa://48267 (100.0)</t>
+          <t>maa://48267 (100.0), maa://48266 (100.0)</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.62), maa://36845 (95.58), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.19)</t>
+          <t>maa://30710 (97.64), maa://36845 (95.61), maa://31558 (97.06), **maa://39217 (37.5), maa://30668 (85.71)</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (98.53)</t>
+          <t>maa://44234 (98.55)</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="C331" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D331" s="14" t="inlineStr">
         <is>
-          <t>maa://32647 (97.55), maa://32415 (96.43), maa://34677 (100.0), maa://32892 (100.0)</t>
+          <t>maa://32647 (97.55), maa://32415 (96.43), maa://34677 (100.0), maa://32892 (100.0), maa://47851 (100.0)</t>
         </is>
       </c>
       <c r="E331" s="14" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>maa://36646 (98.55), maa://36845 (95.58), **maa://39217 (37.5)</t>
+          <t>maa://36646 (98.56), maa://36845 (95.61), **maa://39217 (37.5)</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>maa://36645 (98.02), maa://36841 (93.33), maa://37484 (93.75), maa://37858 (92.0)</t>
+          <t>maa://36645 (98.03), maa://36841 (93.33), maa://37484 (93.75), maa://37858 (92.0)</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>maa://42970 (88.15), maa://44745 (95.45), maa://45952 (100.0), ***maa://46851 (20.0), maa://44896 (100.0)</t>
+          <t>maa://42970 (88.15), maa://44745 (95.65), maa://45952 (100.0), ***maa://46851 (20.0), maa://44896 (100.0)</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -10790,6 +10790,33 @@
       <c r="E368" t="inlineStr">
         <is>
           <t>&gt; 使用非助战隐德来希累计造成100000点伤害&gt; 3星通关主题曲10-12标准实战环境；必须编入非助战隐德来希并上场，且隐德来希至少使用3次灵与欲的惜别</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="13" t="inlineStr">
+        <is>
+          <t>钼铅</t>
+        </is>
+      </c>
+      <c r="B369" s="13" t="inlineStr">
+        <is>
+          <t>9-6</t>
+        </is>
+      </c>
+      <c r="C369" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中非助战钼铅累计部署小型炸弹30个&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战钼铅并上场，且使用钼铅至少击败1名深池重甲卫士</t>
         </is>
       </c>
     </row>

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.20 13:18:45</t>
+          <t>更新日期：2025.03.21 13:18:27</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>maa://20953 (95.0), maa://31173 (95.65)</t>
+          <t>maa://20953 (95.0), maa://31173 (95.83)</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>maa://44235 (97.3), maa://45604 (100.0)</t>
+          <t>maa://44235 (97.35), maa://45604 (100.0)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>maa://24472 (87.57), *maa://35841 (57.14)</t>
+          <t>maa://24472 (87.63), *maa://35841 (57.14)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>maa://29037 (98.0)</t>
+          <t>maa://29037 (98.04)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>maa://20869 (100.0), maa://44690 (90.0)</t>
+          <t>maa://20869 (100.0), maa://44690 (90.91)</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>maa://44232 (99.06), maa://44305 (100.0), maa://45603 (91.3)</t>
+          <t>maa://44232 (99.07), maa://44305 (100.0), maa://45603 (91.3)</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>maa://29633 (93.29), maa://29627 (93.1), maa://29659 (83.87), maa://29861 (100.0)</t>
+          <t>maa://29633 (93.31), maa://29627 (93.14), maa://29659 (83.87), maa://29861 (100.0)</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>maa://34866 (90.0), maa://34714 (96.15)</t>
+          <t>maa://34866 (90.0), maa://34714 (96.3)</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (88.43), *maa://35854 (77.55), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (11.11)</t>
+          <t>maa://44224 (88.64), *maa://35854 (78.0), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (11.11)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>maa://39159 (95.0)</t>
+          <t>maa://39159 (95.24)</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>*maa://30667 (77.7), maa://30666 (83.64), *maa://26836 (78.75), maa://37607 (94.72), *maa://34428 (71.13), **maa://30739 (44.44), *maa://30723 (55.17), maa://39588 (89.58), *maa://37850 (75.0)</t>
+          <t>*maa://30667 (77.7), maa://30666 (83.64), *maa://26836 (78.75), maa://37607 (94.74), *maa://34428 (71.13), **maa://30739 (44.44), *maa://30723 (55.17), maa://39588 (89.58), *maa://37850 (75.0)</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>maa://20879 (84.91), maa://20834 (92.86)</t>
+          <t>maa://20879 (83.64), maa://20834 (92.86)</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>maa://20899 (89.38), ***maa://44744 (25.0), maa://46332 (100.0)</t>
+          <t>maa://20899 (89.38), maa://46332 (100.0), ***maa://44744 (25.0)</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.66), maa://36845 (95.61), maa://31558 (97.06), **maa://39217 (41.18), maa://30668 (86.21)</t>
+          <t>maa://30710 (97.66), maa://36845 (95.65), maa://31558 (97.06), **maa://39217 (41.18), maa://30668 (86.21)</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>maa://35859 (97.44)</t>
+          <t>maa://35859 (97.47)</t>
         </is>
       </c>
       <c r="E299" s="3" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D313" s="12" t="inlineStr">
         <is>
-          <t>maa://34867 (97.44), maa://34715 (100.0)</t>
+          <t>maa://34867 (97.5), maa://34715 (100.0)</t>
         </is>
       </c>
       <c r="E313" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (98.55)</t>
+          <t>maa://44234 (98.57)</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>maa://30671 (81.82), maa://30669 (99.02), maa://37275 (81.58), *maa://32410 (66.67), maa://41605 (100.0), maa://33671 (100.0)</t>
+          <t>maa://30671 (81.93), maa://30669 (99.02), maa://37275 (81.58), *maa://32410 (66.67), maa://41605 (100.0), maa://33671 (100.0)</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="D336" s="14" t="inlineStr">
         <is>
-          <t>maa://34865 (97.42), maa://34717 (93.85), **maa://45066 (50.0)</t>
+          <t>maa://34865 (97.42), maa://34717 (93.94), **maa://45066 (50.0)</t>
         </is>
       </c>
       <c r="E336" s="14" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>maa://36868 (100.0), maa://35996 (96.61), **maa://39217 (41.18)</t>
+          <t>maa://36868 (100.0), maa://35996 (96.67), **maa://39217 (41.18)</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>maa://36646 (98.57), maa://36845 (95.61), **maa://39217 (41.18)</t>
+          <t>maa://36646 (98.59), maa://36845 (95.65), **maa://39217 (41.18)</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>maa://40957 (88.21), maa://44635 (89.77), maa://41035 (90.74), maa://41128 (82.86), maa://44660 (91.43), maa://48026 (100.0)</t>
+          <t>maa://40957 (88.36), maa://44635 (89.89), maa://41035 (90.91), maa://41128 (82.86), maa://44660 (91.43), maa://48026 (100.0)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>maa://41110 (97.89), maa://45605 (100.0)</t>
+          <t>maa://41110 (97.92), maa://45605 (100.0)</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>maa://43875 (97.44)</t>
+          <t>maa://43875 (97.5)</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>maa://42970 (88.32), maa://44745 (96.0), maa://45952 (100.0), ***maa://46851 (20.0), maa://44896 (100.0)</t>
+          <t>maa://42970 (88.37), maa://44745 (96.0), maa://45952 (100.0), ***maa://46851 (20.0), maa://44896 (100.0)</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.03.28 13:20:26</t>
+          <t>更新日期：2025.03.29 13:18:03</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>*maa://20849 (64.1), *maa://28758 (60.61), maa://29036 (95.24), *maa://42172 (80.0), maa://30285 (100.0)</t>
+          <t>*maa://20849 (62.5), *maa://28758 (60.61), maa://29036 (95.24), *maa://42172 (80.0), maa://30285 (100.0)</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>maa://20863 (87.75), maa://20832 (98.94), maa://20727 (100.0)</t>
+          <t>maa://20863 (87.8), maa://20832 (98.94), maa://20727 (100.0)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>*maa://20892 (79.52)</t>
+          <t>*maa://20892 (79.76)</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>maa://28900 (96.15), maa://30126 (100.0)</t>
+          <t>maa://28900 (96.2), maa://30126 (100.0)</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>maa://28784 (94.17), maa://29088 (91.41), maa://20974 (96.1), maa://31124 (96.88), maa://28950 (92.31), *maa://33612 (75.0), maa://29087 (100.0), *maa://20823 (80.0), **maa://42200 (50.0), maa://41832 (85.71)</t>
+          <t>maa://28784 (94.19), maa://29088 (91.41), maa://20974 (96.1), maa://31124 (96.88), maa://28950 (92.31), *maa://33612 (75.0), maa://29087 (100.0), *maa://20823 (80.0), **maa://42200 (50.0), maa://41832 (85.71)</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>maa://36643 (97.78), maa://36864 (97.62), maa://39140 (100.0)</t>
+          <t>maa://36643 (97.79), maa://36864 (97.62), maa://39140 (100.0)</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>maa://25018 (96.11), maa://25776 (91.18), maa://28361 (97.06), maa://25772 (93.88), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (83.33)</t>
+          <t>maa://25018 (96.11), maa://25776 (91.18), maa://28361 (97.14), maa://25772 (93.88), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (83.33)</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>maa://29037 (98.11)</t>
+          <t>maa://29037 (98.15)</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>maa://20908 (98.28), maa://35723 (95.35), *maa://23346 (77.78), maa://38822 (100.0)</t>
+          <t>maa://20908 (98.29), maa://35723 (95.35), *maa://23346 (77.78), maa://38822 (100.0)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>maa://37484 (93.75), maa://24611 (89.66)</t>
+          <t>maa://37484 (93.88), maa://24611 (89.66)</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>maa://20981 (92.31)</t>
+          <t>maa://20981 (92.86)</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>maa://28484 (96.55), **maa://23736 (42.42), *maa://31185 (80.0), maa://30306 (100.0)</t>
+          <t>maa://28484 (96.58), **maa://23736 (42.42), *maa://31185 (80.0), maa://30306 (100.0)</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>maa://29633 (92.98), maa://29627 (93.2), maa://29659 (84.38), maa://29861 (100.0), maa://49074 (100.0)</t>
+          <t>maa://29633 (92.98), maa://29627 (93.24), maa://29659 (84.38), maa://29861 (100.0), maa://49074 (100.0)</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (88.61), *maa://35854 (78.43), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (11.11)</t>
+          <t>maa://44224 (88.7), *maa://35854 (78.85), maa://25760 (85.57), **maa://20872 (50.0), ***maa://43911 (11.11)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="C236" s="13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>*maa://30667 (77.57), maa://30666 (83.64), *maa://26836 (78.88), maa://37607 (94.86), *maa://34428 (71.13), **maa://30739 (43.24), *maa://30723 (55.17), maa://39588 (89.58), *maa://37850 (75.0), ***maa://48101 (25.0)</t>
+          <t>*maa://30667 (77.57), maa://30666 (83.72), *maa://26836 (78.88), maa://37607 (94.89), *maa://34428 (71.13), **maa://30739 (43.24), *maa://30723 (55.17), maa://39588 (89.58), *maa://37850 (75.0), ***maa://48101 (25.0), maa://49172 (100.0)</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>maa://28923 (91.48), maa://28906 (98.11), ***maa://28825 (12.0)</t>
+          <t>maa://28923 (91.48), maa://28906 (98.15), ***maa://28825 (12.0)</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>maa://20879 (83.33), maa://20834 (92.86)</t>
+          <t>maa://20879 (83.61), maa://20834 (92.86)</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>*maa://20825 (68.0), *maa://21445 (76.92), *maa://35726 (63.64), ***maa://20891 (30.0)</t>
+          <t>*maa://20825 (68.0), *maa://21445 (66.67), *maa://35726 (63.64), ***maa://20891 (30.0)</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>maa://35859 (97.53)</t>
+          <t>maa://35859 (97.56)</t>
         </is>
       </c>
       <c r="E299" s="3" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D313" s="12" t="inlineStr">
         <is>
-          <t>maa://34867 (97.56), maa://34715 (100.0)</t>
+          <t>maa://34867 (97.62), maa://34715 (100.0)</t>
         </is>
       </c>
       <c r="E313" s="3" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="D329" s="12" t="inlineStr">
         <is>
-          <t>maa://32416 (88.89)</t>
+          <t>maa://32416 (89.36)</t>
         </is>
       </c>
       <c r="E329" s="3" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="D331" s="14" t="inlineStr">
         <is>
-          <t>maa://32647 (97.59), maa://32415 (96.5), maa://34677 (100.0), maa://32892 (100.0), **maa://47851 (50.0)</t>
+          <t>maa://32647 (97.6), maa://32415 (96.5), maa://34677 (100.0), maa://32892 (100.0), **maa://47851 (50.0)</t>
         </is>
       </c>
       <c r="E331" s="14" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="D336" s="14" t="inlineStr">
         <is>
-          <t>maa://34865 (97.47), maa://34717 (93.94), *maa://45066 (60.0)</t>
+          <t>maa://34865 (97.5), maa://34717 (93.94), *maa://45066 (60.0)</t>
         </is>
       </c>
       <c r="E336" s="14" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>maa://36646 (98.64), maa://36845 (95.65), **maa://39217 (41.18)</t>
+          <t>maa://36646 (98.65), maa://36845 (95.65), **maa://39217 (41.18)</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>maa://36645 (98.05), maa://36841 (93.33), maa://37484 (93.75), maa://37858 (92.0)</t>
+          <t>maa://36645 (98.05), maa://36841 (93.33), maa://37484 (93.88), maa://37858 (92.0)</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>maa://40957 (88.76), maa://44635 (88.3), maa://41035 (91.23), maa://41128 (83.33), maa://44660 (91.67), maa://48026 (96.3)</t>
+          <t>maa://40957 (88.93), maa://44635 (88.42), maa://41035 (91.23), maa://41128 (83.33), maa://44660 (91.67), maa://48026 (96.43)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.04.17 13:19:49</t>
+          <t>更新日期：2025.04.19 13:19:27</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>maa://20863 (88.37), maa://20832 (99.0), maa://20727 (100.0)</t>
+          <t>maa://20863 (88.48), maa://20832 (99.0), maa://20727 (100.0)</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>maa://30500 (98.68), *maa://27290 (70.59), ***maa://42154 (8.33)</t>
+          <t>maa://30500 (98.7), *maa://27290 (70.59), ***maa://42154 (8.33)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>maa://20932 (96.15), maa://42415 (100.0), maa://40838 (100.0)</t>
+          <t>maa://20932 (96.18), maa://42415 (100.0), maa://40838 (100.0)</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>maa://44235 (97.76), maa://45604 (100.0), maa://20961 (100.0), maa://20910 (100.0)</t>
+          <t>maa://44235 (97.79), maa://45604 (100.0), maa://20961 (100.0), maa://20910 (100.0)</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>maa://27970 (98.53), maa://41118 (85.71)</t>
+          <t>maa://27970 (98.55), maa://41118 (85.71)</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>maa://20841 (100.0), maa://24093 (100.0), maa://31559 (96.43), maa://20924 (95.24), maa://25777 (100.0), maa://20631 (100.0), maa://28241 (100.0)</t>
+          <t>maa://20841 (100.0), maa://24093 (100.0), maa://31559 (96.55), maa://20924 (95.24), maa://25777 (100.0), maa://20631 (100.0), maa://28241 (100.0)</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>maa://28187 (97.3), maa://33504 (100.0), maa://45144 (100.0), maa://43531 (100.0)</t>
+          <t>maa://28187 (97.37), maa://33504 (100.0), maa://45144 (100.0), maa://43531 (100.0)</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>maa://28567 (98.15), **maa://20947 (44.12), maa://30525 (100.0), maa://38735 (100.0), *maa://28188 (66.67), maa://30524 (100.0)</t>
+          <t>maa://28567 (98.18), **maa://20947 (44.12), maa://30525 (100.0), maa://38735 (100.0), *maa://28188 (66.67), maa://30524 (100.0)</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>maa://36643 (97.88), maa://36864 (97.65), maa://39140 (100.0)</t>
+          <t>maa://36643 (97.89), maa://36864 (97.65), maa://39140 (100.0)</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>maa://20886 (92.59)</t>
+          <t>maa://20886 (92.86)</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>maa://24472 (87.76), *maa://35841 (60.0)</t>
+          <t>maa://24472 (87.82), *maa://35841 (60.0)</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>maa://25018 (96.19), maa://25776 (91.67), maa://28361 (97.14), maa://25772 (93.88), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (84.62)</t>
+          <t>maa://25018 (96.19), maa://25776 (91.67), maa://28361 (97.14), maa://25772 (93.88), maa://25161 (81.25), maa://32653 (85.71), maa://45194 (85.71)</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>maa://20933 (80.65), maa://20822 (100.0)</t>
+          <t>maa://20933 (80.95), maa://20822 (100.0)</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>maa://20908 (98.13), maa://35723 (95.56), *maa://23346 (77.78), maa://38822 (100.0)</t>
+          <t>maa://20908 (97.89), maa://35723 (95.56), *maa://23346 (77.78), maa://38822 (100.0)</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>maa://21422 (98.88)</t>
+          <t>maa://21422 (98.89)</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>maa://29025 (80.77), **maa://21000 (41.38)</t>
+          <t>maa://29025 (81.48), **maa://21000 (41.38)</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>maa://36641 (98.27), maa://40957 (90.1), maa://36865 (96.53), maa://44635 (87.63), maa://41128 (83.33), maa://44660 (91.67), maa://42918 (100.0), maa://44119 (97.37), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
+          <t>maa://36641 (98.27), maa://40957 (90.24), maa://36865 (96.58), maa://44635 (87.63), maa://41128 (83.33), maa://44660 (91.67), maa://42918 (100.0), maa://44119 (97.37), maa://37300 (100.0), maa://46108 (100.0), maa://42917 (100.0)</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>maa://44232 (99.16), maa://45603 (91.3), maa://44305 (100.0)</t>
+          <t>maa://44232 (99.17), maa://45603 (91.3), maa://44305 (100.0)</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>maa://29633 (93.03), maa://29627 (92.82), maa://29659 (84.85), **maa://30679 (50.0), maa://29861 (100.0), maa://42343 (100.0), maa://49074 (100.0)</t>
+          <t>maa://29633 (93.03), maa://29627 (92.82), maa://29659 (84.85), **maa://30679 (50.0), maa://29861 (100.0), maa://49074 (100.0), maa://42343 (100.0)</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>maa://34866 (92.11), maa://34714 (96.3)</t>
+          <t>maa://34866 (92.31), maa://34714 (96.3)</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (89.18), *maa://35854 (77.36), maa://25760 (86.14), **maa://20872 (50.0), ***maa://43911 (10.53), maa://50388 (100.0)</t>
+          <t>maa://44224 (89.38), *maa://35854 (77.36), maa://25760 (86.14), **maa://20872 (50.0), ***maa://43911 (10.53), maa://50388 (100.0)</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>maa://39156 (94.94), *maa://39550 (58.82)</t>
+          <t>maa://39156 (95.0), *maa://39550 (58.82)</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>maa://27823 (84.93), *maa://28190 (60.61), maa://22894 (90.91), *maa://20906 (72.22), **maa://20907 (35.48)</t>
+          <t>maa://27823 (83.78), *maa://28190 (60.61), maa://22894 (90.91), *maa://20906 (72.22), **maa://20907 (35.48)</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>maa://27823 (84.93), *maa://28190 (60.61), maa://22894 (90.91), *maa://20906 (72.22), **maa://20907 (35.48)</t>
+          <t>maa://27823 (83.78), *maa://28190 (60.61), maa://22894 (90.91), *maa://20906 (72.22), **maa://20907 (35.48)</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>maa://28187 (97.3), maa://43531 (100.0), maa://39520 (100.0)</t>
+          <t>maa://28187 (97.37), maa://43531 (100.0), maa://39520 (100.0)</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>maa://20917 (98.04)</t>
+          <t>maa://20917 (98.08)</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="D237" s="14" t="inlineStr">
         <is>
-          <t>*maa://30667 (77.98), maa://30666 (83.64), **maa://30739 (43.24), *maa://30723 (55.0), maa://39588 (89.58)</t>
+          <t>*maa://30667 (78.03), maa://30666 (83.64), **maa://30739 (43.24), *maa://30723 (55.0), maa://39588 (89.58)</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>maa://42287 (89.55), maa://45570 (96.3), maa://42225 (100.0)</t>
+          <t>maa://42287 (89.71), maa://45570 (96.3), maa://42225 (100.0)</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>maa://24093 (100.0), maa://31559 (96.43), maa://20924 (95.24), maa://49440 (100.0)</t>
+          <t>maa://24093 (100.0), maa://31559 (96.55), maa://20924 (95.24), maa://49440 (100.0)</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>maa://20877 (98.51), maa://45067 (83.33), maa://20836 (100.0), maa://20632 (100.0)</t>
+          <t>maa://20877 (98.53), maa://45067 (83.33), maa://20836 (100.0), maa://20632 (100.0)</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>maa://49643 (90.91)</t>
+          <t>maa://49643 (92.31)</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="D284" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.71), maa://36845 (94.96), maa://31558 (97.06), **maa://39217 (41.18), maa://30668 (86.21)</t>
+          <t>maa://30710 (97.71), maa://36845 (95.0), maa://31558 (97.06), **maa://39217 (41.18), maa://30668 (86.21)</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>maa://25774 (96.97), maa://28133 (92.0), maa://22469 (92.16), **maa://39217 (41.18), **maa://31349 (50.0)</t>
+          <t>maa://25774 (96.97), maa://28133 (92.0), maa://22469 (92.31), **maa://39217 (41.18), **maa://31349 (50.0)</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="D298" s="12" t="inlineStr">
         <is>
-          <t>maa://49642 (98.39), maa://49660 (84.62), maa://50280 (100.0)</t>
+          <t>maa://49642 (98.48), maa://49660 (84.62), maa://50280 (91.67)</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="D303" s="12" t="inlineStr">
         <is>
-          <t>maa://35859 (97.62)</t>
+          <t>maa://35859 (97.65)</t>
         </is>
       </c>
       <c r="E303" s="3" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D306" s="12" t="inlineStr">
         <is>
-          <t>maa://25775 (94.12), *maa://25393 (71.43)</t>
+          <t>maa://25775 (94.2), *maa://25393 (71.43)</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
@@ -9515,7 +9515,7 @@
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>maa://40956 (94.29)</t>
+          <t>maa://40956 (94.44)</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (98.73)</t>
+          <t>maa://44234 (98.78)</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -9650,7 +9650,7 @@
       </c>
       <c r="D326" s="12" t="inlineStr">
         <is>
-          <t>maa://42968 (99.05), maa://49245 (100.0)</t>
+          <t>maa://42968 (99.06), maa://49245 (100.0)</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="D333" s="14" t="inlineStr">
         <is>
-          <t>maa://32416 (90.0)</t>
+          <t>maa://32416 (90.2)</t>
         </is>
       </c>
       <c r="E333" s="14" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D335" s="14" t="inlineStr">
         <is>
-          <t>maa://32647 (97.64), maa://32415 (96.5), maa://34677 (100.0), maa://32892 (100.0), maa://32653 (85.71)</t>
+          <t>maa://32647 (97.64), maa://32415 (96.6), maa://34677 (100.0), maa://32892 (100.0), maa://32653 (85.71)</t>
         </is>
       </c>
       <c r="E335" s="14" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>maa://34865 (97.58), maa://34717 (93.94), *maa://45066 (60.0)</t>
+          <t>maa://34865 (97.6), maa://34717 (93.94), *maa://45066 (60.0)</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>maa://49648 (94.12), **maa://49662 (50.0)</t>
+          <t>maa://49648 (94.74), **maa://49662 (50.0)</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>maa://36646 (98.7), maa://36845 (94.96), **maa://39217 (41.18)</t>
+          <t>maa://36646 (98.72), maa://36845 (95.0), **maa://39217 (41.18)</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>maa://36645 (98.08), maa://36841 (93.33), maa://37484 (93.88), maa://37858 (92.0), maa://40489 (100.0)</t>
+          <t>maa://36645 (98.09), maa://36841 (93.33), maa://37484 (93.88), maa://37858 (92.0), maa://40489 (100.0)</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>maa://40957 (90.1), maa://44635 (87.63), maa://41035 (91.53), maa://41128 (83.33), maa://44660 (91.67), maa://48026 (97.44)</t>
+          <t>maa://40957 (90.24), maa://44635 (87.63), maa://41035 (91.53), maa://41128 (83.33), maa://44660 (91.67), maa://48026 (97.62)</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="C359" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>maa://42333 (100.0), maa://41977 (100.0)</t>
+          <t>maa://42333 (100.0), maa://41977 (100.0), maa://50518 (100.0)</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>maa://44233 (92.68), maa://45570 (96.3)</t>
+          <t>maa://44233 (93.02), maa://45570 (96.3)</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>maa://42970 (89.13), maa://44745 (96.77), maa://45952 (100.0), ***maa://46851 (16.67), maa://49516 (83.33), maa://44896 (100.0)</t>
+          <t>maa://42970 (89.13), maa://44745 (96.77), maa://45952 (100.0), ***maa://46851 (14.29), maa://49516 (85.71), maa://44896 (100.0)</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.05.24 13:19:10</t>
+          <t>更新日期：2025.05.31 13:19:45</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>maa://20990 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>*maa://20996 (60.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>maa://41855 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>*maa://20925 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>maa://20850 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>maa://20980 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>maa://20941 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>*maa://20888 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>maa://20866 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>maa://20857 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>maa://37695 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>maa://39023 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>maa://44401 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>maa://20919 (100.0), *maa://31611 (70.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>*maa://20848 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>maa://20930 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>maa://20897 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>maa://20865 (90.91), maa://20826 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>maa://20900 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>maa://20948 (88.89), maa://30844 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>maa://20876 (96.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>maa://45260 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>maa://20864 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>maa://44220 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>*maa://20849 (70.0), *maa://28758 (66.67), maa://29036 (95.65), *maa://42172 (61.54), maa://30285 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>maa://20920 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>maa://20863 (88.84), maa://20832 (99.05), maa://20727 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>*maa://20871 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>**maa://39024 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1707,12 +1707,12 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>maa://36644 (88.59), maa://36866 (96.15), maa://45572 (90.0), maa://27794 (100.0), maa://20843 (100.0), maa://20960 (100.0), **maa://24483 (50.0), maa://20862 (83.33), *maa://20893 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>maa://30500 (98.84), *maa://27290 (70.59), ***maa://42154 (8.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>maa://20916 (81.82), *maa://52658 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>maa://20847 (96.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>maa://20997 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>maa://27376 (91.3), maa://42635 (97.44), **maa://20838 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>maa://20962 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>*maa://29012 (80.0), maa://20928 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>maa://20882 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>maa://20892 (80.9)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>maa://20918 (95.24), maa://34883 (92.86), maa://20824 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>maa://20889 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>maa://34718 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>maa://20910 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>maa://39025 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>maa://20938 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>maa://20954 (92.31)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>*maa://32845 (73.33), *maa://20982 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>maa://30503 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>maa://21001 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>maa://42295 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>maa://20953 (95.65), maa://31173 (96.15)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>maa://30502 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>maa://20932 (96.3), maa://42415 (100.0), maa://40838 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>maa://44235 (98.15), maa://45604 (100.0), maa://20961 (100.0), maa://44220 (100.0), maa://20910 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>*maa://20965 (72.73)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>maa://28900 (96.39), maa://30126 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>maa://27970 (98.61), maa://41118 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>maa://38298 (88.24)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>maa://20841 (100.0), maa://24093 (100.0), maa://31559 (97.06), maa://20924 (95.24), maa://25777 (100.0), maa://20631 (100.0), maa://28241 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>maa://20844 (96.88)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>*maa://20845 (68.0), maa://38727 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>maa://28187 (97.44), maa://33504 (100.0), maa://45144 (100.0), maa://43531 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>maa://28567 (96.72), **maa://20947 (44.12), maa://30525 (100.0), maa://38735 (100.0), *maa://28188 (70.0), maa://30524 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>maa://20993 (100.0), maa://20914 (100.0), maa://45606 (100.0), maa://20829 (100.0), maa://40159 (100.0), maa://20900 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>maa://39693 (100.0), maa://49348 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>maa://20976 (97.78), maa://20815 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>maa://20974 (96.3), maa://29079 (80.95), maa://29096 (95.65), maa://29087 (100.0), *maa://20823 (80.0), maa://20855 (93.33), maa://20904 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>maa://20944 (95.65), maa://35393 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>maa://20943 (99.35), maa://30673 (100.0), maa://30672 (100.0), maa://20856 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>maa://36643 (98.16), maa://36864 (97.94), maa://39140 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>maa://39139 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>maa://39142 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>maa://20989 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>maa://20873 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>maa://20958 (94.44)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>maa://20957 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>maa://20875 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>maa://20952 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>maa://30525 (100.0), maa://20859 (100.0), *maa://28188 (70.0), maa://30524 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>maa://28072 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="C83" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>maa://45572 (90.0), maa://27794 (100.0), maa://20960 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>maa://20972 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>maa://20874 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>maa://20885 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>maa://20886 (93.55)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>maa://24472 (88.18), *maa://35841 (62.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>maa://44402 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>*maa://28190 (61.76), maa://20880 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="C91" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>maa://24609 (92.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>maa://20890 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="C93" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>maa://20984 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="C94" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>maa://40157 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="C95" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>maa://20927 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>*maa://20926 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -3462,12 +3462,12 @@
       </c>
       <c r="C97" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>maa://20991 (100.0), maa://51015 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="C98" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>maa://20967 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="C99" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>maa://20929 (94.12)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>maa://20852 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>maa://45572 (90.0), maa://27794 (100.0), *maa://20893 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>maa://40517 (95.83), *maa://39240 (60.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="C103" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>*maa://29094 (69.77), maa://28904 (88.24), **maa://20931 (46.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>*maa://20966 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="C105" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>maa://39143 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>maa://45572 (90.0), maa://27794 (100.0), maa://20843 (100.0), **maa://24483 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="C107" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>maa://20894 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>maa://25018 (96.49), maa://51881 (99.23), maa://25776 (92.11), maa://28361 (97.3), maa://25772 (94.12), maa://32653 (85.71), maa://25161 (81.25), maa://45194 (87.5), maa://56588 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C109" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>maa://45259 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>maa://20887 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>*maa://28554 (79.17)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>maa://20933 (83.56), maa://20822 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="C113" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>maa://29037 (98.41)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>maa://20904 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="C115" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>maa://20908 (98.01), maa://35723 (95.92), *maa://23346 (77.78), maa://38822 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>maa://29659 (85.29), maa://29031 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>maa://31560 (87.5), maa://20940 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>maa://20986 (93.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>maa://31560 (87.5), maa://20851 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>maa://20949 (92.31)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>maa://20869 (100.0), maa://44690 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="C122" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>maa://29650 (98.21), maa://45570 (97.62)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>maa://20868 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="C124" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>*maa://20909 (70.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="C125" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>maa://44403 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C126" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>maa://30501 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="C127" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>maa://20914 (100.0), maa://31937 (100.0), maa://20829 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>maa://37484 (94.12), maa://24611 (90.32)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C129" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>maa://24491 (100.0), maa://24493 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>maa://21422 (99.02)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>maa://30719 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>maa://20837 (100.0), maa://37666 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>maa://29023 (100.0), maa://39515 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>maa://39146 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="C135" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>maa://20856 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>maa://20913 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="C137" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>maa://41856 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>maa://29025 (82.14), **maa://21000 (41.38)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="C139" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>**maa://30679 (50.0), maa://45258 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>maa://20981 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="C141" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>maa://37689 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>maa://28484 (97.04), **maa://23736 (43.28), maa://31185 (83.33), maa://30306 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="C143" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>maa://30670 (96.53), maa://31470 (96.55), *maa://45066 (66.67), **maa://30867 (40.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>maa://20971 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>maa://39147 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>maa://20898 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="C147" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>maa://29056 (100.0), ***maa://20901 (8.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>maa://28828 (88.24), maa://20846 (95.83), **maa://47286 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="C149" s="13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>maa://36641 (98.42), maa://40957 (93.17), maa://36865 (96.23), maa://44635 (87.62), maa://44660 (92.31), maa://41128 (83.78), maa://42918 (100.0), maa://44119 (97.44), maa://46108 (100.0), maa://37300 (100.0), maa://42917 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>maa://51549 (96.55), maa://51923 (94.12)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="C151" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>maa://20961 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="C152" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>maa://20963 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="C153" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>maa://39148 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="C154" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>maa://20946 (100.0), maa://20833 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="C155" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>maa://20945 (88.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="C156" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>maa://37694 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="C157" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>**maa://39149 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>maa://20959 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="C159" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>maa://44232 (98.68), maa://45603 (90.0), maa://44305 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>maa://20936 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="C161" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>maa://20855 (93.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>maa://40158 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="C163" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>*maa://32845 (73.33), maa://29054 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>maa://20973 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="C165" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>maa://39150 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="C166" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>maa://20975 (90.91), maa://30806 (100.0), *maa://47950 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="C167" s="13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>maa://29633 (92.49), maa://29627 (92.63), maa://29659 (85.29), maa://49074 (97.22), **maa://30679 (50.0), maa://29861 (100.0), maa://42343 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>maa://49655 (95.45), maa://49867 (93.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C169" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>maa://29059 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>maa://45556 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="C171" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>maa://40159 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="C172" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>maa://39152 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="C173" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>*maa://20905 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="C174" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>maa://32418 (99.68), maa://51440 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="C175" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>maa://37690 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="C176" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>maa://20842 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="C177" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>maa://20912 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="C178" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>maa://20911 (95.45), *maa://29012 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="C179" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>maa://20964 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="C180" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>maa://20983 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
@@ -5730,12 +5730,12 @@
       </c>
       <c r="C181" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>maa://31560 (87.5), *maa://20968 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="C182" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>maa://28104 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="C183" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>maa://20861 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="C184" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>maa://20970 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="C185" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>maa://20969 (86.21), maa://41303 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="C186" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>maa://20999 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="C187" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>maa://35198 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="C188" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>maa://39153 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="C189" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>maa://34866 (92.86), maa://34714 (96.3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="C190" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>maa://34883 (92.86), maa://20895 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="C191" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>maa://20853 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="C192" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>maa://20942 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="C193" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>maa://20992 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
@@ -6081,12 +6081,12 @@
       </c>
       <c r="C194" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>*maa://28190 (61.76), maa://20994 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="C195" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>maa://20860 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="C196" s="13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (90.97), maa://35854 (85.37), maa://25760 (87.16), maa://50388 (97.67), **maa://20872 (50.0), ***maa://43911 (14.29), maa://51066 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="C197" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>maa://39156 (93.98), *maa://39550 (57.89), *maa://53417 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C198" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>maa://27823 (84.42), *maa://28190 (61.76), maa://22894 (90.91), *maa://20906 (72.22), **maa://20907 (35.48)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="C199" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>maa://27823 (84.42), *maa://28190 (61.76), maa://22894 (90.91), *maa://20906 (72.22), **maa://20907 (35.48)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="C200" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>maa://42223 (99.58), maa://49077 (91.67), maa://42292 (97.22), maa://42402 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="C201" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>maa://39154 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="C202" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>maa://20854 (92.31)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="C203" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>maa://20937 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="C204" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>maa://22468 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="C205" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>maa://30673 (100.0), maa://30672 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
@@ -6405,12 +6405,12 @@
       </c>
       <c r="C206" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>maa://20934 (100.0), maa://20827 (100.0), maa://20828 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
@@ -6432,12 +6432,12 @@
       </c>
       <c r="C207" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>maa://20935 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="C208" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>maa://53354 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="C209" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>maa://28133 (92.45), **maa://39217 (41.18), maa://25369 (94.12)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="C210" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>maa://20956 (95.6), *maa://20830 (80.0), maa://44703 (90.91)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="C211" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>*maa://20955 (78.38)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="C212" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>maa://39238 (99.45)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="C213" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>maa://45261 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="C214" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>maa://39694 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="C215" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>maa://24636 (100.0), maa://25778 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="C216" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>maa://48261 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="C217" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>*maa://39157 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
@@ -6717,27 +6717,27 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="17" t="inlineStr">
+      <c r="A218" s="16" t="inlineStr">
         <is>
           <t>远牙</t>
         </is>
       </c>
-      <c r="B218" s="17" t="inlineStr">
+      <c r="B218" s="16" t="inlineStr">
         <is>
           <t>S2-2</t>
         </is>
       </c>
-      <c r="C218" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D218" s="19" t="inlineStr">
-        <is>
-          <t>**maa://26496 (33.33), **maa://20995 (44.44)</t>
-        </is>
-      </c>
-      <c r="E218" s="20" t="inlineStr">
+      <c r="C218" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D218" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>&gt; 由非助战远牙累计造成80歼灭数&gt; 3星通关主题曲S2-2；必须编入非助战远牙并上场，且远牙使用光羽箭至少歼灭8名敌人</t>
         </is>
@@ -6756,12 +6756,12 @@
       </c>
       <c r="C219" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>maa://26499 (100.0), ***maa://20998 (12.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="C220" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>maa://20858 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="C221" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>maa://39695 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="C222" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>maa://20988 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
@@ -6864,12 +6864,12 @@
       </c>
       <c r="C223" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>maa://39158 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="C224" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>maa://28187 (97.44), maa://43531 (100.0), maa://39520 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="C225" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>maa://20985 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="C226" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>maa://20987 (93.1), *maa://35801 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="C227" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>*maa://29644 (73.33), maa://39159 (96.3), ***maa://30061 (30.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
@@ -6999,12 +6999,12 @@
       </c>
       <c r="C228" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>maa://30677 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="C229" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>maa://20896 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="C230" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>maa://29058 (95.83), maa://39140 (100.0), maa://38723 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="C231" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>*maa://48263 (71.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="C232" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>maa://39160 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="C233" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>maa://49491 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="C234" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>maa://35952 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="C235" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>maa://20917 (98.21)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="C236" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>maa://30714 (97.5), maa://30675 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="C237" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D237" s="14" t="inlineStr">
         <is>
-          <t>maa://20922 (94.03), *maa://32623 (75.0), maa://34242 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="C238" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>maa://32999 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="C239" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>*maa://30667 (78.21), maa://30666 (83.33), **maa://30739 (43.24), *maa://30723 (55.74), maa://39588 (88.24)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="C240" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>maa://30512 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="C241" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>maa://20870 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="C242" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>maa://29024 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="C243" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>maa://20867 (93.33), maa://38485 (95.45), *maa://32202 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="C244" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>maa://40160 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="C245" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>maa://43089 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="C246" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>maa://30674 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="C247" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>maa://28923 (92.06), maa://28906 (98.28), ***maa://28825 (11.54)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="C248" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>maa://42287 (89.74), maa://45570 (97.62), maa://42225 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="C249" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>maa://39161 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="C250" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>maa://20923 (92.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="C251" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>maa://24093 (100.0), maa://31559 (97.06), maa://20924 (95.24), *maa://49440 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
@@ -7647,12 +7647,12 @@
       </c>
       <c r="C252" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>maa://40958 (88.0), *maa://45067 (71.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="C253" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>maa://20840 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
@@ -7701,12 +7701,12 @@
       </c>
       <c r="C254" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>maa://20877 (98.63), *maa://45067 (71.43), maa://20836 (100.0), maa://20632 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="C255" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>maa://20879 (87.34), maa://20834 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="C256" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>maa://20839 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="C257" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>maa://30676 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="C258" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>maa://31560 (87.5), maa://20884 (95.45)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="C259" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>maa://47204 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="C260" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>maa://29027 (97.96)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
@@ -7890,12 +7890,12 @@
       </c>
       <c r="C261" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>maa://20977 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="C262" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>maa://39162 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="C263" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>maa://22467 (95.24)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E263" s="3" t="inlineStr">
@@ -7959,27 +7959,27 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="17" t="inlineStr">
+      <c r="A264" s="16" t="inlineStr">
         <is>
           <t>至简</t>
         </is>
       </c>
-      <c r="B264" s="17" t="inlineStr">
+      <c r="B264" s="16" t="inlineStr">
         <is>
           <t>IC-8</t>
         </is>
       </c>
-      <c r="C264" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D264" s="19" t="inlineStr">
-        <is>
-          <t>**maa://30678 (37.5)</t>
-        </is>
-      </c>
-      <c r="E264" s="20" t="inlineStr">
+      <c r="C264" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D264" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
         <is>
           <t>&gt; 战斗中非助战至简累计使用神工意匠20次&gt; 3星通关别传IC-8；必须编入非助战至简并上场，且使用至简歼灭至少2名蜜酿级醒酒助手</t>
         </is>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="C265" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>maa://49643 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="C266" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>maa://48265 (84.62)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="C267" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>*maa://20825 (71.43), *maa://21445 (70.59), *maa://35726 (63.64), ***maa://20891 (30.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="C268" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>maa://25769 (97.35)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="C269" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>maa://20862 (83.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="C270" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D270" s="12" t="inlineStr">
         <is>
-          <t>maa://51881 (99.23), maa://51630 (96.39), maa://51893 (87.5), *maa://55171 (64.29), maa://56588 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="C271" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>maa://39163 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="C272" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>maa://29061 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C273" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>maa://20939 (81.82)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
@@ -8241,12 +8241,12 @@
       </c>
       <c r="C274" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D274" s="12" t="inlineStr">
         <is>
-          <t>maa://39164 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="C275" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>maa://28133 (92.45), maa://33394 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C276" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>maa://42311 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="C277" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>maa://41362 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="C278" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D278" s="12" t="inlineStr">
         <is>
-          <t>maa://20978 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
@@ -8376,12 +8376,12 @@
       </c>
       <c r="C279" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>maa://21002 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="C280" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>*maa://39165 (57.14)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="C281" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>maa://48267 (100.0), maa://48266 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="C282" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>maa://29635 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="C283" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>maa://38296 (89.29)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E283" s="3" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="C284" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D284" s="12" t="inlineStr">
         <is>
-          <t>maa://20899 (89.29), maa://46332 (93.33), ***maa://44744 (25.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="C285" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>maa://53353 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E285" s="3" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="C286" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D286" s="12" t="inlineStr">
         <is>
-          <t>maa://20881 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
@@ -8592,12 +8592,12 @@
       </c>
       <c r="C287" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.83), maa://36845 (95.45), maa://31558 (97.06), **maa://39217 (41.18), maa://30668 (86.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr">
@@ -8619,12 +8619,12 @@
       </c>
       <c r="C288" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D288" s="12" t="inlineStr">
         <is>
-          <t>maa://20902 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="C289" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>maa://29159 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E289" s="3" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="C290" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D290" s="12" t="inlineStr">
         <is>
-          <t>maa://25774 (97.06), maa://28133 (92.45), maa://22469 (92.73), **maa://39217 (41.18), **maa://31349 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="C291" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
         <is>
-          <t>maa://47882 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="C292" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D292" s="12" t="inlineStr">
         <is>
-          <t>maa://32414 (98.77), maa://32505 (100.0), maa://39155 (97.3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="C293" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>maa://45799 (100.0), maa://57199 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E293" s="3" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="C294" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D294" s="12" t="inlineStr">
         <is>
-          <t>maa://42312 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="C295" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
         <is>
-          <t>maa://36642 (100.0), maa://36867 (97.06), maa://39155 (97.3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="C296" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D296" s="12" t="inlineStr">
         <is>
-          <t>**maa://39166 (50.0), maa://39167 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="C297" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>maa://29005 (98.68), maa://31560 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E297" s="3" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="C298" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D298" s="12" t="inlineStr">
         <is>
-          <t>maa://39168 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="C299" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>maa://39169 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E299" s="3" t="inlineStr">
@@ -8943,12 +8943,12 @@
       </c>
       <c r="C300" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D300" s="12" t="inlineStr">
         <is>
-          <t>maa://39170 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="C301" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D301" s="12" t="inlineStr">
         <is>
-          <t>maa://50280 (98.61), maa://49642 (97.67), maa://49660 (91.3), *maa://50517 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="C302" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D302" s="12" t="inlineStr">
         <is>
-          <t>maa://39171 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="C303" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D303" s="12" t="inlineStr">
         <is>
-          <t>maa://27939 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E303" s="3" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="C304" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D304" s="12" t="inlineStr">
         <is>
-          <t>maa://53352 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
@@ -9078,12 +9078,12 @@
       </c>
       <c r="C305" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>maa://29129 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E305" s="3" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="C306" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D306" s="12" t="inlineStr">
         <is>
-          <t>maa://36005 (91.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="C307" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D307" s="12" t="inlineStr">
         <is>
-          <t>maa://35859 (97.7)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E307" s="3" t="inlineStr">
@@ -9159,12 +9159,12 @@
       </c>
       <c r="C308" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D308" s="12" t="inlineStr">
         <is>
-          <t>maa://53348 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="C309" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>**maa://39172 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E309" s="3" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="C310" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D310" s="12" t="inlineStr">
         <is>
-          <t>maa://39173 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="C311" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D311" s="12" t="inlineStr">
         <is>
-          <t>maa://25775 (93.15), *maa://25393 (71.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E311" s="3" t="inlineStr">
@@ -9267,12 +9267,12 @@
       </c>
       <c r="C312" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D312" s="12" t="inlineStr">
         <is>
-          <t>maa://40161 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="C313" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D313" s="12" t="inlineStr">
         <is>
-          <t>maa://25367 (99.26)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E313" s="3" t="inlineStr">
@@ -9321,12 +9321,12 @@
       </c>
       <c r="C314" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D314" s="12" t="inlineStr">
         <is>
-          <t>*maa://43090 (61.54)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="C315" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D315" s="12" t="inlineStr">
         <is>
-          <t>maa://28070 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E315" s="3" t="inlineStr">
@@ -9375,12 +9375,12 @@
       </c>
       <c r="C316" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D316" s="12" t="inlineStr">
         <is>
-          <t>maa://28241 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="C317" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D317" s="12" t="inlineStr">
         <is>
-          <t>maa://25773 (100.0), *maa://26088 (71.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E317" s="3" t="inlineStr">
@@ -9429,12 +9429,12 @@
       </c>
       <c r="C318" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D318" s="12" t="inlineStr">
         <is>
-          <t>maa://39239 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="C319" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D319" s="12" t="inlineStr">
         <is>
-          <t>maa://39692 (99.8), maa://39810 (86.36)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C320" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D320" s="12" t="inlineStr">
         <is>
-          <t>*maa://39174 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="C321" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>maa://39175 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="C322" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D322" s="12" t="inlineStr">
         <is>
-          <t>maa://34867 (97.83), maa://34715 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="C323" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D323" s="12" t="inlineStr">
         <is>
-          <t>maa://39176 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E323" s="3" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="C324" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D324" s="12" t="inlineStr">
         <is>
-          <t>maa://42316 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="C325" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>maa://30680 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="C326" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D326" s="12" t="inlineStr">
         <is>
-          <t>maa://40956 (94.03)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
@@ -9660,27 +9660,27 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="17" t="inlineStr">
+      <c r="A327" s="16" t="inlineStr">
         <is>
           <t>深律</t>
         </is>
       </c>
-      <c r="B327" s="17" t="inlineStr">
+      <c r="B327" s="16" t="inlineStr">
         <is>
           <t>LE-4</t>
         </is>
       </c>
-      <c r="C327" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D327" s="19" t="inlineStr">
-        <is>
-          <t>**maa://39178 (33.33)</t>
-        </is>
-      </c>
-      <c r="E327" s="20" t="inlineStr">
+      <c r="C327" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D327" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="inlineStr">
         <is>
           <t>&gt; 完成5次战斗；必须编入非助战深律并上场，且每次战斗至少释放1次沉音宁神&gt; 3星通关别传LE-4；必须编入非助战深律并上场，且所有干员不被击倒</t>
         </is>
@@ -9699,12 +9699,12 @@
       </c>
       <c r="C328" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D328" s="12" t="inlineStr">
         <is>
-          <t>maa://34205 (87.5), **maa://39541 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
@@ -9726,12 +9726,12 @@
       </c>
       <c r="C329" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D329" s="12" t="inlineStr">
         <is>
-          <t>maa://43092 (100.0), maa://43093 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E329" s="3" t="inlineStr">
@@ -9753,12 +9753,12 @@
       </c>
       <c r="C330" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D330" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (98.94)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="C331" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D331" s="14" t="inlineStr">
         <is>
-          <t>maa://42968 (99.15), maa://49245 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E331" s="14" t="inlineStr">
@@ -9807,12 +9807,12 @@
       </c>
       <c r="C332" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D332" s="14" t="inlineStr">
         <is>
-          <t>*maa://40162 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E332" s="14" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="C333" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D333" s="14" t="inlineStr">
         <is>
-          <t>maa://37692 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E333" s="14" t="inlineStr">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="C334" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D334" s="14" t="inlineStr">
         <is>
-          <t>maa://30671 (82.32), maa://30669 (99.17), maa://37275 (82.5), *maa://32410 (66.67), maa://41605 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E334" s="14" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="C335" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D335" s="14" t="inlineStr">
         <is>
-          <t>maa://38295 (94.32), maa://49332 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E335" s="14" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="C336" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D336" s="14" t="inlineStr">
         <is>
-          <t>maa://32417 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E336" s="14" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="C337" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D337" s="14" t="inlineStr">
         <is>
-          <t>maa://32419 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E337" s="14" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="C338" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>maa://32416 (90.91)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="C339" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>maa://45800 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -10023,12 +10023,12 @@
       </c>
       <c r="C340" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>maa://32647 (97.83), maa://32415 (96.73), maa://34677 (100.0), maa://32892 (100.0), maa://32653 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -10050,12 +10050,12 @@
       </c>
       <c r="C341" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>maa://32420 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="C342" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>maa://35606 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="C343" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>maa://34716 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="C344" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>maa://39179 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="C345" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>maa://34865 (97.73), maa://34717 (94.03), *maa://45066 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="C346" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>maa://39180 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -10212,12 +10212,12 @@
       </c>
       <c r="C347" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>maa://45834 (100.0), maa://45833 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="C348" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>maa://39181 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -10266,12 +10266,12 @@
       </c>
       <c r="C349" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>maa://36868 (100.0), maa://35996 (97.3), **maa://39217 (41.18), maa://47349 (96.3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -10293,12 +10293,12 @@
       </c>
       <c r="C350" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>maa://36647 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="C351" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>maa://42299 (97.5), maa://42224 (81.25)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -10347,12 +10347,12 @@
       </c>
       <c r="C352" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>maa://49648 (94.87), *maa://49662 (69.23)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="C353" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>maa://36646 (98.78), maa://36845 (95.45), **maa://39217 (41.18), maa://51007 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="C354" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>maa://36645 (98.34), maa://36841 (92.54), maa://37484 (94.12), maa://37858 (93.33), maa://40489 (100.0), maa://56268 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="C355" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>maa://42635 (97.44), maa://50629 (100.0), maa://48859 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="C356" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>maa://39183 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="C357" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>maa://39184 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -10509,12 +10509,12 @@
       </c>
       <c r="C358" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>maa://40957 (93.18), maa://44635 (87.62), maa://48026 (96.15), maa://41035 (92.19), maa://44660 (92.31), maa://41128 (83.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="C359" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>maa://40164 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -10563,12 +10563,12 @@
       </c>
       <c r="C360" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>maa://48268 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="C361" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>maa://40165 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="C362" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>maa://45798 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="C363" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>maa://42331 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -10671,12 +10671,12 @@
       </c>
       <c r="C364" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>maa://42333 (100.0), maa://41977 (100.0), maa://50518 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="C365" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>maa://42338 (100.0), maa://41976 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -10725,12 +10725,12 @@
       </c>
       <c r="C366" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>maa://41110 (98.21), maa://45605 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="C367" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>maa://42343 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="C368" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>maa://43095 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="C369" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>maa://44233 (91.49), maa://45570 (97.62)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="C370" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>maa://43097 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -10860,12 +10860,12 @@
       </c>
       <c r="C371" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>maa://43872 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="C372" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>maa://53307 (83.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -10914,12 +10914,12 @@
       </c>
       <c r="C373" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>maa://43875 (98.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -10941,12 +10941,12 @@
       </c>
       <c r="C374" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>maa://42970 (86.53), maa://44745 (98.77), **maa://49516 (50.0), *maa://45952 (80.0), ***maa://46851 (14.29), maa://44896 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -10968,12 +10968,12 @@
       </c>
       <c r="C375" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>maa://44389 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -10995,12 +10995,12 @@
       </c>
       <c r="C376" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>maa://48113 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="C377" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>maa://45807 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -11049,12 +11049,12 @@
       </c>
       <c r="C378" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>maa://50552 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="C379" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>maa://47175 (100.0), maa://47174 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="C380" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>maa://47023 (86.21)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="C381" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>maa://48618 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="C382" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>maa://51907 (100.0), maa://51908 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="C384" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>maa://51898 (100.0), maa://57241 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="C385" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>maa://51880 (99.48), maa://51878 (100.0), maa://56651 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="C386" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>maa://51872 (95.89), maa://51876 (98.46), maa://51873 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">

--- a/Excel/模组任务干员名单作者版.xlsx
+++ b/Excel/模组任务干员名单作者版.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB386"/>
+  <dimension ref="A1:AB392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="10" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.05.24 13:19:10</t>
+          <t>更新日期：2025.06.07 13:19:20</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>maa://20990 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>*maa://20996 (60.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>maa://41855 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -700,12 +700,12 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>*maa://20925 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>maa://20850 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>maa://20980 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -820,12 +820,12 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>maa://20941 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>*maa://20888 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -900,12 +900,12 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>maa://20866 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -939,12 +939,12 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>maa://20857 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>maa://37695 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>maa://39023 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>maa://44401 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>maa://20919 (100.0), *maa://31611 (70.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>*maa://20848 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>maa://20930 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>maa://20897 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1251,12 +1251,12 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>maa://20865 (90.91), maa://20826 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>maa://20900 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>maa://20948 (88.89), maa://30844 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>maa://20876 (96.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>maa://45260 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>maa://20864 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>maa://44220 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>*maa://20849 (70.0), *maa://28758 (66.67), maa://29036 (95.65), *maa://42172 (61.54), maa://30285 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>maa://20920 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>maa://20863 (88.84), maa://20832 (99.05), maa://20727 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>*maa://20871 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>**maa://39024 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -1707,12 +1707,12 @@
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>maa://36644 (88.59), maa://36866 (96.15), maa://45572 (90.0), maa://27794 (100.0), maa://20843 (100.0), maa://20960 (100.0), **maa://24483 (50.0), maa://20862 (83.33), *maa://20893 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>maa://30500 (98.84), *maa://27290 (70.59), ***maa://42154 (8.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>maa://20916 (81.82), *maa://52658 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>maa://20847 (96.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>maa://20997 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>maa://27376 (91.3), maa://42635 (97.44), **maa://20838 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>maa://20962 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>*maa://29012 (80.0), maa://20928 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>maa://20882 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>maa://20892 (80.9)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>maa://20918 (95.24), maa://34883 (92.86), maa://20824 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
@@ -2004,12 +2004,12 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>maa://20889 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>maa://34718 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>maa://20910 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>maa://39025 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>maa://20938 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>maa://20954 (92.31)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>*maa://32845 (73.33), *maa://20982 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>maa://30503 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>maa://21001 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>maa://42295 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>maa://20953 (95.65), maa://31173 (96.15)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>maa://30502 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -2328,12 +2328,12 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>maa://20932 (96.3), maa://42415 (100.0), maa://40838 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>maa://44235 (98.15), maa://45604 (100.0), maa://20961 (100.0), maa://44220 (100.0), maa://20910 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -2382,12 +2382,12 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>*maa://20965 (72.73)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>maa://28900 (96.39), maa://30126 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>maa://27970 (98.61), maa://41118 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>maa://38298 (88.24)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>maa://20841 (100.0), maa://24093 (100.0), maa://31559 (97.06), maa://20924 (95.24), maa://25777 (100.0), maa://20631 (100.0), maa://28241 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>maa://20844 (96.88)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -2544,12 +2544,12 @@
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>*maa://20845 (68.0), maa://38727 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>maa://28187 (97.44), maa://33504 (100.0), maa://45144 (100.0), maa://43531 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>maa://28567 (96.72), **maa://20947 (44.12), maa://30525 (100.0), maa://38735 (100.0), *maa://28188 (70.0), maa://30524 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>maa://20993 (100.0), maa://20914 (100.0), maa://45606 (100.0), maa://20829 (100.0), maa://40159 (100.0), maa://20900 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>maa://39693 (100.0), maa://49348 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>maa://20976 (97.78), maa://20815 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>maa://20974 (96.3), maa://29079 (80.95), maa://29096 (95.65), maa://29087 (100.0), *maa://20823 (80.0), maa://20855 (93.33), maa://20904 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>maa://20944 (95.65), maa://35393 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>maa://20943 (99.35), maa://30673 (100.0), maa://30672 (100.0), maa://20856 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>maa://36643 (98.16), maa://36864 (97.94), maa://39140 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>maa://39139 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>maa://39142 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>maa://20989 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>maa://20873 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>maa://20958 (94.44)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>maa://20957 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>maa://20875 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>maa://20952 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>maa://30525 (100.0), maa://20859 (100.0), *maa://28188 (70.0), maa://30524 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>maa://28072 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="C83" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>maa://45572 (90.0), maa://27794 (100.0), maa://20960 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>maa://20972 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>maa://20874 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>maa://20885 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>maa://20886 (93.55)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>maa://24472 (88.18), *maa://35841 (62.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>maa://44402 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>*maa://28190 (61.76), maa://20880 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="C91" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>maa://24609 (92.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
-          <t>maa://20890 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="C93" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>maa://20984 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="C94" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>maa://40157 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="C95" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>maa://20927 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>*maa://20926 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
@@ -3462,12 +3462,12 @@
       </c>
       <c r="C97" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>maa://20991 (100.0), maa://51015 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="C98" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>maa://20967 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="C99" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>maa://20929 (94.12)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>maa://20852 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>maa://45572 (90.0), maa://27794 (100.0), *maa://20893 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>maa://40517 (95.83), *maa://39240 (60.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E102" s="3" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="C103" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>*maa://29094 (69.77), maa://28904 (88.24), **maa://20931 (46.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="C104" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>*maa://20966 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="C105" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>maa://39143 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>maa://45572 (90.0), maa://27794 (100.0), maa://20843 (100.0), **maa://24483 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="C107" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>maa://20894 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>maa://25018 (96.49), maa://51881 (99.23), maa://25776 (92.11), maa://28361 (97.3), maa://25772 (94.12), maa://32653 (85.71), maa://25161 (81.25), maa://45194 (87.5), maa://56588 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E108" s="3" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="C109" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>maa://45259 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>maa://20887 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>*maa://28554 (79.17)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>maa://20933 (83.56), maa://20822 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="C113" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>maa://29037 (98.41)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
         <is>
-          <t>maa://20904 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E114" s="3" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="C115" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>maa://20908 (98.01), maa://35723 (95.92), *maa://23346 (77.78), maa://38822 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>maa://29659 (85.29), maa://29031 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E116" s="3" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>maa://31560 (87.5), maa://20940 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>maa://20986 (93.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>maa://31560 (87.5), maa://20851 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>maa://20949 (92.31)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>maa://20869 (100.0), maa://44690 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="C122" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>maa://29650 (98.21), maa://45570 (97.62)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>maa://20868 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="C124" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>*maa://20909 (70.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="C125" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>maa://44403 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
@@ -4245,12 +4245,12 @@
       </c>
       <c r="C126" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>maa://30501 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="C127" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>maa://20914 (100.0), maa://31937 (100.0), maa://20829 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>maa://37484 (94.12), maa://24611 (90.32)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C129" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>maa://24491 (100.0), maa://24493 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>maa://21422 (99.02)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>maa://30719 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
-          <t>maa://20837 (100.0), maa://37666 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E132" s="3" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>maa://29023 (100.0), maa://39515 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D134" s="12" t="inlineStr">
         <is>
-          <t>maa://39146 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E134" s="3" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="C135" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>maa://20856 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D136" s="12" t="inlineStr">
         <is>
-          <t>maa://20913 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="C137" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>maa://41856 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
-          <t>maa://29025 (82.14), **maa://21000 (41.38)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="C139" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>**maa://30679 (50.0), maa://45258 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
         <is>
-          <t>maa://20981 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="C141" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>maa://37689 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D142" s="12" t="inlineStr">
         <is>
-          <t>maa://28484 (97.04), **maa://23736 (43.28), maa://31185 (83.33), maa://30306 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="C143" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>maa://30670 (96.53), maa://31470 (96.55), *maa://45066 (66.67), **maa://30867 (40.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D144" s="12" t="inlineStr">
         <is>
-          <t>maa://20971 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>maa://39147 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D146" s="12" t="inlineStr">
         <is>
-          <t>maa://20898 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E146" s="3" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="C147" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>maa://29056 (100.0), ***maa://20901 (8.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D148" s="12" t="inlineStr">
         <is>
-          <t>maa://28828 (88.24), maa://20846 (95.83), **maa://47286 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="C149" s="13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>maa://36641 (98.42), maa://40957 (93.17), maa://36865 (96.23), maa://44635 (87.62), maa://44660 (92.31), maa://41128 (83.78), maa://42918 (100.0), maa://44119 (97.44), maa://46108 (100.0), maa://37300 (100.0), maa://42917 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D150" s="12" t="inlineStr">
         <is>
-          <t>maa://51549 (96.55), maa://51923 (94.12)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="C151" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>maa://20961 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="C152" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D152" s="12" t="inlineStr">
         <is>
-          <t>maa://20963 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="C153" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>maa://39148 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="C154" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D154" s="12" t="inlineStr">
         <is>
-          <t>maa://20946 (100.0), maa://20833 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="C155" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>maa://20945 (88.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="C156" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D156" s="12" t="inlineStr">
         <is>
-          <t>maa://37694 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="C157" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>**maa://39149 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="C158" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D158" s="12" t="inlineStr">
         <is>
-          <t>maa://20959 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E158" s="3" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="C159" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>maa://44232 (98.68), maa://45603 (90.0), maa://44305 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
@@ -5163,12 +5163,12 @@
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D160" s="12" t="inlineStr">
         <is>
-          <t>maa://20936 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="C161" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>maa://20855 (93.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D162" s="12" t="inlineStr">
         <is>
-          <t>maa://40158 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="C163" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>*maa://32845 (73.33), maa://29054 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D164" s="12" t="inlineStr">
         <is>
-          <t>maa://20973 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="C165" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>maa://39150 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="C166" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D166" s="12" t="inlineStr">
         <is>
-          <t>maa://20975 (90.91), maa://30806 (100.0), *maa://47950 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="C167" s="13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>maa://29633 (92.49), maa://29627 (92.63), maa://29659 (85.29), maa://49074 (97.22), **maa://30679 (50.0), maa://29861 (100.0), maa://42343 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D168" s="12" t="inlineStr">
         <is>
-          <t>maa://49655 (95.45), maa://49867 (93.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C169" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>maa://29059 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D170" s="12" t="inlineStr">
         <is>
-          <t>maa://45556 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="C171" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>maa://40159 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
@@ -5487,12 +5487,12 @@
       </c>
       <c r="C172" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D172" s="12" t="inlineStr">
         <is>
-          <t>maa://39152 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
@@ -5514,12 +5514,12 @@
       </c>
       <c r="C173" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>*maa://20905 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="C174" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D174" s="12" t="inlineStr">
         <is>
-          <t>maa://32418 (99.68), maa://51440 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -5558,81 +5558,81 @@
     <row r="175">
       <c r="A175" s="16" t="inlineStr">
         <is>
-          <t>豆苗</t>
+          <t>山</t>
         </is>
       </c>
       <c r="B175" s="16" t="inlineStr">
         <is>
-          <t>S3-7</t>
+          <t>LE-5</t>
         </is>
       </c>
       <c r="C175" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>maa://37690 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战豆苗，并确定第一位部署的干员是豆苗&gt; 3星通关主题曲S3-7；必须编入非助战豆苗并上场，且至少使用1次“大家一起上”</t>
+          <t>&gt; 完成5次战斗，必须编入非助战山，且每次战斗使用山造成至少12000点伤害&gt; 3星通关插曲LE-5，必须编入非助战山并上场，且使用山歼灭至少10名敌人</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="16" t="inlineStr">
         <is>
-          <t>爱丽丝</t>
+          <t>豆苗</t>
         </is>
       </c>
       <c r="B176" s="16" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>S3-7</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D176" s="12" t="inlineStr">
         <is>
-          <t>maa://20842 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战爱丽丝累计造成30歼灭数&gt; 3星通关主题曲2-2；必须编入非助战爱丽丝并上场，且使用爱丽丝歼灭至少2个重装防御者</t>
+          <t>&gt; 完成5次战斗；必须编入非助战豆苗，并确定第一位部署的干员是豆苗&gt; 3星通关主题曲S3-7；必须编入非助战豆苗并上场，且至少使用1次“大家一起上”</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="16" t="inlineStr">
         <is>
-          <t>空弦</t>
+          <t>爱丽丝</t>
         </is>
       </c>
       <c r="B177" s="16" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C177" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>maa://20912 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战空弦累计造成100000点伤害&gt; 3星通关插曲SV-4；必须编入非助战空弦并上场，其他成员不可编入狙击干员</t>
+          <t>&gt; 由非助战爱丽丝累计造成30歼灭数&gt; 3星通关主题曲2-2；必须编入非助战爱丽丝并上场，且使用爱丽丝歼灭至少2个重装防御者</t>
         </is>
       </c>
     </row>
@@ -5644,130 +5644,130 @@
       </c>
       <c r="B178" s="16" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C178" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D178" s="12" t="inlineStr">
         <is>
-          <t>maa://20911 (95.45), *maa://29012 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战空弦并上场，且使用空弦歼灭至少5名敌人&gt; 3星通关主题曲2-9；必须编入非助战空弦并上场，且不编入其他狙击干员</t>
+          <t>&gt; 由非助战空弦累计造成100000点伤害&gt; 3星通关插曲SV-4；必须编入非助战空弦并上场，其他成员不可编入狙击干员</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="16" t="inlineStr">
         <is>
-          <t>图耶</t>
+          <t>空弦</t>
         </is>
       </c>
       <c r="B179" s="16" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="C179" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>maa://20964 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战图耶并上场，且每次战斗至少释放1次强心剂&gt; 3星通关主题曲4-6；必须编入非助战图耶并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战空弦并上场，且使用空弦歼灭至少5名敌人&gt; 3星通关主题曲2-9；必须编入非助战空弦并上场，且不编入其他狙击干员</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="16" t="inlineStr">
         <is>
-          <t>炎狱炎熔</t>
+          <t>图耶</t>
         </is>
       </c>
       <c r="B180" s="16" t="inlineStr">
         <is>
-          <t>WR-4</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D180" s="12" t="inlineStr">
         <is>
-          <t>maa://20983 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战炎狱炎熔累计造成80歼灭数&gt; 3星通关别传WR-4； 必须编入非助战炎狱炎熔并上场，且使用炎狱炎熔歼灭至少8名敌人、其中包括至少1名“偷闲”</t>
+          <t>&gt; 完成5次战斗；必须编入非助战图耶并上场，且每次战斗至少释放1次强心剂&gt; 3星通关主题曲4-6；必须编入非助战图耶并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="16" t="inlineStr">
         <is>
-          <t>乌有</t>
+          <t>炎狱炎熔</t>
         </is>
       </c>
       <c r="B181" s="16" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>WR-4</t>
         </is>
       </c>
       <c r="C181" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>maa://31560 (87.5), *maa://20968 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战乌有并部署至少2次，且使用乌有歼灭至少4名敌人&gt; 3星通关主题曲3-7；必须编入非助战乌有并上场，且使用乌有歼灭至少2个炮手</t>
+          <t>&gt; 由非助战炎狱炎熔累计造成80歼灭数&gt; 3星通关别传WR-4； 必须编入非助战炎狱炎熔并上场，且使用炎狱炎熔歼灭至少8名敌人、其中包括至少1名“偷闲”</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="16" t="inlineStr">
         <is>
-          <t>嵯峨</t>
+          <t>乌有</t>
         </is>
       </c>
       <c r="B182" s="16" t="inlineStr">
         <is>
-          <t>WR-3</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C182" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D182" s="12" t="inlineStr">
         <is>
-          <t>maa://28104 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战嵯峨累计造成80000点伤害&gt; 3星通关别传WR-3；必须编入非助战嵯峨，且第一位部署嵯峨、嵯峨全程不撤退或被击倒</t>
+          <t>&gt; 完成5次战斗；必须编入非助战乌有并部署至少2次，且使用乌有歼灭至少4名敌人&gt; 3星通关主题曲3-7；必须编入非助战乌有并上场，且使用乌有歼灭至少2个炮手</t>
         </is>
       </c>
     </row>
@@ -5779,49 +5779,49 @@
       </c>
       <c r="B183" s="16" t="inlineStr">
         <is>
-          <t>WR-1</t>
+          <t>WR-3</t>
         </is>
       </c>
       <c r="C183" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>maa://20861 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战嵯峨，并确定第一位部署的干员是嵯峨&gt; 3星通关别传WR-1；必须编入非助战嵯峨并上场，其他成员仅可编入2名干员</t>
+          <t>&gt; 由非助战嵯峨累计造成80000点伤害&gt; 3星通关别传WR-3；必须编入非助战嵯峨，且第一位部署嵯峨、嵯峨全程不撤退或被击倒</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="16" t="inlineStr">
         <is>
-          <t>夕</t>
+          <t>嵯峨</t>
         </is>
       </c>
       <c r="B184" s="16" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>WR-1</t>
         </is>
       </c>
       <c r="C184" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D184" s="12" t="inlineStr">
         <is>
-          <t>maa://20970 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计召唤非助战夕的召唤物20回&gt; 使用至多2人（包含助战）的队伍3星通关主题曲1-6；必须编入非助战夕并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战嵯峨，并确定第一位部署的干员是嵯峨&gt; 3星通关别传WR-1；必须编入非助战嵯峨并上场，其他成员仅可编入2名干员</t>
         </is>
       </c>
     </row>
@@ -5833,130 +5833,130 @@
       </c>
       <c r="B185" s="16" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="C185" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>maa://20969 (86.21), maa://41303 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战夕累计造成80歼灭数&gt; 3星通关主题曲4-3；必须编入非助战夕并上场，其他成员仅可编入先锋干员</t>
+          <t>&gt; 战斗中累计召唤非助战夕的召唤物20回&gt; 使用至多2人（包含助战）的队伍3星通关主题曲1-6；必须编入非助战夕并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="16" t="inlineStr">
         <is>
-          <t>战车</t>
+          <t>夕</t>
         </is>
       </c>
       <c r="B186" s="16" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C186" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>maa://20999 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战战车累计造成150000点伤害&gt; 使用至多2人（包含助战）的队伍3星通关主题曲S2-3；必须编入非助战战车并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 由非助战夕累计造成80歼灭数&gt; 3星通关主题曲4-3；必须编入非助战夕并上场，其他成员仅可编入先锋干员</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="16" t="inlineStr">
         <is>
-          <t>闪击</t>
+          <t>战车</t>
         </is>
       </c>
       <c r="B187" s="16" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C187" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>maa://35198 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战闪击累计造成30歼灭数&gt; 3星通关主题曲3-4；必须编入非助战闪击并上场，且使用闪击歼灭至少2名屠夫</t>
+          <t>&gt; 由非助战战车累计造成150000点伤害&gt; 使用至多2人（包含助战）的队伍3星通关主题曲S2-3；必须编入非助战战车并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="16" t="inlineStr">
         <is>
-          <t>霜华</t>
+          <t>闪击</t>
         </is>
       </c>
       <c r="B188" s="16" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>maa://39153 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战霜华累计造成100000点伤害※迎宾踏垫造成的伤害可计数&gt; 3星通关主题曲4-4；必须编入非助战霜华并上场，且使用霜华歼灭弑君者※允许使用迎宾踏垫歼灭弑君者</t>
+          <t>&gt; 由非助战闪击累计造成30歼灭数&gt; 3星通关主题曲3-4；必须编入非助战闪击并上场，且使用闪击歼灭至少2名屠夫</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="16" t="inlineStr">
         <is>
-          <t>灰烬</t>
+          <t>霜华</t>
         </is>
       </c>
       <c r="B189" s="16" t="inlineStr">
         <is>
-          <t>SV-8</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C189" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>maa://34866 (92.86), maa://34714 (96.3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战灰烬累计造成100000点伤害&gt; 3星通关插曲SV-8；必须编入非助战灰烬并上场，且使用灰烬歼灭至少2名囊海爬行者</t>
+          <t>&gt; 由非助战霜华累计造成100000点伤害※迎宾踏垫造成的伤害可计数&gt; 3星通关主题曲4-4；必须编入非助战霜华并上场，且使用霜华歼灭弑君者※允许使用迎宾踏垫歼灭弑君者</t>
         </is>
       </c>
     </row>
@@ -5968,103 +5968,103 @@
       </c>
       <c r="B190" s="16" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>SV-8</t>
         </is>
       </c>
       <c r="C190" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>maa://34883 (92.86), maa://20895 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战灰烬累计歼灭10个精英敌人&gt; 3星通关主题曲1-12；必须编入非助战灰烬并上场，且使用灰烬歼灭W</t>
+          <t>&gt; 由非助战灰烬累计造成100000点伤害&gt; 3星通关插曲SV-8；必须编入非助战灰烬并上场，且使用灰烬歼灭至少2名囊海爬行者</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="16" t="inlineStr">
         <is>
-          <t>暴雨</t>
+          <t>灰烬</t>
         </is>
       </c>
       <c r="B191" s="16" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C191" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>maa://20853 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战暴雨累计使用应急迷彩30次&gt; 3星通关主题曲2-7；必须编入非助战暴雨并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战灰烬累计歼灭10个精英敌人&gt; 3星通关主题曲1-12；必须编入非助战灰烬并上场，且使用灰烬歼灭W</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="16" t="inlineStr">
         <is>
-          <t>熔泉</t>
+          <t>暴雨</t>
         </is>
       </c>
       <c r="B192" s="16" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C192" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D192" s="12" t="inlineStr">
         <is>
-          <t>maa://20942 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战熔泉累计歼灭20个萨卡兹敌人&gt; 3星通关主题曲4-6；必须编入非助战熔泉并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 战斗中非助战暴雨累计使用应急迷彩30次&gt; 3星通关主题曲2-7；必须编入非助战暴雨并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="16" t="inlineStr">
         <is>
-          <t>异客</t>
+          <t>熔泉</t>
         </is>
       </c>
       <c r="B193" s="16" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C193" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>maa://20992 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战异客累计使用辉煌裂片30次&gt; 3星通关主题曲2-2；必须编入非助战异客并上场，其他成员仅可编入先锋和重装干员</t>
+          <t>&gt; 由非助战熔泉累计歼灭20个萨卡兹敌人&gt; 3星通关主题曲4-6；必须编入非助战熔泉并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
     </row>
@@ -6076,76 +6076,76 @@
       </c>
       <c r="B194" s="16" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C194" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D194" s="12" t="inlineStr">
         <is>
-          <t>*maa://28190 (61.76), maa://20994 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战异客并上场，且使用异客造成至少30000点伤害&gt; 3星通关主题曲5-10；必须编入非助战异客并上场，且使用异客歼灭至少2个粉碎攻坚手</t>
+          <t>&gt; 战斗中非助战异客累计使用辉煌裂片30次&gt; 3星通关主题曲2-2；必须编入非助战异客并上场，其他成员仅可编入先锋和重装干员</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="16" t="inlineStr">
         <is>
-          <t>赤冬</t>
+          <t>异客</t>
         </is>
       </c>
       <c r="B195" s="16" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C195" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>maa://20860 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战赤冬累计使用信影流·十文字胜5次&gt; 3星通关主题曲3-8；必须编入非助战赤冬并上场，且使用赤冬歼灭碎骨</t>
+          <t>&gt; 完成5次战斗；必须编入非助战异客并上场，且使用异客造成至少30000点伤害&gt; 3星通关主题曲5-10；必须编入非助战异客并上场，且使用异客歼灭至少2个粉碎攻坚手</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="16" t="inlineStr">
         <is>
-          <t>歌蕾蒂娅</t>
+          <t>赤冬</t>
         </is>
       </c>
       <c r="B196" s="16" t="inlineStr">
         <is>
-          <t>SV-EX-5</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C196" s="13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D196" s="12" t="inlineStr">
         <is>
-          <t>maa://44224 (90.97), maa://35854 (85.37), maa://25760 (87.16), maa://50388 (97.67), **maa://20872 (50.0), ***maa://43911 (14.29), maa://51066 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战歌蕾蒂娅并上场，且每次战斗至少释放1次缺水的碎漩狂舞&gt; 3星通关插曲SV-EX-5；必须编入非助战歌蕾蒂娅，且至少使1个富营养的收割者坠落地穴</t>
+          <t>&gt; 战斗中非助战赤冬累计使用信影流·十文字胜5次&gt; 3星通关主题曲3-8；必须编入非助战赤冬并上场，且使用赤冬歼灭碎骨</t>
         </is>
       </c>
     </row>
@@ -6157,49 +6157,49 @@
       </c>
       <c r="B197" s="16" t="inlineStr">
         <is>
-          <t>SN-EX-3</t>
+          <t>SV-EX-5</t>
         </is>
       </c>
       <c r="C197" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>maa://39156 (93.98), *maa://39550 (57.89), *maa://53417 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战歌蕾蒂娅，且每次战斗至少使2名敌人坠落地穴&gt; 3星通关插曲SN-EX-3；必须编入非助战歌蕾蒂娅并上场，且使用至少2次缺水的掌握怒海或缺水的碎漩狂舞</t>
+          <t>&gt; 完成5次战斗；必须编入非助战歌蕾蒂娅并上场，且每次战斗至少释放1次缺水的碎漩狂舞&gt; 3星通关插曲SV-EX-5；必须编入非助战歌蕾蒂娅，且至少使1个富营养的收割者坠落地穴</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="16" t="inlineStr">
         <is>
-          <t>凯尔希</t>
+          <t>歌蕾蒂娅</t>
         </is>
       </c>
       <c r="B198" s="16" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>SN-EX-3</t>
         </is>
       </c>
       <c r="C198" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>maa://27823 (84.42), *maa://28190 (61.76), maa://22894 (90.91), *maa://20906 (72.22), **maa://20907 (35.48)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战凯尔希累计造成150000点伤害※Mon3tr造成的伤害会计数&gt; 3星通关主题曲5-10；必须编入非助战凯尔希并上场，且使用4次指令：熔毁</t>
+          <t>&gt; 完成5次战斗；必须编入非助战歌蕾蒂娅，且每次战斗至少使2名敌人坠落地穴&gt; 3星通关插曲SN-EX-3；必须编入非助战歌蕾蒂娅并上场，且使用至少2次缺水的掌握怒海或缺水的碎漩狂舞</t>
         </is>
       </c>
     </row>
@@ -6216,51 +6216,51 @@
       </c>
       <c r="C199" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
         <is>
-          <t>maa://27823 (84.42), *maa://28190 (61.76), maa://22894 (90.91), *maa://20906 (72.22), **maa://20907 (35.48)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战凯尔希累计使用指令：熔毁10次&gt; 3星通关主题曲5-10；必须编入非助战凯尔希并上场，且使用Mon3tr歼灭梅菲斯特</t>
+          <t>&gt; 由非助战凯尔希累计造成150000点伤害※Mon3tr造成的伤害会计数&gt; 3星通关主题曲5-10；必须编入非助战凯尔希并上场，且使用4次指令：熔毁</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="16" t="inlineStr">
         <is>
-          <t>浊心斯卡蒂</t>
+          <t>凯尔希</t>
         </is>
       </c>
       <c r="B200" s="16" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C200" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>maa://42223 (99.58), maa://49077 (91.67), maa://42292 (97.22), maa://42402 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>&gt; 携带非助战浊心斯卡蒂完成5次战斗，且每次战斗至少发动一次“同葬无光之愿”&gt; 3星通关插曲SV-5；必须编入非助战浊心斯卡蒂并上场，且队伍中不能有医疗干员</t>
+          <t>&gt; 战斗中非助战凯尔希累计使用指令：熔毁10次&gt; 3星通关主题曲5-10；必须编入非助战凯尔希并上场，且使用Mon3tr歼灭梅菲斯特</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="16" t="inlineStr">
         <is>
-          <t>深靛</t>
+          <t>浊心斯卡蒂</t>
         </is>
       </c>
       <c r="B201" s="16" t="inlineStr">
@@ -6270,98 +6270,98 @@
       </c>
       <c r="C201" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>maa://39154 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战深靛累计造成60000点伤害&gt; 3星通关插曲SV-5；必须编入非助战深靛并上场，且使用2次光影迷宫</t>
+          <t>&gt; 携带非助战浊心斯卡蒂完成5次战斗，且每次战斗至少发动一次“同葬无光之愿”&gt; 3星通关插曲SV-5；必须编入非助战浊心斯卡蒂并上场，且队伍中不能有医疗干员</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="16" t="inlineStr">
         <is>
-          <t>贝娜</t>
+          <t>深靛</t>
         </is>
       </c>
       <c r="B202" s="16" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C202" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>maa://20854 (92.31)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战贝娜并上场，且每次战斗至少释放1次快速修剪&gt; 3星通关主题曲2-3；必须编入非助战贝娜并上场，且使用贝娜歼灭至少1个重装防御者</t>
+          <t>&gt; 由非助战深靛累计造成60000点伤害&gt; 3星通关插曲SV-5；必须编入非助战深靛并上场，且使用2次光影迷宫</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="16" t="inlineStr">
         <is>
-          <t>绮良</t>
+          <t>贝娜</t>
         </is>
       </c>
       <c r="B203" s="16" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C203" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>maa://20937 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战绮良累计使用锚点捕捉5次&gt; 3星通关主题曲3-1；必须编入非助战绮良并上场，且使用绮良歼灭20个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战贝娜并上场，且每次战斗至少释放1次快速修剪&gt; 3星通关主题曲2-3；必须编入非助战贝娜并上场，且使用贝娜歼灭至少1个重装防御者</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="16" t="inlineStr">
         <is>
-          <t>卡涅利安</t>
+          <t>绮良</t>
         </is>
       </c>
       <c r="B204" s="16" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C204" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>maa://22468 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战卡涅利安累计造成120000点伤害&gt; 3星通关主题曲7-3；必须编入非助战卡涅利安并上场，且不编入重装干员</t>
+          <t>&gt; 战斗中非助战绮良累计使用锚点捕捉5次&gt; 3星通关主题曲3-1；必须编入非助战绮良并上场，且使用绮良歼灭20个敌人</t>
         </is>
       </c>
     </row>
@@ -6373,49 +6373,49 @@
       </c>
       <c r="B205" s="16" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C205" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>maa://30673 (100.0), maa://30672 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战卡涅利安累计造成80歼灭数&gt; 3星通关主题曲4-6；必须编入非助战卡涅利安并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 由非助战卡涅利安累计造成120000点伤害&gt; 3星通关主题曲7-3；必须编入非助战卡涅利安并上场，且不编入重装干员</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="16" t="inlineStr">
         <is>
-          <t>帕拉斯</t>
+          <t>卡涅利安</t>
         </is>
       </c>
       <c r="B206" s="16" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C206" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>maa://20934 (100.0), maa://20827 (100.0), maa://20828 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战帕拉斯累计造成50歼灭数&gt; 使用至多2人（包含助战）的队伍3星通关主题曲3-6；必须编入非助战帕拉斯并上场，其他成员仅可编入医疗干员</t>
+          <t>&gt; 由非助战卡涅利安累计造成80歼灭数&gt; 3星通关主题曲4-6；必须编入非助战卡涅利安并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
     </row>
@@ -6427,103 +6427,103 @@
       </c>
       <c r="B207" s="16" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C207" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>maa://20935 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战帕拉斯累计使用英勇的祝福5次&gt; 3星通关主题曲4-3；必须编入非助战帕拉斯并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 由非助战帕拉斯累计造成50歼灭数&gt; 使用至多2人（包含助战）的队伍3星通关主题曲3-6；必须编入非助战帕拉斯并上场，其他成员仅可编入医疗干员</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="16" t="inlineStr">
         <is>
-          <t>龙舌兰</t>
+          <t>帕拉斯</t>
         </is>
       </c>
       <c r="B208" s="16" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C208" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>maa://53354 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战龙舌兰累计造成30歼灭数&gt; 3星通关主题曲7-11；必须编入非助战龙舌兰并上场，且使用2次剑走偏锋</t>
+          <t>&gt; 战斗中非助战帕拉斯累计使用英勇的祝福5次&gt; 3星通关主题曲4-3；必须编入非助战帕拉斯并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="16" t="inlineStr">
         <is>
-          <t>羽毛笔</t>
+          <t>龙舌兰</t>
         </is>
       </c>
       <c r="B209" s="16" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C209" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>maa://28133 (92.45), **maa://39217 (41.18), maa://25369 (94.12)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战羽毛笔并上场，且使用羽毛笔造成至少12000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战羽毛笔并上场，且使用羽毛笔至少歼灭15个敌人</t>
+          <t>&gt; 由非助战龙舌兰累计造成30歼灭数&gt; 3星通关主题曲7-11；必须编入非助战龙舌兰并上场，且使用2次剑走偏锋</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="16" t="inlineStr">
         <is>
-          <t>水月</t>
+          <t>羽毛笔</t>
         </is>
       </c>
       <c r="B210" s="16" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C210" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>maa://20956 (95.6), *maa://20830 (80.0), maa://44703 (90.91)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战水月累计造成150000点伤害&gt; 3星通关主题曲4-3；必须编入非助战水月并上场，且使用水月歼灭至少2名萨卡兹狙击手</t>
+          <t>&gt; 完成5次战斗；必须编入非助战羽毛笔并上场，且使用羽毛笔造成至少12000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战羽毛笔并上场，且使用羽毛笔至少歼灭15个敌人</t>
         </is>
       </c>
     </row>
@@ -6535,130 +6535,130 @@
       </c>
       <c r="B211" s="16" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C211" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>*maa://20955 (78.38)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战水月累计造成50歼灭数&gt; 3星通关主题曲4-5；必须编入非助战水月并上场，且使用水月歼灭10个敌人</t>
+          <t>&gt; 由非助战水月累计造成150000点伤害&gt; 3星通关主题曲4-3；必须编入非助战水月并上场，且使用水月歼灭至少2名萨卡兹狙击手</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="16" t="inlineStr">
         <is>
-          <t>假日威龙陈</t>
+          <t>水月</t>
         </is>
       </c>
       <c r="B212" s="16" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C212" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>maa://39238 (99.45)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战假日威龙陈累计造成120000伤害&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战假日威龙陈并上场，且使用假日威龙陈至少歼灭20个敌人</t>
+          <t>&gt; 由非助战水月累计造成50歼灭数&gt; 3星通关主题曲4-5；必须编入非助战水月并上场，且使用水月歼灭10个敌人</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="16" t="inlineStr">
         <is>
-          <t>罗比菈塔</t>
+          <t>假日威龙陈</t>
         </is>
       </c>
       <c r="B213" s="16" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C213" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>maa://45261 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战罗比菈塔累计部署支援装置25个&gt; 3星通关主题曲3-8；必须编入非助战罗比菈塔并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战假日威龙陈累计造成120000伤害&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战假日威龙陈并上场，且使用假日威龙陈至少歼灭20个敌人</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="16" t="inlineStr">
         <is>
-          <t>桑葚</t>
+          <t>罗比菈塔</t>
         </is>
       </c>
       <c r="B214" s="16" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C214" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>maa://39694 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战桑葚并上场，且每次战斗至少释放1次安全区域&gt; 3星通关插曲SV-5；必须编入非助战桑葚并上场，其他成员仅可编入7名干员</t>
+          <t>&gt; 战斗中非助战罗比菈塔累计部署支援装置25个&gt; 3星通关主题曲3-8；必须编入非助战罗比菈塔并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="16" t="inlineStr">
         <is>
-          <t>琴柳</t>
+          <t>桑葚</t>
         </is>
       </c>
       <c r="B215" s="16" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C215" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>maa://24636 (100.0), maa://25778 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战琴柳累计使用信仰传承10次&gt; 3星通关主题曲9-2；必须编入非助战琴柳并上场，且不编入其他先锋干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战桑葚并上场，且每次战斗至少释放1次安全区域&gt; 3星通关插曲SV-5；必须编入非助战桑葚并上场，其他成员仅可编入7名干员</t>
         </is>
       </c>
     </row>
@@ -6670,76 +6670,76 @@
       </c>
       <c r="B216" s="16" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C216" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>maa://48261 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战琴柳并上场，且每次战斗至少释放1次光辉旗帜&gt; 3星通关主题曲5-3；必须编入非助战琴柳并上场，且至少使用3次光辉旗帜</t>
+          <t>&gt; 战斗中非助战琴柳累计使用信仰传承10次&gt; 3星通关主题曲9-2；必须编入非助战琴柳并上场，且不编入其他先锋干员</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="16" t="inlineStr">
         <is>
+          <t>琴柳</t>
+        </is>
+      </c>
+      <c r="B217" s="16" t="inlineStr">
+        <is>
+          <t>5-3</t>
+        </is>
+      </c>
+      <c r="C217" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D217" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>&gt; 完成5次战斗；必须编入非助战琴柳并上场，且每次战斗至少释放1次光辉旗帜&gt; 3星通关主题曲5-3；必须编入非助战琴柳并上场，且至少使用3次光辉旗帜</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="16" t="inlineStr">
+        <is>
           <t>灰毫</t>
         </is>
       </c>
-      <c r="B217" s="16" t="inlineStr">
+      <c r="B218" s="16" t="inlineStr">
         <is>
           <t>7-9</t>
         </is>
       </c>
-      <c r="C217" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D217" s="12" t="inlineStr">
-        <is>
-          <t>*maa://39157 (75.0)</t>
-        </is>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
+      <c r="C218" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D218" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>&gt; 由非助战灰毫累计造成100000点伤害&gt; 3星通关主题曲7-9；必须编入非助战灰毫并上场，且使用灰毫歼灭至少2名游击队传令兵</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="17" t="inlineStr">
-        <is>
-          <t>远牙</t>
-        </is>
-      </c>
-      <c r="B218" s="17" t="inlineStr">
-        <is>
-          <t>S2-2</t>
-        </is>
-      </c>
-      <c r="C218" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D218" s="19" t="inlineStr">
-        <is>
-          <t>**maa://26496 (33.33), **maa://20995 (44.44)</t>
-        </is>
-      </c>
-      <c r="E218" s="20" t="inlineStr">
-        <is>
-          <t>&gt; 由非助战远牙累计造成80歼灭数&gt; 3星通关主题曲S2-2；必须编入非助战远牙并上场，且远牙使用光羽箭至少歼灭8名敌人</t>
         </is>
       </c>
     </row>
@@ -6751,157 +6751,157 @@
       </c>
       <c r="B219" s="16" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C219" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>maa://26499 (100.0), ***maa://20998 (12.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战远牙并上场，且每次战斗至少释放2次光羽箭&gt; 3星通关主题曲2-5；必须编入非助战远牙并上场，且使用远牙歼灭至少2名高阶术师</t>
+          <t>&gt; 由非助战远牙累计造成80歼灭数&gt; 3星通关主题曲S2-2；必须编入非助战远牙并上场，且远牙使用光羽箭至少歼灭8名敌人</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="16" t="inlineStr">
         <is>
-          <t>布丁</t>
+          <t>远牙</t>
         </is>
       </c>
       <c r="B220" s="16" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C220" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>maa://20858 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战布丁累计造成150000点伤害&gt; 3星通关主题曲2-10；必须编入非助战布丁并上场，且布丁使用技能扩散电流至少歼灭2个重装防御者</t>
+          <t>&gt; 完成5次战斗；必须编入非助战远牙并上场，且每次战斗至少释放2次光羽箭&gt; 3星通关主题曲2-5；必须编入非助战远牙并上场，且使用远牙歼灭至少2名高阶术师</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="16" t="inlineStr">
         <is>
-          <t>蜜莓</t>
+          <t>布丁</t>
         </is>
       </c>
       <c r="B221" s="16" t="inlineStr">
         <is>
-          <t>GA-2</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C221" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>maa://39695 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战蜜莓累计使用振奋8次&gt; 3星通关别传GA-2；必须编入非助战蜜莓并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战布丁累计造成150000点伤害&gt; 3星通关主题曲2-10；必须编入非助战布丁并上场，且布丁使用技能扩散电流至少歼灭2个重装防御者</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="16" t="inlineStr">
         <is>
-          <t>野鬃</t>
+          <t>蜜莓</t>
         </is>
       </c>
       <c r="B222" s="16" t="inlineStr">
         <is>
-          <t>MN-2</t>
+          <t>GA-2</t>
         </is>
       </c>
       <c r="C222" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>maa://20988 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战野鬃，并确定第一位部署的干员是野鬃&gt; 3星通关别传MN-2；必须编入非助战野鬃并上场，其他成员不可编入先锋干员</t>
+          <t>&gt; 战斗中非助战蜜莓累计使用振奋8次&gt; 3星通关别传GA-2；必须编入非助战蜜莓并上场，且不编入其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="16" t="inlineStr">
         <is>
-          <t>蚀清</t>
+          <t>野鬃</t>
         </is>
       </c>
       <c r="B223" s="16" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>MN-2</t>
         </is>
       </c>
       <c r="C223" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>maa://39158 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战蚀清累计造成100000点伤害&gt; 3星通关别传BI-6；必须编入非助战蚀清并上场，且至少使用2次传导蚀滞弹</t>
+          <t>&gt; 完成5次战斗；必须编入非助战野鬃，并确定第一位部署的干员是野鬃&gt; 3星通关别传MN-2；必须编入非助战野鬃并上场，其他成员不可编入先锋干员</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="16" t="inlineStr">
         <is>
-          <t>焰尾</t>
+          <t>蚀清</t>
         </is>
       </c>
       <c r="B224" s="16" t="inlineStr">
         <is>
-          <t>NL-5</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C224" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>maa://28187 (97.44), maa://43531 (100.0), maa://39520 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战焰尾并上场，且每次战斗至少释放2次焰心&gt; 3星通关别传NL-5；必须编入非助战焰尾，且第一位部署焰尾、焰尾全程不撤退或被击倒</t>
+          <t>&gt; 由非助战蚀清累计造成100000点伤害&gt; 3星通关别传BI-6；必须编入非助战蚀清并上场，且至少使用2次传导蚀滞弹</t>
         </is>
       </c>
     </row>
@@ -6913,49 +6913,49 @@
       </c>
       <c r="B225" s="16" t="inlineStr">
         <is>
-          <t>NL-3</t>
+          <t>NL-5</t>
         </is>
       </c>
       <c r="C225" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
         <is>
-          <t>maa://20985 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战焰尾累计造成40000点伤害&gt; 3星通关别传NL-3；必须编入非助战焰尾并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战焰尾并上场，且每次战斗至少释放2次焰心&gt; 3星通关别传NL-5；必须编入非助战焰尾，且第一位部署焰尾、焰尾全程不撤退或被击倒</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="16" t="inlineStr">
         <is>
-          <t>耀骑士临光</t>
+          <t>焰尾</t>
         </is>
       </c>
       <c r="B226" s="16" t="inlineStr">
         <is>
-          <t>MN-8</t>
+          <t>NL-3</t>
         </is>
       </c>
       <c r="C226" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>maa://20987 (93.1), *maa://35801 (77.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战耀骑士临光累计造成100歼灭数&gt; 3星通关别传MN-8；必须编入非助战耀骑士临光并上场，且使用耀骑士临光歼灭至少1个腐败骑士或凋零骑士</t>
+          <t>&gt; 由非助战焰尾累计造成40000点伤害&gt; 3星通关别传NL-3；必须编入非助战焰尾并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
@@ -6967,103 +6967,103 @@
       </c>
       <c r="B227" s="16" t="inlineStr">
         <is>
-          <t>NL-10</t>
+          <t>MN-8</t>
         </is>
       </c>
       <c r="C227" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>*maa://29644 (73.33), maa://39159 (96.3), ***maa://30061 (30.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战耀骑士临光并上场，且每次战斗至少释放1次耀阳颔首&gt; 3星通关别传NL-10；必须编入非助战耀骑士临光并上场，且使用耀骑士临光击败血骑士狄开俄波利斯</t>
+          <t>&gt; 由非助战耀骑士临光累计造成100歼灭数&gt; 3星通关别传MN-8；必须编入非助战耀骑士临光并上场，且使用耀骑士临光歼灭至少1个腐败骑士或凋零骑士</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="16" t="inlineStr">
         <is>
-          <t>耶拉</t>
+          <t>耀骑士临光</t>
         </is>
       </c>
       <c r="B228" s="16" t="inlineStr">
         <is>
-          <t>BI-7</t>
+          <t>NL-10</t>
         </is>
       </c>
       <c r="C228" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>maa://30677 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战耶拉累计造成80000点伤害&gt; 3星通关别传BI-7；必须编入非助战耶拉并上场，且至少使用2次心随意动</t>
+          <t>&gt; 完成5次战斗；必须编入非助战耀骑士临光并上场，且每次战斗至少释放1次耀阳颔首&gt; 3星通关别传NL-10；必须编入非助战耀骑士临光并上场，且使用耀骑士临光击败血骑士狄开俄波利斯</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="16" t="inlineStr">
         <is>
-          <t>极光</t>
+          <t>耶拉</t>
         </is>
       </c>
       <c r="B229" s="16" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>BI-7</t>
         </is>
       </c>
       <c r="C229" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>maa://20896 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战极光累计造成40000点伤害&gt; 3星通关主题曲3-8；必须编入非助战极光并上场，且使用极光歼灭碎骨</t>
+          <t>&gt; 由非助战耶拉累计造成80000点伤害&gt; 3星通关别传BI-7；必须编入非助战耶拉并上场，且至少使用2次心随意动</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="16" t="inlineStr">
         <is>
-          <t>灵知</t>
+          <t>极光</t>
         </is>
       </c>
       <c r="B230" s="16" t="inlineStr">
         <is>
-          <t>BI-7</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C230" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>maa://29058 (95.83), maa://39140 (100.0), maa://38723 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战灵知并上场，且每次战斗至少释放1次失温症&gt; 3星通关别传BI-7，必须编入非助战灵知并上场，且不编入其他辅助干员</t>
+          <t>&gt; 由非助战极光累计造成40000点伤害&gt; 3星通关主题曲3-8；必须编入非助战极光并上场，且使用极光歼灭碎骨</t>
         </is>
       </c>
     </row>
@@ -7075,110 +7075,110 @@
       </c>
       <c r="B231" s="16" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>BI-7</t>
         </is>
       </c>
       <c r="C231" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>*maa://48263 (71.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战灵知累计使用10次失温症&gt; 3星通关主题曲5-6；必须编入非助战灵知并上场，且使用灵知击败至少5个法术大师A1</t>
+          <t>&gt; 完成5次战斗；必须编入非助战灵知并上场，且每次战斗至少释放1次失温症&gt; 3星通关别传BI-7，必须编入非助战灵知并上场，且不编入其他辅助干员</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="16" t="inlineStr">
         <is>
-          <t>九色鹿</t>
+          <t>灵知</t>
         </is>
       </c>
       <c r="B232" s="16" t="inlineStr">
         <is>
-          <t>IW-3</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C232" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>maa://39160 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战九色鹿累计使用仙山去远8次&gt; 3星通关别传IW-3；必须编入非助战九色鹿并上场，且不编入其他辅助干员</t>
+          <t>&gt; 战斗中非助战灵知累计使用10次失温症&gt; 3星通关主题曲5-6；必须编入非助战灵知并上场，且使用灵知击败至少5个法术大师A1</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="16" t="inlineStr">
         <is>
-          <t>寒芒克洛丝</t>
+          <t>九色鹿</t>
         </is>
       </c>
       <c r="B233" s="16" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>IW-3</t>
         </is>
       </c>
       <c r="C233" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>maa://49491 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战寒芒克洛丝累计使用封喉5次&gt; 3星通关主题曲3-8；必须编入非助战寒芒克洛丝并上场，且使用寒芒克洛丝歼灭碎骨</t>
+          <t>&gt; 战斗中非助战九色鹿累计使用仙山去远8次&gt; 3星通关别传IW-3；必须编入非助战九色鹿并上场，且不编入其他辅助干员</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="16" t="inlineStr">
         <is>
-          <t>夜半</t>
+          <t>寒芒克洛丝</t>
         </is>
       </c>
       <c r="B234" s="16" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C234" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>maa://35952 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战夜半累计使用安眠10次&gt; 3星通关主题曲3-1；必须编入非助战夜半并上场，且至少使用3次安眠</t>
+          <t>&gt; 战斗中非助战寒芒克洛丝累计使用封喉5次&gt; 3星通关主题曲3-8；必须编入非助战寒芒克洛丝并上场，且使用寒芒克洛丝歼灭碎骨</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="16" t="inlineStr">
         <is>
-          <t>老鲤</t>
+          <t>夜半</t>
         </is>
       </c>
       <c r="B235" s="16" t="inlineStr">
@@ -7188,17 +7188,17 @@
       </c>
       <c r="C235" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>maa://20917 (98.21)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战老鲤累计造成80歼灭数&gt; 3星通关主题曲3-1；必须编入非助战老鲤并上场，其他成员仅可编入狙击、先锋与医疗干员</t>
+          <t>&gt; 战斗中非助战夜半累计使用安眠10次&gt; 3星通关主题曲3-1；必须编入非助战夜半并上场，且至少使用3次安眠</t>
         </is>
       </c>
     </row>
@@ -7210,184 +7210,184 @@
       </c>
       <c r="B236" s="16" t="inlineStr">
         <is>
-          <t>IW-EX-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C236" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>maa://30714 (97.5), maa://30675 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战老鲤并上场，且每次战斗至少释放1次贵客盈门&gt; 3星通关别传IW-EX-1；必须编入非助战老鲤并上场，且使用老鲤至少歼灭10个敌人</t>
+          <t>&gt; 由非助战老鲤累计造成80歼灭数&gt; 3星通关主题曲3-1；必须编入非助战老鲤并上场，其他成员仅可编入狙击、先锋与医疗干员</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="16" t="inlineStr">
         <is>
-          <t>令</t>
+          <t>老鲤</t>
         </is>
       </c>
       <c r="B237" s="16" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>IW-EX-1</t>
         </is>
       </c>
       <c r="C237" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D237" s="14" t="inlineStr">
         <is>
-          <t>maa://20922 (94.03), *maa://32623 (75.0), maa://34242 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战令并上场，且使用令与令的召唤物歼灭至少7名敌人&gt; 3星通关主题曲3-4；必须编入非助战令并上场，且整场战斗仅部署过令与至多4位其他干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战老鲤并上场，且每次战斗至少释放1次贵客盈门&gt; 3星通关别传IW-EX-1；必须编入非助战老鲤并上场，且使用老鲤至少歼灭10个敌人</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="16" t="inlineStr">
         <is>
-          <t>夏栎</t>
+          <t>令</t>
         </is>
       </c>
       <c r="B238" s="16" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C238" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>maa://32999 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战夏栎累计使用生灵的回响8次&gt; 3星通关主题曲9-2标准实战环境；必须编入非助战夏栎并上场，且不编入其他医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战令并上场，且使用令与令的召唤物歼灭至少7名敌人&gt; 3星通关主题曲3-4；必须编入非助战令并上场，且整场战斗仅部署过令与至多4位其他干员</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="16" t="inlineStr">
         <is>
-          <t>澄闪</t>
+          <t>夏栎</t>
         </is>
       </c>
       <c r="B239" s="16" t="inlineStr">
         <is>
-          <t>R8-8</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C239" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>*maa://30667 (78.21), maa://30666 (83.33), **maa://30739 (43.24), *maa://30723 (55.74), maa://39588 (88.24)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战澄闪累计造成100000点伤害&gt; 3星通关主题曲R8-8；必须编入非助战澄闪并上场，且使用澄闪歼灭至少2名帝国炮火先兆者</t>
+          <t>&gt; 战斗中非助战夏栎累计使用生灵的回响8次&gt; 3星通关主题曲9-2标准实战环境；必须编入非助战夏栎并上场，且不编入其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="16" t="inlineStr">
         <is>
-          <t>见行者</t>
+          <t>澄闪</t>
         </is>
       </c>
       <c r="B240" s="16" t="inlineStr">
         <is>
-          <t>GA-EX-1</t>
+          <t>R8-8</t>
         </is>
       </c>
       <c r="C240" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>maa://30512 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战见行者并上场，且每次战斗至少释放2次惊爆射击&gt; 3星通关别传GA-EX-1；必须编入非助战见行者，且本场战斗至少使3个寻路者精锐狙击手坠落地穴</t>
+          <t>&gt; 由非助战澄闪累计造成100000点伤害&gt; 3星通关主题曲R8-8；必须编入非助战澄闪并上场，且使用澄闪歼灭至少2名帝国炮火先兆者</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="16" t="inlineStr">
         <is>
-          <t>风丸</t>
+          <t>见行者</t>
         </is>
       </c>
       <c r="B241" s="16" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>GA-EX-1</t>
         </is>
       </c>
       <c r="C241" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>maa://20870 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战风丸累计使用纸艺·双影10次&gt; 3星通关主题曲3-1；必须编入非助战风丸并上场，且使用风丸歼灭至少30名敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战见行者并上场，且每次战斗至少释放2次惊爆射击&gt; 3星通关别传GA-EX-1；必须编入非助战见行者，且本场战斗至少使3个寻路者精锐狙击手坠落地穴</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="16" t="inlineStr">
         <is>
-          <t>菲亚梅塔</t>
+          <t>风丸</t>
         </is>
       </c>
       <c r="B242" s="16" t="inlineStr">
         <is>
-          <t>GA-4</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C242" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>maa://29024 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战菲亚梅塔并上场，且使用菲亚梅塔歼灭至少10个敌人&gt; 3星通关别传GA-4；必须编入非助战菲亚梅塔并上场，且队伍中不能有其他狙击干员</t>
+          <t>&gt; 由非助战风丸累计使用纸艺·双影10次&gt; 3星通关主题曲3-1；必须编入非助战风丸并上场，且使用风丸歼灭至少30名敌人</t>
         </is>
       </c>
     </row>
@@ -7399,130 +7399,130 @@
       </c>
       <c r="B243" s="16" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>GA-4</t>
         </is>
       </c>
       <c r="C243" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>maa://20867 (93.33), maa://38485 (95.45), *maa://32202 (80.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战菲亚梅塔累计造成180000点伤害&gt; 3星通关主题曲S5-9；必须编入非助战菲亚梅塔并上场，且使用菲亚梅塔造成至少60000点伤害</t>
+          <t>&gt; 完成5次战斗；必须编入非助战菲亚梅塔并上场，且使用菲亚梅塔歼灭至少10个敌人&gt; 3星通关别传GA-4；必须编入非助战菲亚梅塔并上场，且队伍中不能有其他狙击干员</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="16" t="inlineStr">
         <is>
-          <t>褐果</t>
+          <t>菲亚梅塔</t>
         </is>
       </c>
       <c r="B244" s="16" t="inlineStr">
         <is>
-          <t>SV-3</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C244" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>maa://40160 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战褐果并上场，且每次战斗至少释放1次厚土迸发&gt; 3星通关插曲SV-3；必须编入非助战褐果并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战菲亚梅塔累计造成180000点伤害&gt; 3星通关主题曲S5-9；必须编入非助战菲亚梅塔并上场，且使用菲亚梅塔造成至少60000点伤害</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="16" t="inlineStr">
         <is>
-          <t>海蒂</t>
+          <t>褐果</t>
         </is>
       </c>
       <c r="B245" s="16" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>SV-3</t>
         </is>
       </c>
       <c r="C245" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
         <is>
-          <t>maa://43089 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战海蒂累计使用8次“虚构故事·怒士”&gt; 3星通关主题曲9-7标准实战环境；必须编入非助战海蒂并上场，且海蒂使用至少3次“虚构故事·锈城”</t>
+          <t>&gt; 完成5次战斗；必须编入非助战褐果并上场，且每次战斗至少释放1次厚土迸发&gt; 3星通关插曲SV-3；必须编入非助战褐果并上场，且不编入其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="16" t="inlineStr">
         <is>
-          <t>洛洛</t>
+          <t>海蒂</t>
         </is>
       </c>
       <c r="B246" s="16" t="inlineStr">
         <is>
-          <t>RI-EX-4</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C246" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>maa://30674 (88.89)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战洛洛累计使用自负此轭10次&gt; 3星通关别传RI-EX-4；必须编入非助战洛洛并上场，且使用洛洛歼灭至少2名提亚卡乌冠军</t>
+          <t>&gt; 战斗中非助战海蒂累计使用8次“虚构故事·怒士”&gt; 3星通关主题曲9-7标准实战环境；必须编入非助战海蒂并上场，且海蒂使用至少3次“虚构故事·锈城”</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="16" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>洛洛</t>
         </is>
       </c>
       <c r="B247" s="16" t="inlineStr">
         <is>
-          <t>7-15</t>
+          <t>RI-EX-4</t>
         </is>
       </c>
       <c r="C247" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>maa://28923 (92.06), maa://28906 (98.28), ***maa://28825 (11.54)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战号角累计使用终极防线10次&gt; 3星通关主题曲7-15；必须编入非助战号角并上场，且使用号角至少歼灭10个敌人</t>
+          <t>&gt; 战斗中非助战洛洛累计使用自负此轭10次&gt; 3星通关别传RI-EX-4；必须编入非助战洛洛并上场，且使用洛洛歼灭至少2名提亚卡乌冠军</t>
         </is>
       </c>
     </row>
@@ -7534,76 +7534,76 @@
       </c>
       <c r="B248" s="16" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>7-15</t>
         </is>
       </c>
       <c r="C248" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>maa://42287 (89.74), maa://45570 (97.62), maa://42225 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战号角累计造成100000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战号角并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中非助战号角累计使用终极防线10次&gt; 3星通关主题曲7-15；必须编入非助战号角并上场，且使用号角至少歼灭10个敌人</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="16" t="inlineStr">
         <is>
-          <t>掠风</t>
+          <t>号角</t>
         </is>
       </c>
       <c r="B249" s="16" t="inlineStr">
         <is>
-          <t>11-9</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C249" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>maa://39161 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战掠风累计使用此身为源10次&gt; 3星通关主题曲11-9标准实战环境；必须编入非助战掠风并上场，其他成员仅可编入术师、重装与医疗干员</t>
+          <t>&gt; 由非助战号角累计造成100000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战号角并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="16" t="inlineStr">
         <is>
-          <t>流明</t>
+          <t>掠风</t>
         </is>
       </c>
       <c r="B250" s="16" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>11-9</t>
         </is>
       </c>
       <c r="C250" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>maa://20923 (92.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战流明并上场，且每次战斗至少释放2次灯火不灭&gt; 3星通关主题曲6-9；且仅可编入非助战流明1名医疗干员并上场</t>
+          <t>&gt; 战斗中非助战掠风累计使用此身为源10次&gt; 3星通关主题曲11-9标准实战环境；必须编入非助战掠风并上场，其他成员仅可编入术师、重装与医疗干员</t>
         </is>
       </c>
     </row>
@@ -7615,49 +7615,49 @@
       </c>
       <c r="B251" s="16" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="C251" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>maa://24093 (100.0), maa://31559 (97.06), maa://20924 (95.24), *maa://49440 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战流明累计使用沛霖10次&gt; 3星通关别传OF-5；必须编入非助战流明并上场，且不编入其他医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战流明并上场，且每次战斗至少释放2次灯火不灭&gt; 3星通关主题曲6-9；且仅可编入非助战流明1名医疗干员并上场</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="16" t="inlineStr">
         <is>
-          <t>艾丽妮</t>
+          <t>流明</t>
         </is>
       </c>
       <c r="B252" s="16" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C252" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>maa://40958 (88.0), *maa://45067 (71.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战艾丽妮累计造成100000点伤害&gt; 3星通关插曲SV-EX-1；必须编入非助战艾丽妮并上场，且使用2次判决</t>
+          <t>&gt; 战斗中非助战流明累计使用沛霖10次&gt; 3星通关别传OF-5；必须编入非助战流明并上场，且不编入其他医疗干员</t>
         </is>
       </c>
     </row>
@@ -7669,49 +7669,49 @@
       </c>
       <c r="B253" s="16" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C253" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>maa://20840 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战艾丽妮使用技能累计造成50歼灭数&gt; 3星通关插曲SV-4；必须编入非助战艾丽妮并上场，且使用艾丽妮歼灭15个敌人</t>
+          <t>&gt; 由非助战艾丽妮累计造成100000点伤害&gt; 3星通关插曲SV-EX-1；必须编入非助战艾丽妮并上场，且使用2次判决</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="16" t="inlineStr">
         <is>
-          <t>归溟幽灵鲨</t>
+          <t>艾丽妮</t>
         </is>
       </c>
       <c r="B254" s="16" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C254" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>maa://20877 (98.63), *maa://45067 (71.43), maa://20836 (100.0), maa://20632 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战归溟幽灵鲨累计造成30歼灭数&gt; 3星通关插曲SV-EX-1；必须编入非助战归溟幽灵鲨并上场，且使用归溟幽灵鲨歼灭至少1个囊海爬行者</t>
+          <t>&gt; 由非助战艾丽妮使用技能累计造成50歼灭数&gt; 3星通关插曲SV-4；必须编入非助战艾丽妮并上场，且使用艾丽妮歼灭15个敌人</t>
         </is>
       </c>
     </row>
@@ -7723,103 +7723,103 @@
       </c>
       <c r="B255" s="16" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C255" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>maa://20879 (87.34), maa://20834 (92.86)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战归溟幽灵鲨并上场，且每次战斗至少释放1次生存的重压&gt; 3星通关主题曲S4-1；必须编入非助战归溟幽灵鲨并上场，且使用归溟幽灵鲨歼灭10个敌人</t>
+          <t>&gt; 由非助战归溟幽灵鲨累计造成30歼灭数&gt; 3星通关插曲SV-EX-1；必须编入非助战归溟幽灵鲨并上场，且使用归溟幽灵鲨歼灭至少1个囊海爬行者</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="16" t="inlineStr">
         <is>
-          <t>埃拉托</t>
+          <t>归溟幽灵鲨</t>
         </is>
       </c>
       <c r="B256" s="16" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>S4-1</t>
         </is>
       </c>
       <c r="C256" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>maa://20839 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战埃拉托累计使用英雄赞歌5次&gt; 3星通关主题曲S5-9；必须编入非助战埃拉托并上场，其他成员不可编入狙击干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战归溟幽灵鲨并上场，且每次战斗至少释放1次生存的重压&gt; 3星通关主题曲S4-1；必须编入非助战归溟幽灵鲨并上场，且使用归溟幽灵鲨歼灭10个敌人</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="16" t="inlineStr">
         <is>
-          <t>濯尘芙蓉</t>
+          <t>埃拉托</t>
         </is>
       </c>
       <c r="B257" s="16" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C257" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>maa://30676 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战濯尘芙蓉累计使用抚业之触10次&gt; 3星通关别传LE-4；必须编入非助战濯尘芙蓉并上场，且至少使用2次抚业之触</t>
+          <t>&gt; 战斗中非助战埃拉托累计使用英雄赞歌5次&gt; 3星通关主题曲S5-9；必须编入非助战埃拉托并上场，其他成员不可编入狙击干员</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="16" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>濯尘芙蓉</t>
         </is>
       </c>
       <c r="B258" s="16" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C258" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>maa://31560 (87.5), maa://20884 (95.45)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战黑键累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲3-7；必须编入非助战黑键并上场，且使用黑键歼灭至少1个重装防御组长</t>
+          <t>&gt; 战斗中非助战濯尘芙蓉累计使用抚业之触10次&gt; 3星通关别传LE-4；必须编入非助战濯尘芙蓉并上场，且至少使用2次抚业之触</t>
         </is>
       </c>
     </row>
@@ -7831,22 +7831,22 @@
       </c>
       <c r="B259" s="16" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C259" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>maa://47204 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战黑键并上场，且使用黑键歼灭至少6个敌人&gt; 3星通关主题曲3-6；必须编入非助战黑键并上场，且使用黑键歼灭屠宰老手</t>
+          <t>&gt; 由非助战黑键累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲3-7；必须编入非助战黑键并上场，且使用黑键歼灭至少1个重装防御组长</t>
         </is>
       </c>
     </row>
@@ -7858,1325 +7858,1325 @@
       </c>
       <c r="B260" s="16" t="inlineStr">
         <is>
-          <t>11-12</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C260" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>maa://29027 (97.96)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战黑键累计使用寂静之声10次&gt; 3星通关主题曲11-12标准实战环境；必须编入非助战黑键并上场，且使用黑键歼灭至少2名伦蒂尼姆城防自行炮</t>
+          <t>&gt; 完成5次战斗；必须编入非助战黑键并上场，且使用黑键歼灭至少6个敌人&gt; 3星通关主题曲3-6；必须编入非助战黑键并上场，且使用黑键歼灭屠宰老手</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="16" t="inlineStr">
         <is>
-          <t>星源</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B261" s="16" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="C261" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>maa://20977 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战星源累计造成40歼灭数&gt; 3星通关主题曲4-3；必须编入非助战星源并上场，其他成员仅可编入重装干员</t>
+          <t>&gt; 战斗中非助战黑键累计使用寂静之声10次&gt; 3星通关主题曲11-12标准实战环境；必须编入非助战黑键并上场，且使用黑键歼灭至少2名伦蒂尼姆城防自行炮</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="16" t="inlineStr">
         <is>
-          <t>承曦格雷伊</t>
+          <t>星源</t>
         </is>
       </c>
       <c r="B262" s="16" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C262" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>maa://39162 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战承曦格雷伊累计使用晨曦信标10次&gt; 3星通关主题曲1-3；必须编入非助战承曦格雷伊并上场，其他成员仅可编入先锋干员</t>
+          <t>&gt; 由非助战星源累计造成40歼灭数&gt; 3星通关主题曲4-3；必须编入非助战星源并上场，其他成员仅可编入重装干员</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="16" t="inlineStr">
         <is>
+          <t>承曦格雷伊</t>
+        </is>
+      </c>
+      <c r="B263" s="16" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="C263" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D263" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中非助战承曦格雷伊累计使用晨曦信标10次&gt; 3星通关主题曲1-3；必须编入非助战承曦格雷伊并上场，其他成员仅可编入先锋干员</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="16" t="inlineStr">
+        <is>
           <t>多萝西</t>
         </is>
       </c>
-      <c r="B263" s="16" t="inlineStr">
-        <is>
-          <t>4-5</t>
-        </is>
-      </c>
-      <c r="C263" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D263" s="12" t="inlineStr">
-        <is>
-          <t>maa://22467 (95.24)</t>
-        </is>
-      </c>
-      <c r="E263" s="3" t="inlineStr">
-        <is>
-          <t>&gt; 战斗中非助战多萝西累计部署共振装置50个&gt; 3星通关主题曲4-5；必须编入非助战多萝西并上场，其他成员仅可编入3名干员</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="17" t="inlineStr">
-        <is>
-          <t>至简</t>
-        </is>
-      </c>
-      <c r="B264" s="17" t="inlineStr">
-        <is>
-          <t>IC-8</t>
-        </is>
-      </c>
-      <c r="C264" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D264" s="19" t="inlineStr">
-        <is>
-          <t>**maa://30678 (37.5)</t>
-        </is>
-      </c>
-      <c r="E264" s="20" t="inlineStr">
-        <is>
-          <t>&gt; 战斗中非助战至简累计使用神工意匠20次&gt; 3星通关别传IC-8；必须编入非助战至简并上场，且使用至简歼灭至少2名蜜酿级醒酒助手</t>
+      <c r="B264" s="16" t="inlineStr">
+        <is>
+          <t>MB-EX-1</t>
+        </is>
+      </c>
+      <c r="C264" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D264" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>&gt; 由非助战多萝西累计造成120000点伤害&gt; 3星通关插曲MB-EX-1，必须编入非助战多萝西并上场，其他成员仅可编入近卫干员</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="16" t="inlineStr">
         <is>
-          <t>晓歌</t>
+          <t>多萝西</t>
         </is>
       </c>
       <c r="B265" s="16" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C265" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>maa://49643 (90.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计部署非助战晓歌12次&gt; 3星通关主题曲5-3；必须编入非助战晓歌并上场，且使用晓歌歼灭至少3个特战术师或特战术师组长</t>
+          <t>&gt; 战斗中非助战多萝西累计部署共振装置50个&gt; 3星通关主题曲4-5；必须编入非助战多萝西并上场，其他成员仅可编入3名干员</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="16" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>至简</t>
         </is>
       </c>
       <c r="B266" s="16" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>IC-8</t>
         </is>
       </c>
       <c r="C266" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>maa://48265 (84.62)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战鸿雪并上场，且每次战斗至少释放1次锐笔速写&gt; 3星通关主题曲9-7标准实战环境，必须编入非助战鸿雪并上场，且使用鸿雪歼灭至少10名敌人，其中包括至少1个深池重甲卫士</t>
+          <t>&gt; 战斗中非助战至简累计使用神工意匠20次&gt; 3星通关别传IC-8；必须编入非助战至简并上场，且使用至简歼灭至少2名蜜酿级醒酒助手</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="16" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>晓歌</t>
         </is>
       </c>
       <c r="B267" s="16" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C267" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>*maa://20825 (71.43), *maa://21445 (70.59), *maa://35726 (63.64), ***maa://20891 (30.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计部署非助战鸿雪的“打字机”10次&gt; 3星通关主题曲2-10；必须编入非助战鸿雪并上场，且使用鸿雪或“打字机”歼灭碎骨</t>
+          <t>&gt; 战斗中累计部署非助战晓歌12次&gt; 3星通关主题曲5-3；必须编入非助战晓歌并上场，且使用晓歌歼灭至少3个特战术师或特战术师组长</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="16" t="inlineStr">
         <is>
-          <t>百炼嘉维尔</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B268" s="16" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C268" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>maa://25769 (97.35)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战百炼嘉维尔累计使用链锯强袭10次&gt; 3星通关主题曲9-2标准实战环境；必须编入非助战百炼嘉维尔并上场，且使用百炼嘉维尔至少歼灭15个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战鸿雪并上场，且每次战斗至少释放1次锐笔速写&gt; 3星通关主题曲9-7标准实战环境，必须编入非助战鸿雪并上场，且使用鸿雪歼灭至少10名敌人，其中包括至少1个深池重甲卫士</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="16" t="inlineStr">
         <is>
-          <t>但书</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B269" s="16" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C269" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>maa://20862 (83.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战但书累计使用致胜立论14次&gt; 3星通关主题曲4-7；必须编入非助战但书并上场，且使用但书至少歼灭3只高能源石虫</t>
+          <t>&gt; 战斗中累计部署非助战鸿雪的“打字机”10次&gt; 3星通关主题曲2-10；必须编入非助战鸿雪并上场，且使用鸿雪或“打字机”歼灭碎骨</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="16" t="inlineStr">
         <is>
-          <t>玛恩纳</t>
+          <t>百炼嘉维尔</t>
         </is>
       </c>
       <c r="B270" s="16" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C270" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D270" s="12" t="inlineStr">
         <is>
-          <t>maa://51881 (99.23), maa://51630 (96.39), maa://51893 (87.5), *maa://55171 (64.29), maa://56588 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战玛恩纳累计造成120000点伤害&gt; 3星通关主题曲11-15标准实战环境；必须编入非助战玛恩纳并上场，且使用2次未照耀的荣光</t>
+          <t>&gt; 战斗中非助战百炼嘉维尔累计使用链锯强袭10次&gt; 3星通关主题曲9-2标准实战环境；必须编入非助战百炼嘉维尔并上场，且使用百炼嘉维尔至少歼灭15个敌人</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="16" t="inlineStr">
         <is>
-          <t>罗小黑</t>
+          <t>但书</t>
         </is>
       </c>
       <c r="B271" s="16" t="inlineStr">
         <is>
-          <t>IW-4</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C271" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>maa://39163 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战罗小黑并上场，且每次战斗至少释放1次碎金为刃&gt; 3星通关别传IW-4；必须编入非助战罗小黑并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 战斗中非助战但书累计使用致胜立论14次&gt; 3星通关主题曲4-7；必须编入非助战但书并上场，且使用但书至少歼灭3只高能源石虫</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="16" t="inlineStr">
         <is>
-          <t>海沫</t>
+          <t>玛恩纳</t>
         </is>
       </c>
       <c r="B272" s="16" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C272" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>maa://29061 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战海沫并上场，且使用海沫造成至少12000点伤害&gt; 3星通关插曲SN-2；必须携带并部署非助战海沫，其他成员仅可编入2名干员</t>
+          <t>&gt; 使用非助战玛恩纳累计造成120000点伤害&gt; 3星通关主题曲11-15标准实战环境；必须编入非助战玛恩纳并上场，且使用2次未照耀的荣光</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="16" t="inlineStr">
         <is>
-          <t>铅踝</t>
+          <t>罗小黑</t>
         </is>
       </c>
       <c r="B273" s="16" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>IW-4</t>
         </is>
       </c>
       <c r="C273" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>maa://20939 (81.82)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战铅踝累计造成30歼灭数&gt; 3星通关主题曲S3-5；必须编入非助战铅踝并上场，且使用铅踝歼灭至少2个隐形弩手</t>
+          <t>&gt; 完成5次战斗；必须编入非助战罗小黑并上场，且每次战斗至少释放1次碎金为刃&gt; 3星通关别传IW-4；必须编入非助战罗小黑并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="16" t="inlineStr">
         <is>
-          <t>达格达</t>
+          <t>海沫</t>
         </is>
       </c>
       <c r="B274" s="16" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C274" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D274" s="12" t="inlineStr">
         <is>
-          <t>maa://39164 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战达格达累计造成30歼灭数&gt; 3星通关主题曲11-5标准实战环境；必须编入非助战达格达并上场，且使用达格达至少歼灭10个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战海沫并上场，且使用海沫造成至少12000点伤害&gt; 3星通关插曲SN-2；必须携带并部署非助战海沫，其他成员仅可编入2名干员</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="16" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>铅踝</t>
         </is>
       </c>
       <c r="B275" s="16" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C275" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>maa://28133 (92.45), maa://33394 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战白铁累计部署支援装置25个&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战白铁并上场，且使用白铁或白铁的支援装置歼灭至少15名萨卡兹枯朽战士</t>
+          <t>&gt; 由非助战铅踝累计造成30歼灭数&gt; 3星通关主题曲S3-5；必须编入非助战铅踝并上场，且使用铅踝歼灭至少2个隐形弩手</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="16" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>达格达</t>
         </is>
       </c>
       <c r="B276" s="16" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="C276" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>maa://42311 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战白铁累计使用8次“铁钳号·原型机”&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战白铁并上场，且使用白铁至少歼灭10个敌人</t>
+          <t>&gt; 由非助战达格达累计造成30歼灭数&gt; 3星通关主题曲11-5标准实战环境；必须编入非助战达格达并上场，且使用达格达至少歼灭10个敌人</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="16" t="inlineStr">
         <is>
-          <t>石英</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="B277" s="16" t="inlineStr">
         <is>
-          <t>DH-4</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C277" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>maa://41362 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成3次战斗；必须编入非助战石英并上场，且每次战斗至少释放1次全力相搏&gt; 3星通关别传DH-4；必须编入非助战石英并上场，并使用石英至少击败2名控潮术师</t>
+          <t>&gt; 战斗中非助战白铁累计部署支援装置25个&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战白铁并上场，且使用白铁或白铁的支援装置歼灭至少15名萨卡兹枯朽战士</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="16" t="inlineStr">
         <is>
-          <t>雪绒</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="B278" s="16" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C278" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D278" s="12" t="inlineStr">
         <is>
-          <t>maa://20978 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战雪绒累计使用坠雪10次&gt; 3星通关主题曲2-3；必须编入非助战雪绒并上场，且使用雪绒歼灭至少2名重装防御者</t>
+          <t>&gt; 战斗中非助战白铁累计使用8次“铁钳号·原型机”&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战白铁并上场，且使用白铁至少歼灭10个敌人</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="16" t="inlineStr">
         <is>
-          <t>子月</t>
+          <t>石英</t>
         </is>
       </c>
       <c r="B279" s="16" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>DH-4</t>
         </is>
       </c>
       <c r="C279" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>maa://21002 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战子月累计造成30歼灭数&gt; 3星通关主题曲2-5；必须编入非助战子月并上场，且使用子月歼灭至少2个高阶术师</t>
+          <t>&gt; 完成3次战斗；必须编入非助战石英并上场，且每次战斗至少释放1次全力相搏&gt; 3星通关别传DH-4；必须编入非助战石英并上场，并使用石英至少击败2名控潮术师</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="16" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>雪绒</t>
         </is>
       </c>
       <c r="B280" s="16" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C280" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>*maa://39165 (57.14)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战伺夜并上场，且每次战斗至少释放1次领袖的尊严&gt; 3星通关主题曲3-8；必须编入非助战伺夜并上场，且使用伺夜歼灭碎骨</t>
+          <t>&gt; 战斗中非助战雪绒累计使用坠雪10次&gt; 3星通关主题曲2-3；必须编入非助战雪绒并上场，且使用雪绒歼灭至少2名重装防御者</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="16" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>子月</t>
         </is>
       </c>
       <c r="B281" s="16" t="inlineStr">
         <is>
-          <t>IS-6</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C281" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>maa://48267 (100.0), maa://48266 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战伺夜，并确定第一位部署的干员是伺夜&gt; 3星通关别传IS-6；必须编入非助战伺夜并上场，且至少使用3次领袖的尊严</t>
+          <t>&gt; 由非助战子月累计造成30歼灭数&gt; 3星通关主题曲2-5；必须编入非助战子月并上场，且使用子月歼灭至少2个高阶术师</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="16" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B282" s="16" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C282" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>maa://29635 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战斥罪累计造成40歼灭数&gt; 3星通关别传CB-4；必须携带并部署非助战斥罪，其他成员仅可编入4名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战伺夜并上场，且每次战斗至少释放1次领袖的尊严&gt; 3星通关主题曲3-8；必须编入非助战伺夜并上场，且使用伺夜歼灭碎骨</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="16" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B283" s="16" t="inlineStr">
         <is>
-          <t>IS-7</t>
+          <t>IS-6</t>
         </is>
       </c>
       <c r="C283" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>maa://38296 (89.29)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战斥罪累计使用披荆斩棘5次&gt; 3星通关别传IS-7；必须编入非助战斥罪并上场，且不编入其他医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战伺夜，并确定第一位部署的干员是伺夜&gt; 3星通关别传IS-6；必须编入非助战伺夜并上场，且至少使用3次领袖的尊严</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="16" t="inlineStr">
         <is>
-          <t>缄默德克萨斯</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B284" s="16" t="inlineStr">
         <is>
-          <t>CB-8</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C284" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D284" s="12" t="inlineStr">
         <is>
-          <t>maa://20899 (89.29), maa://46332 (93.33), ***maa://44744 (25.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战缄默德克萨斯累计歼灭10个精英或领袖敌人&gt; 3星通关别传CB-8；必须编入非助战缄默德克萨斯并上场，且使用缄默德克萨斯歼灭至少2个灰尾</t>
+          <t>&gt; 由非助战斥罪累计造成40歼灭数&gt; 3星通关别传CB-4；必须携带并部署非助战斥罪，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="16" t="inlineStr">
         <is>
-          <t>谜图</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B285" s="16" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>IS-7</t>
         </is>
       </c>
       <c r="C285" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>maa://53353 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战谜图并上场，且使用谜图歼灭至少3个敌人&gt; 3星通关主题曲9-4标准实战环境；必须编入非助战谜图并上场，其他成员不可编入先锋干员</t>
+          <t>&gt; 战斗中非助战斥罪累计使用披荆斩棘5次&gt; 3星通关别传IS-7；必须编入非助战斥罪并上场，且不编入其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="16" t="inlineStr">
         <is>
-          <t>和弦</t>
+          <t>缄默德克萨斯</t>
         </is>
       </c>
       <c r="B286" s="16" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>CB-8</t>
         </is>
       </c>
       <c r="C286" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D286" s="12" t="inlineStr">
         <is>
-          <t>maa://20881 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战和弦并上场，且每次战斗至少释放一次沉溺之灾&gt; 3星通关主题曲6-5；必须编入非助战和弦并上场，且使用和弦歼灭至少2个宿主重装士兵</t>
+          <t>&gt; 由非助战缄默德克萨斯累计歼灭10个精英或领袖敌人&gt; 3星通关别传CB-8；必须编入非助战缄默德克萨斯并上场，且使用缄默德克萨斯歼灭至少2个灰尾</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="16" t="inlineStr">
         <is>
-          <t>焰影苇草</t>
+          <t>谜图</t>
         </is>
       </c>
       <c r="B287" s="16" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C287" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>maa://30710 (97.83), maa://36845 (95.45), maa://31558 (97.06), **maa://39217 (41.18), maa://30668 (86.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战焰影苇草累计使用枯荣共息10次&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战焰影苇草并上场，且使用焰影苇草至少歼灭40个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战谜图并上场，且使用谜图歼灭至少3个敌人&gt; 3星通关主题曲9-4标准实战环境；必须编入非助战谜图并上场，其他成员不可编入先锋干员</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="16" t="inlineStr">
         <is>
-          <t>截云</t>
+          <t>和弦</t>
         </is>
       </c>
       <c r="B288" s="16" t="inlineStr">
         <is>
-          <t>S2-2</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C288" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D288" s="12" t="inlineStr">
         <is>
-          <t>maa://20902 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战截云累计造成100000点伤害&gt; 3星通关主题曲S2-2；必须编入非助战截云并上场，且使用截云至少歼灭10名敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战和弦并上场，且每次战斗至少释放一次沉溺之灾&gt; 3星通关主题曲6-5；必须编入非助战和弦并上场，且使用和弦歼灭至少2个宿主重装士兵</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="16" t="inlineStr">
         <is>
-          <t>火哨</t>
+          <t>焰影苇草</t>
         </is>
       </c>
       <c r="B289" s="16" t="inlineStr">
         <is>
-          <t>S4-6</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C289" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>maa://29159 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战火哨累计使用焦土8次&gt; 3星通关主题曲S4-6；必须携带并部署非助战火哨，其他成员仅可编入远程位干员</t>
+          <t>&gt; 战斗中非助战焰影苇草累计使用枯荣共息10次&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战焰影苇草并上场，且使用焰影苇草至少歼灭40个敌人</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="16" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>截云</t>
         </is>
       </c>
       <c r="B290" s="16" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C290" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D290" s="12" t="inlineStr">
         <is>
-          <t>maa://25774 (97.06), maa://28133 (92.45), maa://22469 (92.73), **maa://39217 (41.18), **maa://31349 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战林累计歼灭80个敌人&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战林并上场，且不编入重装干员</t>
+          <t>&gt; 由非助战截云累计造成100000点伤害&gt; 3星通关主题曲S2-2；必须编入非助战截云并上场，且使用截云至少歼灭10名敌人</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="16" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>火哨</t>
         </is>
       </c>
       <c r="B291" s="16" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>S4-6</t>
         </is>
       </c>
       <c r="C291" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
         <is>
-          <t>maa://47882 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战林并上场，且每次战斗至少释放1次流光乍裂&gt; 3星通关主题曲6-5；必须携带且部署非助战林，且至少释放3次流光乍裂</t>
+          <t>&gt; 战斗中非助战火哨累计使用焦土8次&gt; 3星通关主题曲S4-6；必须携带并部署非助战火哨，其他成员仅可编入远程位干员</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="16" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B292" s="16" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C292" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D292" s="12" t="inlineStr">
         <is>
-          <t>maa://32414 (98.77), maa://32505 (100.0), maa://39155 (97.3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战重岳累计造成120000点伤害&gt; 3星通关别传WB-7；必须携带并部署非助战重岳，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战林累计歼灭80个敌人&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战林并上场，且不编入重装干员</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="16" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B293" s="16" t="inlineStr">
         <is>
-          <t>GA-5</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C293" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>maa://45799 (100.0), maa://57199 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战重岳累计使用50次我无&gt; 3星通关别传GA-5；必须携带且部署非助战重岳，其他成员仅可编入4名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战林并上场，且每次战斗至少释放1次流光乍裂&gt; 3星通关主题曲6-5；必须携带且部署非助战林，且至少释放3次流光乍裂</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="16" t="inlineStr">
         <is>
-          <t>铎铃</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B294" s="16" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C294" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D294" s="12" t="inlineStr">
         <is>
-          <t>maa://42312 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战铎铃累计使用乡心无改6次&gt; 3星通关主题曲2-1；必须编入非助战铎铃并上场，且使用3次乡心无改</t>
+          <t>&gt; 由非助战重岳累计造成120000点伤害&gt; 3星通关别传WB-7；必须携带并部署非助战重岳，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="16" t="inlineStr">
         <is>
-          <t>仇白</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B295" s="16" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>GA-5</t>
         </is>
       </c>
       <c r="C295" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
         <is>
-          <t>maa://36642 (100.0), maa://36867 (97.06), maa://39155 (97.3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战仇白累计造成40歼灭数&gt; 3星通关别传WB-7；必须编入非助战仇白并上场，并使用仇白至少击败3名“破坚”</t>
+          <t>&gt; 使用非助战重岳累计使用50次我无&gt; 3星通关别传GA-5；必须携带且部署非助战重岳，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="16" t="inlineStr">
         <is>
-          <t>火龙S黑角</t>
+          <t>铎铃</t>
         </is>
       </c>
       <c r="B296" s="16" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C296" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D296" s="12" t="inlineStr">
         <is>
-          <t>**maa://39166 (50.0), maa://39167 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战火龙S黑角累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲3-8；必须编入非助战火龙S黑角并上场，且使用火龙S黑角歼灭碎骨</t>
+          <t>&gt; 战斗中非助战铎铃累计使用乡心无改6次&gt; 3星通关主题曲2-1；必须编入非助战铎铃并上场，且使用3次乡心无改</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="16" t="inlineStr">
         <is>
-          <t>麒麟R夜刀</t>
+          <t>仇白</t>
         </is>
       </c>
       <c r="B297" s="16" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C297" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>maa://29005 (98.68), maa://31560 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；每次战斗至少部署3次非助战的麒麟R夜刀&gt; 3星通关主题曲3-7；必须编入非助战麒麟R夜刀并上场，且使用麒麟R夜刀歼灭至少2名炮手</t>
+          <t>&gt; 由非助战仇白累计造成40歼灭数&gt; 3星通关别传WB-7；必须编入非助战仇白并上场，并使用仇白至少击败3名“破坚”</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="16" t="inlineStr">
         <is>
-          <t>休谟斯</t>
+          <t>火龙S黑角</t>
         </is>
       </c>
       <c r="B298" s="16" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C298" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D298" s="12" t="inlineStr">
         <is>
-          <t>maa://39168 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战休谟斯并上场，且每次战斗至少释放1次高效处理&gt; 3星通关主题曲7-8；必须编入非助战休谟斯并上场，其他成员仅可编入近战位干员</t>
+          <t>&gt; 由非助战火龙S黑角累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲3-8；必须编入非助战火龙S黑角并上场，且使用火龙S黑角歼灭碎骨</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="16" t="inlineStr">
         <is>
-          <t>摩根</t>
+          <t>麒麟R夜刀</t>
         </is>
       </c>
       <c r="B299" s="16" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C299" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>maa://39169 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战摩根累计造成80000点伤害&gt; 3星通关主题曲4-5，必须编入非助战摩根并上场，且使用摩根至少歼灭10名敌人</t>
+          <t>&gt; 完成5次战斗；每次战斗至少部署3次非助战的麒麟R夜刀&gt; 3星通关主题曲3-7；必须编入非助战麒麟R夜刀并上场，且使用麒麟R夜刀歼灭至少2名炮手</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="16" t="inlineStr">
         <is>
-          <t>洋灰</t>
+          <t>休谟斯</t>
         </is>
       </c>
       <c r="B300" s="16" t="inlineStr">
         <is>
-          <t>IW-EX-6</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C300" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D300" s="12" t="inlineStr">
         <is>
-          <t>maa://39170 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战洋灰并上场，且每次战斗至少释放1次结构加固&gt; 3星通关别传IW-EX-6，必须编入非助战洋灰并上场，且不编入其他重装干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战休谟斯并上场，且每次战斗至少释放1次高效处理&gt; 3星通关主题曲7-8；必须编入非助战休谟斯并上场，其他成员仅可编入近战位干员</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="16" t="inlineStr">
         <is>
-          <t>伊内丝</t>
+          <t>摩根</t>
         </is>
       </c>
       <c r="B301" s="16" t="inlineStr">
         <is>
-          <t>12-12</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C301" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D301" s="12" t="inlineStr">
         <is>
-          <t>maa://50280 (98.61), maa://49642 (97.67), maa://49660 (91.3), *maa://50517 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计部署非助战伊内丝12次&gt; 3星通关主题曲12-12标准实战环境；必须编入非助战伊内丝并上场，且至少使用3次暗夜无明</t>
+          <t>&gt; 由非助战摩根累计造成80000点伤害&gt; 3星通关主题曲4-5，必须编入非助战摩根并上场，且使用摩根至少歼灭10名敌人</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="16" t="inlineStr">
         <is>
-          <t>玫拉</t>
+          <t>洋灰</t>
         </is>
       </c>
       <c r="B302" s="16" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>IW-EX-6</t>
         </is>
       </c>
       <c r="C302" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D302" s="12" t="inlineStr">
         <is>
-          <t>maa://39171 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战玫拉并上场，且每次战斗至少释放1次临界爆发&gt; 3星通关主题曲S3-5；必须编入非助战玫拉并上场，其他成员仅可编入6名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战洋灰并上场，且每次战斗至少释放1次结构加固&gt; 3星通关别传IW-EX-6，必须编入非助战洋灰并上场，且不编入其他重装干员</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="16" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>伊内丝</t>
         </is>
       </c>
       <c r="B303" s="16" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>12-12</t>
         </is>
       </c>
       <c r="C303" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D303" s="12" t="inlineStr">
         <is>
-          <t>maa://27939 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战淬羽赫默累计使用无畏者协议8次&gt; 3星通关主题曲6-3；必须编入非助战淬羽赫默并上场，且所有干员不被击倒</t>
+          <t>&gt; 战斗中累计部署非助战伊内丝12次&gt; 3星通关主题曲12-12标准实战环境；必须编入非助战伊内丝并上场，且至少使用3次暗夜无明</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="16" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>玫拉</t>
         </is>
       </c>
       <c r="B304" s="16" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C304" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D304" s="12" t="inlineStr">
         <is>
-          <t>maa://53352 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战淬羽赫默并上场，且每次战斗至少释放1次无畏者协议&gt; 3星通关插曲WB-5；必须编入非助战淬羽赫默并上场，且所有干员不被击倒</t>
+          <t>&gt; 完成5次战斗；必须编入非助战玫拉并上场，且每次战斗至少释放1次临界爆发&gt; 3星通关主题曲S3-5；必须编入非助战玫拉并上场，其他成员仅可编入6名干员</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="16" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B305" s="16" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C305" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>maa://29129 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战霍尔海雅累计造成120000点伤害&gt; 3星通关别传OF-7；必须编入非助战霍尔海雅并上场，且至少使用2次博览者的狂语</t>
+          <t>&gt; 战斗中非助战淬羽赫默累计使用无畏者协议8次&gt; 3星通关主题曲6-3；必须编入非助战淬羽赫默并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="16" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B306" s="16" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C306" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D306" s="12" t="inlineStr">
         <is>
-          <t>maa://36005 (91.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战霍尔海雅并上场，且每次战斗至少释放1次博览者的狂语&gt; 3星通关主题曲4-3；必须编入非助战霍尔海雅并上场，且使用霍尔海雅至少歼灭10个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战淬羽赫默并上场，且每次战斗至少释放1次无畏者协议&gt; 3星通关插曲WB-5；必须编入非助战淬羽赫默并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="16" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B307" s="16" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C307" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D307" s="12" t="inlineStr">
         <is>
-          <t>maa://35859 (97.7)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E307" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战缪尔赛思，并确定第一位部署的干员是缪尔赛思&gt; 3星通关主题曲3-4；必须编入非助战缪尔赛思并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战霍尔海雅累计造成120000点伤害&gt; 3星通关别传OF-7；必须编入非助战霍尔海雅并上场，且至少使用2次博览者的狂语</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="16" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B308" s="16" t="inlineStr">
         <is>
-          <t>6-12</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C308" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D308" s="12" t="inlineStr">
         <is>
-          <t>maa://53348 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战缪尔赛思并上场，且每次战斗至少释放1次生态耦合&gt; 3星通关主题曲6-12；必须编入非助战缪尔赛思并上场，且使用2次生态耦合</t>
+          <t>&gt; 完成5次战斗；必须编入非助战霍尔海雅并上场，且每次战斗至少释放1次博览者的狂语&gt; 3星通关主题曲4-3；必须编入非助战霍尔海雅并上场，且使用霍尔海雅至少歼灭10个敌人</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="16" t="inlineStr">
         <is>
-          <t>隐现</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B309" s="16" t="inlineStr">
@@ -9186,2000 +9186,2000 @@
       </c>
       <c r="C309" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>**maa://39172 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E309" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战隐现累计造成30歼灭数&gt; 3星通关主题曲3-4；必须编入非助战隐现并上场，且不编入其他狙击干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战缪尔赛思，并确定第一位部署的干员是缪尔赛思&gt; 3星通关主题曲3-4；必须编入非助战缪尔赛思并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="16" t="inlineStr">
         <is>
-          <t>空构</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B310" s="16" t="inlineStr">
         <is>
-          <t>DM-2</t>
+          <t>6-12</t>
         </is>
       </c>
       <c r="C310" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D310" s="12" t="inlineStr">
         <is>
-          <t>maa://39173 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战空构累计造成60000点伤害&gt; 3星通关插曲DM-2；必须编入非助战空构并上场，且至少使用1次临场铳械改装</t>
+          <t>&gt; 完成5次战斗；必须编入非助战缪尔赛思并上场，且每次战斗至少释放1次生态耦合&gt; 3星通关主题曲6-12；必须编入非助战缪尔赛思并上场，且使用2次生态耦合</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="16" t="inlineStr">
         <is>
-          <t>圣约送葬人</t>
+          <t>隐现</t>
         </is>
       </c>
       <c r="B311" s="16" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C311" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D311" s="12" t="inlineStr">
         <is>
-          <t>maa://25775 (93.15), *maa://25393 (71.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E311" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战圣约送葬人累计造成80000点伤害&gt; 3星通关主题曲7-14；必须编入非助战圣约送葬人并上场，且使用圣约送葬人歼灭至少2名游击队盾卫</t>
+          <t>&gt; 由非助战隐现累计造成30歼灭数&gt; 3星通关主题曲3-4；必须编入非助战隐现并上场，且不编入其他狙击干员</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="16" t="inlineStr">
         <is>
-          <t>寒檀</t>
+          <t>空构</t>
         </is>
       </c>
       <c r="B312" s="16" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>DM-2</t>
         </is>
       </c>
       <c r="C312" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D312" s="12" t="inlineStr">
         <is>
-          <t>maa://40161 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战寒檀并上场，且每次战斗至少释放1次“女巫之泪”&gt; 3星通关别传BI-2；必须编入非助战寒檀并上场，且使用寒檀至少歼灭8个敌人</t>
+          <t>&gt; 由非助战空构累计造成60000点伤害&gt; 3星通关插曲DM-2；必须编入非助战空构并上场，且至少使用1次临场铳械改装</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="16" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>圣约送葬人</t>
         </is>
       </c>
       <c r="B313" s="16" t="inlineStr">
         <is>
-          <t>S2-1</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C313" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D313" s="12" t="inlineStr">
         <is>
-          <t>maa://25367 (99.26)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E313" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战提丰累计造成120000点伤害&gt; 3星通关主题曲S2-1；必须编入非助战提丰并上场，其他成员仅可编入近战位干员</t>
+          <t>&gt; 由非助战圣约送葬人累计造成80000点伤害&gt; 3星通关主题曲7-14；必须编入非助战圣约送葬人并上场，且使用圣约送葬人歼灭至少2名游击队盾卫</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="16" t="inlineStr">
         <is>
-          <t>凛视</t>
+          <t>寒檀</t>
         </is>
       </c>
       <c r="B314" s="16" t="inlineStr">
         <is>
-          <t>7-13</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C314" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D314" s="12" t="inlineStr">
         <is>
-          <t>*maa://43090 (61.54)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战凛视累计造成30次凋亡爆发&gt; 3星通关主题曲7-13；必须编入非助战凛视并上场，且凛视造成至少1次凋亡爆发</t>
+          <t>&gt; 完成5次战斗；必须编入非助战寒檀并上场，且每次战斗至少释放1次“女巫之泪”&gt; 3星通关别传BI-2；必须编入非助战寒檀并上场，且使用寒檀至少歼灭8个敌人</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="16" t="inlineStr">
         <is>
-          <t>苍苔</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B315" s="16" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>S2-1</t>
         </is>
       </c>
       <c r="C315" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D315" s="12" t="inlineStr">
         <is>
-          <t>maa://28070 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E315" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战苍苔并上场，且每次战斗至少释放1次土石的恒心&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战苍苔并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战提丰累计造成120000点伤害&gt; 3星通关主题曲S2-1；必须编入非助战提丰并上场，其他成员仅可编入近战位干员</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="16" t="inlineStr">
         <is>
-          <t>青枳</t>
+          <t>凛视</t>
         </is>
       </c>
       <c r="B316" s="16" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>7-13</t>
         </is>
       </c>
       <c r="C316" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D316" s="12" t="inlineStr">
         <is>
-          <t>maa://28241 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战青枳，并确定第一位部署的干员是青枳&gt; 3星通关别传OF-5；必须编入非助战青枳并上场，且不编入其他先锋干员</t>
+          <t>&gt; 由非助战凛视累计造成30次凋亡爆发&gt; 3星通关主题曲7-13；必须编入非助战凛视并上场，且凛视造成至少1次凋亡爆发</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="16" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>苍苔</t>
         </is>
       </c>
       <c r="B317" s="16" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C317" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D317" s="12" t="inlineStr">
         <is>
-          <t>maa://25773 (100.0), *maa://26088 (71.43)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E317" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战琳琅诗怀雅累计造成60000点伤害※香槟炸弹造成的伤害也会参与计数&gt; 3星通关主题曲5-2；必须编入非助战琳琅诗怀雅并上场，且使用琳琅诗怀雅至少歼灭15个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战苍苔并上场，且每次战斗至少释放1次土石的恒心&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战苍苔并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="16" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>青枳</t>
         </is>
       </c>
       <c r="B318" s="16" t="inlineStr">
         <is>
-          <t>11-16</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C318" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D318" s="12" t="inlineStr">
         <is>
-          <t>maa://39239 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战琳琅诗怀雅累计造成40歼灭数&gt; 3星通关主题曲11-16标准实战环境；必须编入非助战琳琅诗怀雅并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战青枳，并确定第一位部署的干员是青枳&gt; 3星通关别传OF-5；必须编入非助战青枳并上场，且不编入其他先锋干员</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="16" t="inlineStr">
         <is>
-          <t>纯烬艾雅法拉</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B319" s="16" t="inlineStr">
         <is>
-          <t>FC-5</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C319" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D319" s="12" t="inlineStr">
         <is>
-          <t>maa://39692 (99.8), maa://39810 (86.36)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E319" s="3" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战纯烬艾雅法拉并上场，且每次战斗至少释放1次火山回响&gt; 3星通关别传FC-5；必须编入非助战纯烬艾雅法拉并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战琳琅诗怀雅累计造成60000点伤害※香槟炸弹造成的伤害也会参与计数&gt; 3星通关主题曲5-2；必须编入非助战琳琅诗怀雅并上场，且使用琳琅诗怀雅至少歼灭15个敌人</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="16" t="inlineStr">
         <is>
-          <t>冰酿</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B320" s="16" t="inlineStr">
         <is>
-          <t>S3-3</t>
+          <t>11-16</t>
         </is>
       </c>
       <c r="C320" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D320" s="12" t="inlineStr">
         <is>
-          <t>*maa://39174 (75.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战冰酿累计造成80000伤害&gt; 3星通关主题曲S3-3；必须编入非助战冰酿并上场，且使用冰酿至少歼灭8个敌人</t>
+          <t>&gt; 由非助战琳琅诗怀雅累计造成40歼灭数&gt; 3星通关主题曲11-16标准实战环境；必须编入非助战琳琅诗怀雅并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="16" t="inlineStr">
         <is>
-          <t>杏仁</t>
+          <t>纯烬艾雅法拉</t>
         </is>
       </c>
       <c r="B321" s="16" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>FC-5</t>
         </is>
       </c>
       <c r="C321" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>maa://39175 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E321" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战杏仁累计使用强力牵引10次&gt; 3星通关别传BI-2；必须编入非助战杏仁并上场，且至少使用2次强力牵引</t>
+          <t>&gt; 完成5次战斗；必须编入非助战纯烬艾雅法拉并上场，且每次战斗至少释放1次火山回响&gt; 3星通关别传FC-5；必须编入非助战纯烬艾雅法拉并上场，且不编入其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="16" t="inlineStr">
         <is>
-          <t>涤火杰西卡</t>
+          <t>冰酿</t>
         </is>
       </c>
       <c r="B322" s="16" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>S3-3</t>
         </is>
       </c>
       <c r="C322" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D322" s="12" t="inlineStr">
         <is>
-          <t>maa://34867 (97.83), maa://34715 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战涤火杰西卡累计造成30歼灭数&gt; 3星通关主题曲3-8；必须编入非助战涤火杰西卡并上场，且使用涤火杰西卡歼灭碎骨</t>
+          <t>&gt; 由非助战冰酿累计造成80000伤害&gt; 3星通关主题曲S3-3；必须编入非助战冰酿并上场，且使用冰酿至少歼灭8个敌人</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="16" t="inlineStr">
         <is>
-          <t>维荻</t>
+          <t>杏仁</t>
         </is>
       </c>
       <c r="B323" s="16" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C323" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D323" s="12" t="inlineStr">
         <is>
-          <t>maa://39176 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E323" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战维荻累计造成60000点伤害&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战维荻并上场，且至少使用2次双刃毒藤</t>
+          <t>&gt; 战斗中非助战杏仁累计使用强力牵引10次&gt; 3星通关别传BI-2；必须编入非助战杏仁并上场，且至少使用2次强力牵引</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="16" t="inlineStr">
         <is>
-          <t>戴菲恩</t>
+          <t>涤火杰西卡</t>
         </is>
       </c>
       <c r="B324" s="16" t="inlineStr">
         <is>
-          <t>WD-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C324" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D324" s="12" t="inlineStr">
         <is>
-          <t>maa://42316 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战戴菲恩累计造成30歼灭数&gt; 3星通关插曲WD-6；必须携带且部署非助战戴菲恩，且至少使用2次抢攻</t>
+          <t>&gt; 由非助战涤火杰西卡累计造成30歼灭数&gt; 3星通关主题曲3-8；必须编入非助战涤火杰西卡并上场，且使用涤火杰西卡歼灭碎骨</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="16" t="inlineStr">
         <is>
-          <t>刺玫</t>
+          <t>维荻</t>
         </is>
       </c>
       <c r="B325" s="16" t="inlineStr">
         <is>
-          <t>IC-2</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C325" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>maa://30680 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E325" s="3" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战刺玫累计使用荆藤庇荫10次&gt; 3星通关别传IC-2；必须编入非助战刺玫并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战维荻累计造成60000点伤害&gt; 3星通关主题曲9-3标准实战环境；必须编入非助战维荻并上场，且至少使用2次双刃毒藤</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="16" t="inlineStr">
         <is>
-          <t>赫德雷</t>
+          <t>戴菲恩</t>
         </is>
       </c>
       <c r="B326" s="16" t="inlineStr">
         <is>
-          <t>IW-7</t>
+          <t>WD-6</t>
         </is>
       </c>
       <c r="C326" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D326" s="12" t="inlineStr">
         <is>
-          <t>maa://40956 (94.03)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战赫德雷累计歼灭5个精英或领袖敌人&gt; 3星通关别传IW-7；必须编入非助战赫德雷并上场，并使用赫德雷至少击败2名沉沙</t>
+          <t>&gt; 由非助战戴菲恩累计造成30歼灭数&gt; 3星通关插曲WD-6；必须携带且部署非助战戴菲恩，且至少使用2次抢攻</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="17" t="inlineStr">
-        <is>
-          <t>深律</t>
-        </is>
-      </c>
-      <c r="B327" s="17" t="inlineStr">
-        <is>
-          <t>LE-4</t>
-        </is>
-      </c>
-      <c r="C327" s="18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D327" s="19" t="inlineStr">
-        <is>
-          <t>**maa://39178 (33.33)</t>
-        </is>
-      </c>
-      <c r="E327" s="20" t="inlineStr">
-        <is>
-          <t>&gt; 完成5次战斗；必须编入非助战深律并上场，且每次战斗至少释放1次沉音宁神&gt; 3星通关别传LE-4；必须编入非助战深律并上场，且所有干员不被击倒</t>
+      <c r="A327" s="16" t="inlineStr">
+        <is>
+          <t>刺玫</t>
+        </is>
+      </c>
+      <c r="B327" s="16" t="inlineStr">
+        <is>
+          <t>IC-2</t>
+        </is>
+      </c>
+      <c r="C327" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D327" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E327" s="3" t="inlineStr">
+        <is>
+          <t>&gt; 战斗中非助战刺玫累计使用荆藤庇荫10次&gt; 3星通关别传IC-2；必须编入非助战刺玫并上场，且不编入其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="16" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>赫德雷</t>
         </is>
       </c>
       <c r="B328" s="16" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>IW-7</t>
         </is>
       </c>
       <c r="C328" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D328" s="12" t="inlineStr">
         <is>
-          <t>maa://34205 (87.5), **maa://39541 (50.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战止颂累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲7-11；必须编入非助战止颂并上场，且使用止颂歼灭至少2名雇佣军萨卡兹战士</t>
+          <t>&gt; 由非助战赫德雷累计歼灭5个精英或领袖敌人&gt; 3星通关别传IW-7；必须编入非助战赫德雷并上场，并使用赫德雷至少击败2名沉沙</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="16" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>深律</t>
         </is>
       </c>
       <c r="B329" s="16" t="inlineStr">
         <is>
-          <t>TW-5</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C329" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D329" s="12" t="inlineStr">
         <is>
-          <t>maa://43092 (100.0), maa://43093 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E329" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战止颂累计造成120000点伤害&gt; 3星通关别传TW-5；必须编入非助战止颂并上场，且使用止颂击败至少6名敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战深律并上场，且每次战斗至少释放1次沉音宁神&gt; 3星通关别传LE-4；必须编入非助战深律并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="16" t="inlineStr">
         <is>
-          <t>薇薇安娜</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B330" s="16" t="inlineStr">
         <is>
-          <t>MN-3</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C330" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D330" s="12" t="inlineStr">
         <is>
-          <t>maa://44234 (98.94)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>&gt; 由非助战薇薇安娜累计歼灭10个精英或领袖敌人&gt; 3星通关别传MN-3；必须编入非助战薇薇安娜并上场，且使用薇薇安娜歼灭“锈铜”奥尔默·英格拉</t>
+          <t>&gt; 由非助战止颂累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲7-11；必须编入非助战止颂并上场，且使用止颂歼灭至少2名雇佣军萨卡兹战士</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="13" t="inlineStr">
         <is>
-          <t>塑心</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B331" s="13" t="inlineStr">
         <is>
-          <t>GA-7</t>
+          <t>TW-5</t>
         </is>
       </c>
       <c r="C331" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D331" s="14" t="inlineStr">
         <is>
-          <t>maa://42968 (99.15), maa://49245 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E331" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战塑心累计造成75000点凋亡损伤&gt; 3星通关别传GA-7；必须编入非助战塑心并上场，且塑心造成至少15000点凋亡损伤</t>
+          <t>&gt; 由非助战止颂累计造成120000点伤害&gt; 3星通关别传TW-5；必须编入非助战止颂并上场，且使用止颂击败至少6名敌人</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>哈洛德</t>
+          <t>薇薇安娜</t>
         </is>
       </c>
       <c r="B332" s="13" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>MN-3</t>
         </is>
       </c>
       <c r="C332" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D332" s="14" t="inlineStr">
         <is>
-          <t>*maa://40162 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E332" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战哈洛德累计使用重症优先8次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战哈洛德并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战薇薇安娜累计歼灭10个精英或领袖敌人&gt; 3星通关别传MN-3；必须编入非助战薇薇安娜并上场，且使用薇薇安娜歼灭“锈铜”奥尔默·英格拉</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="13" t="inlineStr">
         <is>
-          <t>烈夏</t>
+          <t>塑心</t>
         </is>
       </c>
       <c r="B333" s="13" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>GA-7</t>
         </is>
       </c>
       <c r="C333" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D333" s="14" t="inlineStr">
         <is>
-          <t>maa://37692 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E333" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战烈夏累计造成30歼灭数&gt; 3星通关主题曲4-3；必须编入非助战烈夏并上场，且不编入其他近卫干员</t>
+          <t>&gt; 由非助战塑心累计造成75000点凋亡损伤&gt; 3星通关别传GA-7；必须编入非助战塑心并上场，且塑心造成至少15000点凋亡损伤</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>锏</t>
+          <t>哈洛德</t>
         </is>
       </c>
       <c r="B334" s="13" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C334" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D334" s="14" t="inlineStr">
         <is>
-          <t>maa://30671 (82.32), maa://30669 (99.17), maa://37275 (82.5), *maa://32410 (66.67), maa://41605 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E334" s="14" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战锏并上场，且每次战斗至少释放1次归于宁静&gt; 3星通关别传BI-6；必须编入非助战锏并上场，且使用锏至少歼灭10个敌人</t>
+          <t>&gt; 战斗中非助战哈洛德累计使用重症优先8次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战哈洛德并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="13" t="inlineStr">
         <is>
-          <t>莱伊</t>
+          <t>烈夏</t>
         </is>
       </c>
       <c r="B335" s="13" t="inlineStr">
         <is>
-          <t>S9-1</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C335" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D335" s="14" t="inlineStr">
         <is>
-          <t>maa://38295 (94.32), maa://49332 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E335" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战莱伊累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲S9-1标准实战环境；必须编入非助战莱伊并上场，且使用莱伊使用至少2次“得见光芒”</t>
+          <t>&gt; 由非助战烈夏累计造成30歼灭数&gt; 3星通关主题曲4-3；必须编入非助战烈夏并上场，且不编入其他近卫干员</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>万顷</t>
+          <t>锏</t>
         </is>
       </c>
       <c r="B336" s="13" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C336" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D336" s="14" t="inlineStr">
         <is>
-          <t>maa://32417 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E336" s="14" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战万顷累计使用支援号令·γ型10次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战万顷并上场，且至少使用2次应东风</t>
+          <t>&gt; 完成5次战斗；必须编入非助战锏并上场，且每次战斗至少释放1次归于宁静&gt; 3星通关别传BI-6；必须编入非助战锏并上场，且使用锏至少歼灭10个敌人</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="13" t="inlineStr">
         <is>
-          <t>小满</t>
+          <t>莱伊</t>
         </is>
       </c>
       <c r="B337" s="13" t="inlineStr">
         <is>
-          <t>9-11</t>
+          <t>S9-1</t>
         </is>
       </c>
       <c r="C337" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D337" s="14" t="inlineStr">
         <is>
-          <t>maa://32419 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E337" s="14" t="inlineStr">
         <is>
-          <t>&gt; 由非助战小满累计造成60000点伤害&gt; 3星通关主题曲9-11标准实战环境；必须编入非助战小满并上场，且至少使用2次乡音沉沉</t>
+          <t>&gt; 由非助战莱伊累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲S9-1标准实战环境；必须编入非助战莱伊并上场，且使用莱伊使用至少2次“得见光芒”</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>万顷</t>
         </is>
       </c>
       <c r="B338" s="13" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C338" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>maa://32416 (90.91)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>&gt; 由非助战左乐累计造成40歼灭数&gt; 3星通关别传WB-5；必须编入非助战左乐并上场，且使用左乐至少歼灭8个敌人</t>
+          <t>&gt; 战斗中非助战万顷累计使用支援号令·γ型10次&gt; 3星通关主题曲9-13标准实战环境；必须编入非助战万顷并上场，且至少使用2次应东风</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="13" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>小满</t>
         </is>
       </c>
       <c r="B339" s="13" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>9-11</t>
         </is>
       </c>
       <c r="C339" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>maa://45800 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战左乐累计造成100000点伤害&gt; 3星通关别传RI-7；必须携带且部署非助战左乐，且至少释放3次佑序有炎</t>
+          <t>&gt; 由非助战小满累计造成60000点伤害&gt; 3星通关主题曲9-11标准实战环境；必须编入非助战小满并上场，且至少使用2次乡音沉沉</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>黍</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B340" s="13" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C340" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>maa://32647 (97.83), maa://32415 (96.73), maa://34677 (100.0), maa://32892 (100.0), maa://32653 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战黍并上场，且每次战斗至少释放1次离离枯荣&gt; 3星通关主题曲11-11标准实战环境；必须编入非助战黍并上场，且所有干员不被击倒</t>
+          <t>&gt; 由非助战左乐累计造成40歼灭数&gt; 3星通关别传WB-5；必须编入非助战左乐并上场，且使用左乐至少歼灭8个敌人</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="13" t="inlineStr">
         <is>
-          <t>红隼</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B341" s="13" t="inlineStr">
         <is>
-          <t>11-18</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C341" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>maa://32420 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战红隼并上场，且每次战斗至少释放2次醉刃乱舞&gt; 3星通关主题曲11-18标准实战环境；必须编入非助战红隼，且第一位部署红隼、红隼全程不撤退或被击倒</t>
+          <t>&gt; 使用非助战左乐累计造成100000点伤害&gt; 3星通关别传RI-7；必须携带且部署非助战左乐，且至少释放3次佑序有炎</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>导火索</t>
+          <t>黍</t>
         </is>
       </c>
       <c r="B342" s="13" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="C342" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>maa://35606 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>&gt; 由非助战导火索累计造成80000点伤害&gt; 3星通关主题曲3-1；必须编入非助战导火索并上场，且使用导火索至少歼灭30个敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战黍并上场，且每次战斗至少释放1次离离枯荣&gt; 3星通关主题曲11-11标准实战环境；必须编入非助战黍并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="13" t="inlineStr">
         <is>
-          <t>双月</t>
+          <t>红隼</t>
         </is>
       </c>
       <c r="B343" s="13" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>11-18</t>
         </is>
       </c>
       <c r="C343" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>maa://34716 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战双月累计使用全知者的战术10次&gt; 3星通关主题曲3-7；必须编入非助战双月并上场，且至少使用2次全知者的战术</t>
+          <t>&gt; 完成5次战斗；必须编入非助战红隼并上场，且每次战斗至少释放2次醉刃乱舞&gt; 3星通关主题曲11-18标准实战环境；必须编入非助战红隼，且第一位部署红隼、红隼全程不撤退或被击倒</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>导火索</t>
         </is>
       </c>
       <c r="B344" s="13" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C344" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>maa://39179 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战医生累计使用激素手枪8次&gt; 3星通关主题曲2-5；必须编入非助战医生并上场，且不编入医疗干员</t>
+          <t>&gt; 由非助战导火索累计造成80000点伤害&gt; 3星通关主题曲3-1；必须编入非助战导火索并上场，且使用导火索至少歼灭30个敌人</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="13" t="inlineStr">
         <is>
-          <t>艾拉</t>
+          <t>双月</t>
         </is>
       </c>
       <c r="B345" s="13" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C345" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>maa://34865 (97.73), maa://34717 (94.03), *maa://45066 (66.67)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战艾拉累计部署雷鸣地雷30个&gt; 3星通关插曲DM-EX-1；必须编入非助战艾拉并上场，且使用艾拉歼灭至少2名萨卡兹穿刺手</t>
+          <t>&gt; 战斗中非助战双月累计使用全知者的战术10次&gt; 3星通关主题曲3-7；必须编入非助战双月并上场，且至少使用2次全知者的战术</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>露托</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="B346" s="13" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C346" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>maa://39180 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战露托累计使用强磁防卫8次&gt; 3星通关主题曲3-1；必须编入非助战露托并上场，且不编入其他重装干员</t>
+          <t>&gt; 战斗中非助战医生累计使用激素手枪8次&gt; 3星通关主题曲2-5；必须编入非助战医生并上场，且不编入医疗干员</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="13" t="inlineStr">
         <is>
-          <t>奥达</t>
+          <t>艾拉</t>
         </is>
       </c>
       <c r="B347" s="13" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C347" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>maa://45834 (100.0), maa://45833 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战奥达累计使用4次锻锤之力&gt; 3星通关主题曲S3-6；必须携带且部署非助战奥达，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中非助战艾拉累计部署雷鸣地雷30个&gt; 3星通关插曲DM-EX-1；必须编入非助战艾拉并上场，且使用艾拉歼灭至少2名萨卡兹穿刺手</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>阿罗玛</t>
+          <t>露托</t>
         </is>
       </c>
       <c r="B348" s="13" t="inlineStr">
         <is>
-          <t>GT-HX-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C348" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>maa://39181 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战阿罗玛并上场，且每次战斗至少释放1次小心地滑&gt; 3星通关别传GT-HX-3；必须编入非助战阿罗玛并上场，且使用阿罗玛至少歼灭20个敌人</t>
+          <t>&gt; 战斗中非助战露托累计使用强磁防卫8次&gt; 3星通关主题曲3-1；必须编入非助战露托并上场，且不编入其他重装干员</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="13" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>奥达</t>
         </is>
       </c>
       <c r="B349" s="13" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C349" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>maa://36868 (100.0), maa://35996 (97.3), **maa://39217 (41.18), maa://47349 (96.3)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>&gt; 由非助战阿斯卡纶累计造成180000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战阿斯卡纶并上场，且使用阿斯卡纶至少歼灭30个敌人</t>
+          <t>&gt; 使用非助战奥达累计使用4次锻锤之力&gt; 3星通关主题曲S3-6；必须携带且部署非助战奥达，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>历阵锐枪芬</t>
+          <t>阿罗玛</t>
         </is>
       </c>
       <c r="B350" s="13" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>GT-HX-3</t>
         </is>
       </c>
       <c r="C350" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>maa://36647 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战历阵锐枪芬，并确定第一位部署的干员是历阵锐枪芬&gt; 3星通关主题曲4-2；必须编入非助战历阵锐枪芬并上场，且不编入其他先锋干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战阿罗玛并上场，且每次战斗至少释放1次小心地滑&gt; 3星通关别传GT-HX-3；必须编入非助战阿罗玛并上场，且使用阿罗玛至少歼灭20个敌人</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="13" t="inlineStr">
         <is>
-          <t>魔王</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B351" s="13" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C351" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>maa://42299 (97.5), maa://42224 (81.25)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>&gt; 携带非助战魔王完成5次战斗，且每次战斗至少发动一次“编织重构现世”&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战魔王并上场，其他成员仅可编入近战位干员</t>
+          <t>&gt; 由非助战阿斯卡纶累计造成180000点伤害&gt; 3星通关主题曲11-6标准实战环境；必须编入非助战阿斯卡纶并上场，且使用阿斯卡纶至少歼灭30个敌人</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B352" s="13" t="inlineStr">
         <is>
-          <t>14-9</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C352" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>maa://49648 (94.87), *maa://49662 (69.23)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>&gt; 由非助战逻各斯累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲14-9标准实战环境；必须编入非助战逻各斯并上场，且使用逻各斯至少歼灭7个敌人</t>
+          <t>&gt; 战斗中非助战阿斯卡纶累计使用“降临”5次&gt; 3星通关主题曲5-10，必须编入非助战阿斯卡纶并上场，其他成员不可编入特种干员</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="13" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>历阵锐枪芬</t>
         </is>
       </c>
       <c r="B353" s="13" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C353" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>maa://36646 (98.78), maa://36845 (95.45), **maa://39217 (41.18), maa://51007 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>&gt; 由非助战逻各斯累计造成100000点伤害&gt; 3星通关主题曲11-6标准实战环境，必须编入非助战逻各斯并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战历阵锐枪芬，并确定第一位部署的干员是历阵锐枪芬&gt; 3星通关主题曲4-2；必须编入非助战历阵锐枪芬并上场，且不编入其他先锋干员</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>维什戴尔</t>
+          <t>魔王</t>
         </is>
       </c>
       <c r="B354" s="13" t="inlineStr">
         <is>
-          <t>DM-5</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C354" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>maa://36645 (98.34), maa://36841 (92.54), maa://37484 (94.12), maa://37858 (93.33), maa://40489 (100.0), maa://56268 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>&gt; 由非助战维什戴尔累计造成120000伤害&gt; 3星通关插曲DM-5；必须编入非助战维什戴尔并上场，且使用维什戴尔至少歼灭20个敌人</t>
+          <t>&gt; 携带非助战魔王完成5次战斗，且每次战斗至少发动一次“编织重构现世”&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战魔王并上场，其他成员仅可编入近战位干员</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="13" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B355" s="13" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>14-9</t>
         </is>
       </c>
       <c r="C355" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>maa://42635 (97.44), maa://50629 (100.0), maa://48859 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战医疗职业的阿米娅累计使用慈悲愿景5次&gt; 3星通关主题曲3-8；必须编入非助战医疗职业的阿米娅并上场，且不编入其他医疗干员</t>
+          <t>&gt; 由非助战逻各斯累计歼灭10个精英或领袖敌人&gt; 3星通关主题曲14-9标准实战环境；必须编入非助战逻各斯并上场，且使用逻各斯至少歼灭7个敌人</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>深巡</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B356" s="13" t="inlineStr">
         <is>
-          <t>SN-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C356" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>maa://39183 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战深巡累计使用行动能力剥夺8次&gt; 3星通关插曲SN-5，必须编入非助战深巡并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战逻各斯累计造成100000点伤害&gt; 3星通关主题曲11-6标准实战环境，必须编入非助战逻各斯并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="13" t="inlineStr">
         <is>
-          <t>海霓</t>
+          <t>维什戴尔</t>
         </is>
       </c>
       <c r="B357" s="13" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>DM-5</t>
         </is>
       </c>
       <c r="C357" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>maa://39184 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战海霓累计使用阻滞性显色剂8次&gt; 3星通关插曲SV-4；必须编入非助战海霓并上场，且不编入其他辅助干员</t>
+          <t>&gt; 由非助战维什戴尔累计造成120000伤害&gt; 3星通关插曲DM-5；必须编入非助战维什戴尔并上场，且使用维什戴尔至少歼灭20个敌人</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>乌尔比安</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B358" s="13" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C358" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>maa://40957 (93.18), maa://44635 (87.62), maa://48026 (96.15), maa://41035 (92.19), maa://44660 (92.31), maa://41128 (83.78)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战乌尔比安累计使用必须开辟的通路10次&gt; 3星通关插曲SV-6；必须编入非助战乌尔比安并上场，并使用乌尔比安至少击败2名囊海爬行者</t>
+          <t>&gt; 战斗中非助战医疗职业的阿米娅累计使用慈悲愿景5次&gt; 3星通关主题曲3-8；必须编入非助战医疗职业的阿米娅并上场，且不编入其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="13" t="inlineStr">
         <is>
-          <t>渡桥</t>
+          <t>深巡</t>
         </is>
       </c>
       <c r="B359" s="13" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>SN-5</t>
         </is>
       </c>
       <c r="C359" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>maa://40164 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战渡桥累计使用承压功率8次&gt; 3星通关主题曲3-1；必须编入非助战渡桥并上场，且至少使用3次承压功率</t>
+          <t>&gt; 战斗中非助战深巡累计使用行动能力剥夺8次&gt; 3星通关插曲SN-5，必须编入非助战深巡并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>锡人</t>
+          <t>海霓</t>
         </is>
       </c>
       <c r="B360" s="13" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C360" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>maa://48268 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战锡人累计使用8次“大拉里”&gt; 3星通关主题曲4-3，必须编入非助战锡人并上场，且队伍中不能有其他医疗干员</t>
+          <t>&gt; 战斗中非助战海霓累计使用阻滞性显色剂8次&gt; 3星通关插曲SV-4；必须编入非助战海霓并上场，且不编入其他辅助干员</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="13" t="inlineStr">
         <is>
-          <t>衡沙</t>
+          <t>乌尔比安</t>
         </is>
       </c>
       <c r="B361" s="13" t="inlineStr">
         <is>
-          <t>DV-2</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C361" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>maa://40165 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>&gt; 战斗中累计召唤非助战衡沙的召唤物20回&gt; 3星通关别传DV-2；必须编入非助战衡沙并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 战斗中非助战乌尔比安累计使用必须开辟的通路10次&gt; 3星通关插曲SV-6；必须编入非助战乌尔比安并上场，并使用乌尔比安至少击败2名囊海爬行者</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>渡桥</t>
         </is>
       </c>
       <c r="B362" s="13" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C362" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>maa://45798 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>&gt; 由非助战佩佩累计造成40歼灭数&gt; 3星通关主题曲3-8；必须编入非助战佩佩并上场，且使用佩佩歼灭碎骨</t>
+          <t>&gt; 战斗中非助战渡桥累计使用承压功率8次&gt; 3星通关主题曲3-1；必须编入非助战渡桥并上场，且至少使用3次承压功率</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="13" t="inlineStr">
         <is>
-          <t>森西</t>
+          <t>锡人</t>
         </is>
       </c>
       <c r="B363" s="13" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C363" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>maa://42331 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战森西累计使用团体魔物大餐6次&gt; 3星通关主题曲1-12；必须编入非助战森西并上场，且所有干员不被击倒</t>
+          <t>&gt; 战斗中非助战锡人累计使用8次“大拉里”&gt; 3星通关主题曲4-3，必须编入非助战锡人并上场，且队伍中不能有其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>齐尔查克</t>
+          <t>衡沙</t>
         </is>
       </c>
       <c r="B364" s="13" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>DV-2</t>
         </is>
       </c>
       <c r="C364" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>maa://42333 (100.0), maa://41977 (100.0), maa://50518 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战齐尔查克累计使用随机应变6次&gt; 3星通关主题曲4-3；必须编入非助战齐尔查克并上场，其他成员不可编入先锋干员</t>
+          <t>&gt; 战斗中累计召唤非助战衡沙的召唤物20回&gt; 3星通关别传DV-2；必须编入非助战衡沙并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="13" t="inlineStr">
         <is>
-          <t>莱欧斯</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B365" s="13" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C365" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>maa://42338 (100.0), maa://41976 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战莱欧斯并上场，且每次战斗至少释放1次威吓战法&gt; 3星通关主题曲2-4；必须编入非助战莱欧斯并上场，并使用莱欧斯至少击败1名高阶术师</t>
+          <t>&gt; 由非助战佩佩累计造成40歼灭数&gt; 3星通关主题曲3-8；必须编入非助战佩佩并上场，且使用佩佩歼灭碎骨</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>玛露西尔</t>
+          <t>森西</t>
         </is>
       </c>
       <c r="B366" s="13" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C366" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>maa://41110 (98.21), maa://45605 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>&gt; 由非助战玛露西尔累计造成100000点伤害&gt; 3星通关主题曲5-10；必须编入非助战玛露西尔并上场，且使用玛露西尔至少歼灭10名敌人</t>
+          <t>&gt; 战斗中非助战森西累计使用团体魔物大餐6次&gt; 3星通关主题曲1-12；必须编入非助战森西并上场，且所有干员不被击倒</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="13" t="inlineStr">
         <is>
-          <t>凯瑟琳</t>
+          <t>齐尔查克</t>
         </is>
       </c>
       <c r="B367" s="13" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C367" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>maa://42343 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战凯瑟琳累计部署15个“支援装置”&gt; 3星通关主题曲11-7标准实战环境；必须编入非助战凯瑟琳并上场，且凯瑟琳使用至少2次“战火淬炼”</t>
+          <t>&gt; 战斗中非助战齐尔查克累计使用随机应变6次&gt; 3星通关主题曲4-3；必须编入非助战齐尔查克并上场，其他成员不可编入先锋干员</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="13" t="inlineStr">
         <is>
-          <t>波卜</t>
+          <t>莱欧斯</t>
         </is>
       </c>
       <c r="B368" s="13" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C368" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>maa://43095 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>&gt; 由非助战波卜累计造成30次灼燃爆发&gt; 3星通关主题曲4-8；必须编入非助战波卜并上场，且波卜使用至少2次“此路不通”</t>
+          <t>&gt; 完成5次战斗；必须编入非助战莱欧斯并上场，且每次战斗至少释放1次威吓战法&gt; 3星通关主题曲2-4；必须编入非助战莱欧斯并上场，并使用莱欧斯至少击败1名高阶术师</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="13" t="inlineStr">
         <is>
-          <t>维娜·维多利亚</t>
+          <t>玛露西尔</t>
         </is>
       </c>
       <c r="B369" s="13" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C369" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>maa://44233 (91.49), maa://45570 (97.62)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>&gt; 由非助战维娜·维多利亚累计造成120000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战维娜·维多利亚并上场，其他成员仅可编入5名干员</t>
+          <t>&gt; 由非助战玛露西尔累计造成100000点伤害&gt; 3星通关主题曲5-10；必须编入非助战玛露西尔并上场，且使用玛露西尔至少歼灭10名敌人</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="13" t="inlineStr">
         <is>
-          <t>裁度</t>
+          <t>凯瑟琳</t>
         </is>
       </c>
       <c r="B370" s="13" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C370" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>maa://43097 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战裁度并部署至少2次，且使用裁度击败至少4名敌人&gt; 3星通关主题曲5-8；必须编入非助战裁度并上场，且至少束缚12次敌人</t>
+          <t>&gt; 使用非助战凯瑟琳累计部署15个“支援装置”&gt; 3星通关主题曲11-7标准实战环境；必须编入非助战凯瑟琳并上场，且凯瑟琳使用至少2次“战火淬炼”</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="13" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>波卜</t>
         </is>
       </c>
       <c r="B371" s="13" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C371" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>maa://43872 (85.71)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；每次战斗至少部署3次非助战弑君者&gt; 3星通关主题曲4-4；必须编入非助战弑君者并上场，且不编入其他特种干员</t>
+          <t>&gt; 由非助战波卜累计造成30次灼燃爆发&gt; 3星通关主题曲4-8；必须编入非助战波卜并上场，且波卜使用至少2次“此路不通”</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="13" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>维娜·维多利亚</t>
         </is>
       </c>
       <c r="B372" s="13" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C372" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>maa://53307 (83.33)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战弑君者累计使用8次烽烟行刑场&gt; 3星通关主题曲4-8；必须编入非助战弑君者并上场，且使用2次烽烟行刑场</t>
+          <t>&gt; 由非助战维娜·维多利亚累计造成120000点伤害&gt; 3星通关主题曲9-5标准实战环境；必须编入非助战维娜·维多利亚并上场，其他成员仅可编入5名干员</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="13" t="inlineStr">
         <is>
-          <t>忍冬</t>
+          <t>裁度</t>
         </is>
       </c>
       <c r="B373" s="13" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C373" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>maa://43875 (98.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>&gt; 由非助战忍冬累计造成80000点伤害&gt; 3星通关主题曲S2-3；必须编入非助战忍冬并上场，且使用忍冬击败至少24名敌人</t>
+          <t>&gt; 完成5次战斗；必须编入非助战裁度并部署至少2次，且使用裁度击败至少4名敌人&gt; 3星通关主题曲5-8；必须编入非助战裁度并上场，且至少束缚12次敌人</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="13" t="inlineStr">
         <is>
-          <t>荒芜拉普兰德</t>
+          <t>弑君者</t>
         </is>
       </c>
       <c r="B374" s="13" t="inlineStr">
         <is>
-          <t>IS-8</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C374" s="13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>maa://42970 (86.53), maa://44745 (98.77), **maa://49516 (50.0), *maa://45952 (80.0), ***maa://46851 (14.29), maa://44896 (87.5)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>&gt; 由非助战荒芜拉普兰德累计造成150000点伤害&gt; 3星通关别传IS-8；必须编入非助战荒芜拉普兰德并上场，且荒芜拉普兰德使用至少2次逐猎狂飙或终幕·浩劫</t>
+          <t>&gt; 完成5次战斗；每次战斗至少部署3次非助战弑君者&gt; 3星通关主题曲4-4；必须编入非助战弑君者并上场，且不编入其他特种干员</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="13" t="inlineStr">
         <is>
-          <t>瑰盐</t>
+          <t>弑君者</t>
         </is>
       </c>
       <c r="B375" s="13" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C375" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>maa://44389 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战瑰盐累计使用绝妙的长效药呀8次&gt; 3星通关主题曲4-6；必须编入非助战瑰盐并上场，且至少使用1次绝妙的长效药呀</t>
+          <t>&gt; 战斗中非助战弑君者累计使用8次烽烟行刑场&gt; 3星通关主题曲4-8；必须编入非助战弑君者并上场，且使用2次烽烟行刑场</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="13" t="inlineStr">
         <is>
-          <t>引星棘刺</t>
+          <t>忍冬</t>
         </is>
       </c>
       <c r="B376" s="13" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C376" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>maa://48113 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战引星棘刺累计使用20次解构涌潮&gt; 3星通关别传OF-7；必须编入非助战引星棘刺并上场，其他成员仅可编入4名干员</t>
+          <t>&gt; 由非助战忍冬累计造成80000点伤害&gt; 3星通关主题曲S2-3；必须编入非助战忍冬并上场，且使用忍冬击败至少24名敌人</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="13" t="inlineStr">
         <is>
-          <t>行箸</t>
+          <t>荒芜拉普兰德</t>
         </is>
       </c>
       <c r="B377" s="13" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>IS-8</t>
         </is>
       </c>
       <c r="C377" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>maa://45807 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战行箸累计使用8次食不厌精&gt; 3星通关主题曲3-2；必须编入非助战行箸并上场，且所有干员不能被击倒</t>
+          <t>&gt; 由非助战荒芜拉普兰德累计造成150000点伤害&gt; 3星通关别传IS-8；必须编入非助战荒芜拉普兰德并上场，且荒芜拉普兰德使用至少2次逐猎狂飙或终幕·浩劫</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="13" t="inlineStr">
         <is>
-          <t>寻澜</t>
+          <t>瑰盐</t>
         </is>
       </c>
       <c r="B378" s="13" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C378" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>maa://50552 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战寻澜并上场，且使用寻澜歼灭至少3个敌人&gt; 3星通关主题曲3-5；必须编入非助战寻澜并上场，且至少使用2次洞悉</t>
+          <t>&gt; 战斗中非助战瑰盐累计使用绝妙的长效药呀8次&gt; 3星通关主题曲4-6；必须编入非助战瑰盐并上场，且至少使用1次绝妙的长效药呀</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="13" t="inlineStr">
         <is>
-          <t>诺威尔</t>
+          <t>特克诺</t>
         </is>
       </c>
       <c r="B379" s="13" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C379" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>maa://47175 (100.0), maa://47174 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战诺威尔并上场，且每次战斗至少释放1次生命不息&gt; 3星通关主题曲5-7；必须编入非助战诺威尔并上场，且队伍中不能有其他医疗干员</t>
+          <t>&gt; 完成5次战斗；必须编入非助战特克诺并上场，且每次战斗至少释放1次“恣意挥洒”&gt; 3星通关插曲DH-6，必须编入非助战特克诺并上场，其他成员仅可编入7名干员</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="13" t="inlineStr">
         <is>
-          <t>隐德来希</t>
+          <t>引星棘刺</t>
         </is>
       </c>
       <c r="B380" s="13" t="inlineStr">
         <is>
-          <t>10-12</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C380" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>maa://47023 (86.21)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战隐德来希累计造成100000点伤害&gt; 3星通关主题曲10-12标准实战环境；必须编入非助战隐德来希并上场，且隐德来希至少使用3次灵与欲的惜别</t>
+          <t>&gt; 战斗中非助战引星棘刺累计使用20次解构涌潮&gt; 3星通关别传OF-7；必须编入非助战引星棘刺并上场，其他成员仅可编入4名干员</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="13" t="inlineStr">
         <is>
-          <t>钼铅</t>
+          <t>行箸</t>
         </is>
       </c>
       <c r="B381" s="13" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C381" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>maa://48618 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>&gt; 战斗中非助战钼铅累计部署矿石“杀手”30个&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战钼铅并上场，且使用钼铅至少击败1名深池重甲卫士</t>
+          <t>&gt; 使用非助战行箸累计使用8次食不厌精&gt; 3星通关主题曲3-2；必须编入非助战行箸并上场，且所有干员不能被击倒</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="13" t="inlineStr">
         <is>
-          <t>骋风</t>
+          <t>寻澜</t>
         </is>
       </c>
       <c r="B382" s="13" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C382" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>maa://51907 (100.0), maa://51908 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战骋风并上场，且每次战斗至少释放1次招无虚发&gt; 3星通关插曲SN-2；必须编入非助战骋风并上场，且使用2次招无虚发</t>
+          <t>&gt; 完成5次战斗；必须编入非助战寻澜并上场，且使用寻澜歼灭至少3个敌人&gt; 3星通关主题曲3-5；必须编入非助战寻澜并上场，且至少使用2次洞悉</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="13" t="inlineStr">
         <is>
-          <t>阿兰娜</t>
+          <t>诺威尔</t>
         </is>
       </c>
       <c r="B383" s="13" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>5-7</t>
         </is>
       </c>
       <c r="C383" s="13" t="inlineStr">
@@ -11194,88 +11194,250 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>&gt; 使用非助战阿兰娜累计部署15个“支援装置”&gt; 3星通关主题曲7-14；必须编入非助战阿兰娜并上场，且至少使用2次“万斤顶”</t>
+          <t>&gt; 完成5次战斗；必须编入非助战诺威尔并上场，且每次战斗至少释放1次生命不息&gt; 3星通关主题曲5-7；必须编入非助战诺威尔并上场，且队伍中不能有其他医疗干员</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="13" t="inlineStr">
         <is>
-          <t>信仰搅拌机</t>
+          <t>隐德来希</t>
         </is>
       </c>
       <c r="B384" s="13" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C384" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>maa://51898 (100.0), maa://57241 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>&gt; 完成5次战斗；必须编入非助战信仰搅拌机并上场，且每次战斗至少释放1次退休前布道&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战信仰搅拌机并上场，且使用信仰搅拌机歼灭至少10名敌人</t>
+          <t>&gt; 使用非助战隐德来希累计造成100000点伤害&gt; 3星通关主题曲10-12标准实战环境；必须编入非助战隐德来希并上场，且隐德来希至少使用3次灵与欲的惜别</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="13" t="inlineStr">
         <is>
-          <t>蕾缪安</t>
+          <t>钼铅</t>
         </is>
       </c>
       <c r="B385" s="13" t="inlineStr">
         <is>
-          <t>13-13</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C385" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>maa://51880 (99.48), maa://51878 (100.0), maa://56651 (100.0)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>&gt; 由非助战蕾缪安累计造成30歼灭数&gt; 3星通关主题曲13-13标准实战环境；必须编入非助战蕾缪安并上场，且蕾缪安歼灭至少2个萨卡兹骸骨鞭笞者</t>
+          <t>&gt; 战斗中非助战钼铅累计部署矿石“杀手”30个&gt; 3星通关主题曲9-6标准实战环境；必须编入非助战钼铅并上场，且使用钼铅至少击败1名深池重甲卫士</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="13" t="inlineStr">
         <is>
+          <t>死芒</t>
+        </is>
+      </c>
+      <c r="B386" s="13" t="inlineStr">
+        <is>
+          <t>4-8</t>
+        </is>
+      </c>
+      <c r="C386" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>&gt; 完成5次战斗；必须编入非助战死芒并上场，且每次战斗至少释放2次“冠死以冕”&gt; 3星通关主题曲4-8，必须编入非助战死芒并上场，其他成员仅可编入辅助干员</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="13" t="inlineStr">
+        <is>
+          <t>骋风</t>
+        </is>
+      </c>
+      <c r="B387" s="13" t="inlineStr">
+        <is>
+          <t>SN-2</t>
+        </is>
+      </c>
+      <c r="C387" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>&gt; 完成5次战斗；必须编入非助战骋风并上场，且每次战斗至少释放1次招无虚发&gt; 3星通关插曲SN-2；必须编入非助战骋风并上场，且使用2次招无虚发</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="13" t="inlineStr">
+        <is>
+          <t>阿兰娜</t>
+        </is>
+      </c>
+      <c r="B388" s="13" t="inlineStr">
+        <is>
+          <t>7-14</t>
+        </is>
+      </c>
+      <c r="C388" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>&gt; 使用非助战阿兰娜累计部署15个“支援装置”&gt; 3星通关主题曲7-14；必须编入非助战阿兰娜并上场，且至少使用2次“万斤顶”</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="13" t="inlineStr">
+        <is>
+          <t>信仰搅拌机</t>
+        </is>
+      </c>
+      <c r="B389" s="13" t="inlineStr">
+        <is>
+          <t>14-5</t>
+        </is>
+      </c>
+      <c r="C389" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>&gt; 完成5次战斗；必须编入非助战信仰搅拌机并上场，且每次战斗至少释放1次退休前布道&gt; 3星通关主题曲14-5标准实战环境；必须编入非助战信仰搅拌机并上场，且使用信仰搅拌机歼灭至少10名敌人</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="13" t="inlineStr">
+        <is>
+          <t>蕾缪安</t>
+        </is>
+      </c>
+      <c r="B390" s="13" t="inlineStr">
+        <is>
+          <t>13-13</t>
+        </is>
+      </c>
+      <c r="C390" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>&gt; 由非助战蕾缪安累计造成30歼灭数&gt; 3星通关主题曲13-13标准实战环境；必须编入非助战蕾缪安并上场，且蕾缪安歼灭至少2个萨卡兹骸骨鞭笞者</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="13" t="inlineStr">
+        <is>
           <t>新约能天使</t>
         </is>
       </c>
-      <c r="B386" s="13" t="inlineStr">
+      <c r="B391" s="13" t="inlineStr">
         <is>
           <t>GA-EX-5</t>
         </is>
       </c>
-      <c r="C386" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>maa://51872 (95.89), maa://51876 (98.46), maa://51873 (100.0)</t>
-        </is>
-      </c>
-      <c r="E386" t="inlineStr">
+      <c r="C391" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
         <is>
           <t>&gt; 战斗中非助战新约能天使累计使用开火成瘾症8次&gt; 3星通关插曲GA-EX-5；必须编入非助战新约能天使并上场，且使用2次开火成瘾症</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="13" t="inlineStr">
+        <is>
+          <t>酒神</t>
+        </is>
+      </c>
+      <c r="B392" s="13" t="inlineStr">
+        <is>
+          <t>9-6</t>
+        </is>
+      </c>
+      <c r="C392" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>&gt; 使用非助战酒神累计造成60000点神经损伤&gt; 3星通关主题曲9-6标准实战环境，必须编入非助战酒神并上场，且酒神使用至少2次“空剧场”</t>
         </is>
       </c>
     </row>
